--- a/data/meta_analysis/Cat meta-analysis - correlations.xlsx
+++ b/data/meta_analysis/Cat meta-analysis - correlations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ejlundgren/Dropbox/Projects/iucn_evidence/CATS/data/meta_analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wallacha@qut.edu.au/Documents/Research/Manuscripts/Death Star/Cats vs vertebrates/Datasets/Meta-analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128F564A-E351-9E4E-A688-491617E1894B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2313D25-3F2E-3540-B07B-45353F44CC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29380" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29380" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Correlations" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5709" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6034" uniqueCount="228">
   <si>
     <t>scientificName</t>
   </si>
@@ -704,16 +704,19 @@
     <t>Baker</t>
   </si>
   <si>
-    <t>ES_ARM</t>
+    <t>unit_of_replication</t>
   </si>
   <si>
-    <t>Peromyscus pseudocrinitus</t>
+    <t>Plots</t>
   </si>
   <si>
-    <t>Rodríguez-Moreno A, Arnaud G, Tershy BR (2007) Impacto de la eradicación del gato (Felis catus), en dos roedores endémicos de la Isla Coronados, Golfo de California, México. Acta Zoológica Mexicana, 23, 1-13.</t>
+    <t>Sites</t>
   </si>
   <si>
-    <t>Isla Coronados, Gulf of California</t>
+    <t>Nests</t>
+  </si>
+  <si>
+    <t>Surveys</t>
   </si>
 </sst>
 </file>
@@ -881,7 +884,7 @@
     </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1146,13 +1149,22 @@
     <xf numFmtId="17" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="17" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
@@ -2280,7 +2292,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AO493"/>
+  <dimension ref="A1:AO481"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
@@ -2307,7 +2319,7 @@
     <col min="24" max="16384" width="8.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>128</v>
       </c>
@@ -2374,8 +2386,11 @@
       <c r="V1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W1" s="88" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>129</v>
       </c>
@@ -2430,8 +2445,11 @@
       <c r="V2" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W2" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>129</v>
       </c>
@@ -2486,8 +2504,11 @@
       <c r="V3" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W3" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>129</v>
       </c>
@@ -2542,8 +2563,11 @@
       <c r="V4" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W4" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>129</v>
       </c>
@@ -2598,8 +2622,11 @@
       <c r="V5" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W5" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>129</v>
       </c>
@@ -2654,8 +2681,11 @@
       <c r="V6" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W6" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>129</v>
       </c>
@@ -2710,8 +2740,11 @@
       <c r="V7" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W7" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="22" t="s">
         <v>130</v>
       </c>
@@ -2766,8 +2799,11 @@
       <c r="V8" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W8" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="22" t="s">
         <v>130</v>
       </c>
@@ -2822,8 +2858,11 @@
       <c r="V9" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W9" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="22" t="s">
         <v>130</v>
       </c>
@@ -2878,8 +2917,11 @@
       <c r="V10" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W10" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="22" t="s">
         <v>130</v>
       </c>
@@ -2934,8 +2976,11 @@
       <c r="V11" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W11" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="22" t="s">
         <v>130</v>
       </c>
@@ -2990,8 +3035,11 @@
       <c r="V12" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W12" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="22" t="s">
         <v>130</v>
       </c>
@@ -3046,8 +3094,11 @@
       <c r="V13" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W13" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="22" t="s">
         <v>130</v>
       </c>
@@ -3102,8 +3153,11 @@
       <c r="V14" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W14" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="22" t="s">
         <v>130</v>
       </c>
@@ -3158,8 +3212,11 @@
       <c r="V15" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W15" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="22" t="s">
         <v>130</v>
       </c>
@@ -3214,8 +3271,11 @@
       <c r="V16" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W16" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="22" t="s">
         <v>130</v>
       </c>
@@ -3270,8 +3330,11 @@
       <c r="V17" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W17" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="22" t="s">
         <v>130</v>
       </c>
@@ -3326,8 +3389,11 @@
       <c r="V18" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W18" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="22" t="s">
         <v>130</v>
       </c>
@@ -3382,8 +3448,11 @@
       <c r="V19" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W19" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="22" t="s">
         <v>130</v>
       </c>
@@ -3438,8 +3507,11 @@
       <c r="V20" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W20" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
         <v>131</v>
       </c>
@@ -3494,8 +3566,11 @@
       <c r="V21" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="22" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W21" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
         <v>131</v>
       </c>
@@ -3550,8 +3625,11 @@
       <c r="V22" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W22" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8" t="s">
         <v>131</v>
       </c>
@@ -3606,8 +3684,11 @@
       <c r="V23" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W23" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
         <v>131</v>
       </c>
@@ -3662,8 +3743,11 @@
       <c r="V24" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W24" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8" t="s">
         <v>131</v>
       </c>
@@ -3718,8 +3802,11 @@
       <c r="V25" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W25" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
         <v>131</v>
       </c>
@@ -3774,8 +3861,11 @@
       <c r="V26" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W26" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
         <v>131</v>
       </c>
@@ -3830,8 +3920,11 @@
       <c r="V27" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="28" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W27" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
         <v>131</v>
       </c>
@@ -3886,8 +3979,11 @@
       <c r="V28" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W28" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
         <v>131</v>
       </c>
@@ -3942,8 +4038,11 @@
       <c r="V29" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="30" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W29" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
         <v>131</v>
       </c>
@@ -3998,8 +4097,11 @@
       <c r="V30" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="31" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W30" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
         <v>131</v>
       </c>
@@ -4054,8 +4156,11 @@
       <c r="V31" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="32" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W31" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
         <v>131</v>
       </c>
@@ -4110,8 +4215,11 @@
       <c r="V32" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W32" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="22" t="s">
         <v>132</v>
       </c>
@@ -4168,8 +4276,11 @@
       <c r="V33" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W33" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="22" t="s">
         <v>132</v>
       </c>
@@ -4226,8 +4337,11 @@
       <c r="V34" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="35" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W34" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="22" t="s">
         <v>132</v>
       </c>
@@ -4284,8 +4398,11 @@
       <c r="V35" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="36" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W35" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="22" t="s">
         <v>132</v>
       </c>
@@ -4342,8 +4459,11 @@
       <c r="V36" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="37" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W36" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="22" t="s">
         <v>132</v>
       </c>
@@ -4400,8 +4520,11 @@
       <c r="V37" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="38" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W37" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="22" t="s">
         <v>132</v>
       </c>
@@ -4458,8 +4581,11 @@
       <c r="V38" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="39" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W38" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="22" t="s">
         <v>132</v>
       </c>
@@ -4516,8 +4642,11 @@
       <c r="V39" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="40" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W39" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="22" t="s">
         <v>132</v>
       </c>
@@ -4574,8 +4703,11 @@
       <c r="V40" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="41" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W40" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="22" t="s">
         <v>132</v>
       </c>
@@ -4632,8 +4764,11 @@
       <c r="V41" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="42" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W41" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="22" t="s">
         <v>132</v>
       </c>
@@ -4690,8 +4825,11 @@
       <c r="V42" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="43" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W42" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="22" t="s">
         <v>132</v>
       </c>
@@ -4748,8 +4886,11 @@
       <c r="V43" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="44" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W43" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="22" t="s">
         <v>132</v>
       </c>
@@ -4806,8 +4947,11 @@
       <c r="V44" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="45" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W44" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="22" t="s">
         <v>132</v>
       </c>
@@ -4864,8 +5008,11 @@
       <c r="V45" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="46" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W45" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="22" t="s">
         <v>132</v>
       </c>
@@ -4922,8 +5069,11 @@
       <c r="V46" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="47" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W46" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="22" t="s">
         <v>132</v>
       </c>
@@ -4980,8 +5130,11 @@
       <c r="V47" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="48" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W47" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="22" t="s">
         <v>132</v>
       </c>
@@ -5038,8 +5191,11 @@
       <c r="V48" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="49" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W48" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="22" t="s">
         <v>132</v>
       </c>
@@ -5096,8 +5252,11 @@
       <c r="V49" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="50" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W49" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="22" t="s">
         <v>132</v>
       </c>
@@ -5154,8 +5313,11 @@
       <c r="V50" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="51" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W50" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="22" t="s">
         <v>132</v>
       </c>
@@ -5212,8 +5374,11 @@
       <c r="V51" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="52" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W51" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="22" t="s">
         <v>132</v>
       </c>
@@ -5270,8 +5435,11 @@
       <c r="V52" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="53" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W52" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="22" t="s">
         <v>132</v>
       </c>
@@ -5328,8 +5496,11 @@
       <c r="V53" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="54" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W53" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="22" t="s">
         <v>132</v>
       </c>
@@ -5386,8 +5557,11 @@
       <c r="V54" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="55" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W54" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="22" t="s">
         <v>132</v>
       </c>
@@ -5444,8 +5618,11 @@
       <c r="V55" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="56" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W55" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="22" t="s">
         <v>132</v>
       </c>
@@ -5502,8 +5679,11 @@
       <c r="V56" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="57" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W56" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="8" t="s">
         <v>133</v>
       </c>
@@ -5560,8 +5740,11 @@
       <c r="V57" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="58" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W57" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
         <v>133</v>
       </c>
@@ -5618,8 +5801,11 @@
       <c r="V58" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="59" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W58" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
         <v>133</v>
       </c>
@@ -5676,8 +5862,11 @@
       <c r="V59" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="60" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W59" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
         <v>133</v>
       </c>
@@ -5734,8 +5923,11 @@
       <c r="V60" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="61" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W60" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
         <v>133</v>
       </c>
@@ -5792,8 +5984,11 @@
       <c r="V61" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="62" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W61" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
         <v>133</v>
       </c>
@@ -5850,8 +6045,11 @@
       <c r="V62" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="63" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W62" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
         <v>133</v>
       </c>
@@ -5908,8 +6106,11 @@
       <c r="V63" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="64" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W63" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
         <v>133</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="V64" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="65" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W64" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="8" t="s">
         <v>133</v>
       </c>
@@ -6024,8 +6228,11 @@
       <c r="V65" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="66" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W65" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
         <v>133</v>
       </c>
@@ -6082,8 +6289,11 @@
       <c r="V66" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="67" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W66" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
         <v>133</v>
       </c>
@@ -6140,8 +6350,11 @@
       <c r="V67" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="68" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W67" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="8" t="s">
         <v>133</v>
       </c>
@@ -6198,8 +6411,11 @@
       <c r="V68" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="69" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W68" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
         <v>133</v>
       </c>
@@ -6256,8 +6472,11 @@
       <c r="V69" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="70" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W69" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="8" t="s">
         <v>133</v>
       </c>
@@ -6314,8 +6533,11 @@
       <c r="V70" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="71" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W70" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
         <v>133</v>
       </c>
@@ -6372,8 +6594,11 @@
       <c r="V71" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="72" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W71" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="8" t="s">
         <v>133</v>
       </c>
@@ -6430,8 +6655,11 @@
       <c r="V72" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="73" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W72" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="8" t="s">
         <v>133</v>
       </c>
@@ -6488,8 +6716,11 @@
       <c r="V73" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="74" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W73" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="8" t="s">
         <v>133</v>
       </c>
@@ -6546,8 +6777,11 @@
       <c r="V74" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="75" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W74" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="8" t="s">
         <v>133</v>
       </c>
@@ -6604,8 +6838,11 @@
       <c r="V75" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="76" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W75" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
         <v>133</v>
       </c>
@@ -6662,8 +6899,11 @@
       <c r="V76" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="77" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W76" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
         <v>133</v>
       </c>
@@ -6720,8 +6960,11 @@
       <c r="V77" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="78" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W77" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
         <v>133</v>
       </c>
@@ -6778,8 +7021,11 @@
       <c r="V78" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W78" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="8" t="s">
         <v>133</v>
       </c>
@@ -6836,8 +7082,11 @@
       <c r="V79" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="80" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W79" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
         <v>133</v>
       </c>
@@ -6894,8 +7143,11 @@
       <c r="V80" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="81" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W80" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="22" t="s">
         <v>134</v>
       </c>
@@ -6952,8 +7204,11 @@
       <c r="V81" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="82" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W81" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="22" t="s">
         <v>134</v>
       </c>
@@ -7010,8 +7265,11 @@
       <c r="V82" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="83" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W82" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="22" t="s">
         <v>134</v>
       </c>
@@ -7068,8 +7326,11 @@
       <c r="V83" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="84" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W83" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="22" t="s">
         <v>134</v>
       </c>
@@ -7126,8 +7387,11 @@
       <c r="V84" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="85" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W84" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="22" t="s">
         <v>134</v>
       </c>
@@ -7184,8 +7448,11 @@
       <c r="V85" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="86" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W85" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="22" t="s">
         <v>134</v>
       </c>
@@ -7242,8 +7509,11 @@
       <c r="V86" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="87" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W86" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="22" t="s">
         <v>134</v>
       </c>
@@ -7300,8 +7570,11 @@
       <c r="V87" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="88" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W87" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="22" t="s">
         <v>134</v>
       </c>
@@ -7358,8 +7631,11 @@
       <c r="V88" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="89" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W88" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="22" t="s">
         <v>134</v>
       </c>
@@ -7416,8 +7692,11 @@
       <c r="V89" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="90" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W89" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="22" t="s">
         <v>134</v>
       </c>
@@ -7474,8 +7753,11 @@
       <c r="V90" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="91" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W90" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="22" t="s">
         <v>134</v>
       </c>
@@ -7532,8 +7814,11 @@
       <c r="V91" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="92" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W91" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="22" t="s">
         <v>134</v>
       </c>
@@ -7590,8 +7875,11 @@
       <c r="V92" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="93" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W92" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="22" t="s">
         <v>134</v>
       </c>
@@ -7648,8 +7936,11 @@
       <c r="V93" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="94" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W93" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="22" t="s">
         <v>134</v>
       </c>
@@ -7706,8 +7997,11 @@
       <c r="V94" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="95" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W94" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="22" t="s">
         <v>134</v>
       </c>
@@ -7764,8 +8058,11 @@
       <c r="V95" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="96" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W95" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="22" t="s">
         <v>134</v>
       </c>
@@ -7822,8 +8119,11 @@
       <c r="V96" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="97" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W96" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="22" t="s">
         <v>134</v>
       </c>
@@ -7880,8 +8180,11 @@
       <c r="V97" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="98" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W97" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="22" t="s">
         <v>134</v>
       </c>
@@ -7938,8 +8241,11 @@
       <c r="V98" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="99" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W98" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="22" t="s">
         <v>134</v>
       </c>
@@ -7996,8 +8302,11 @@
       <c r="V99" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="100" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W99" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="22" t="s">
         <v>134</v>
       </c>
@@ -8054,8 +8363,11 @@
       <c r="V100" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="101" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W100" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="22" t="s">
         <v>134</v>
       </c>
@@ -8112,8 +8424,11 @@
       <c r="V101" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="102" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W101" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="22" t="s">
         <v>134</v>
       </c>
@@ -8170,8 +8485,11 @@
       <c r="V102" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="103" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W102" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="22" t="s">
         <v>134</v>
       </c>
@@ -8228,8 +8546,11 @@
       <c r="V103" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="104" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W103" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="22" t="s">
         <v>134</v>
       </c>
@@ -8286,8 +8607,11 @@
       <c r="V104" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="105" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W104" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="8" t="s">
         <v>135</v>
       </c>
@@ -8344,8 +8668,11 @@
       <c r="V105" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="106" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W105" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="8" t="s">
         <v>135</v>
       </c>
@@ -8402,8 +8729,11 @@
       <c r="V106" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="107" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W106" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="8" t="s">
         <v>135</v>
       </c>
@@ -8460,8 +8790,11 @@
       <c r="V107" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="108" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W107" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="8" t="s">
         <v>135</v>
       </c>
@@ -8518,8 +8851,11 @@
       <c r="V108" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="109" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W108" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="8" t="s">
         <v>135</v>
       </c>
@@ -8576,8 +8912,11 @@
       <c r="V109" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="110" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W109" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="8" t="s">
         <v>135</v>
       </c>
@@ -8634,8 +8973,11 @@
       <c r="V110" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="111" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W110" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="8" t="s">
         <v>135</v>
       </c>
@@ -8692,8 +9034,11 @@
       <c r="V111" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="112" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W111" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="8" t="s">
         <v>135</v>
       </c>
@@ -8750,8 +9095,11 @@
       <c r="V112" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="113" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W112" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="22" t="s">
         <v>136</v>
       </c>
@@ -8808,8 +9156,11 @@
       <c r="V113" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="114" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W113" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="22" t="s">
         <v>136</v>
       </c>
@@ -8866,8 +9217,11 @@
       <c r="V114" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="115" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W114" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="22" t="s">
         <v>136</v>
       </c>
@@ -8924,8 +9278,11 @@
       <c r="V115" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="116" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W115" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="22" t="s">
         <v>136</v>
       </c>
@@ -8982,8 +9339,11 @@
       <c r="V116" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="117" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W116" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="22" t="s">
         <v>136</v>
       </c>
@@ -9040,8 +9400,11 @@
       <c r="V117" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="118" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W117" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="22" t="s">
         <v>136</v>
       </c>
@@ -9098,8 +9461,11 @@
       <c r="V118" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="119" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W118" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="22" t="s">
         <v>136</v>
       </c>
@@ -9156,8 +9522,11 @@
       <c r="V119" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="120" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W119" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="22" t="s">
         <v>136</v>
       </c>
@@ -9214,8 +9583,11 @@
       <c r="V120" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="121" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W120" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="8" t="s">
         <v>137</v>
       </c>
@@ -9270,8 +9642,11 @@
       <c r="V121" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="122" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W121" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="8" t="s">
         <v>137</v>
       </c>
@@ -9326,8 +9701,11 @@
       <c r="V122" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="123" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W122" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="8" t="s">
         <v>137</v>
       </c>
@@ -9382,8 +9760,11 @@
       <c r="V123" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="124" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W123" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="8" t="s">
         <v>137</v>
       </c>
@@ -9438,8 +9819,11 @@
       <c r="V124" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="125" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W124" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="8" t="s">
         <v>137</v>
       </c>
@@ -9494,8 +9878,11 @@
       <c r="V125" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="126" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W125" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="8" t="s">
         <v>137</v>
       </c>
@@ -9550,8 +9937,11 @@
       <c r="V126" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="127" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W126" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="8" t="s">
         <v>137</v>
       </c>
@@ -9606,8 +9996,11 @@
       <c r="V127" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="128" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W127" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="8" t="s">
         <v>137</v>
       </c>
@@ -9662,8 +10055,11 @@
       <c r="V128" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="129" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W128" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="8" t="s">
         <v>137</v>
       </c>
@@ -9718,8 +10114,11 @@
       <c r="V129" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="130" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W129" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="8" t="s">
         <v>137</v>
       </c>
@@ -9774,8 +10173,11 @@
       <c r="V130" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="131" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W130" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="8" t="s">
         <v>137</v>
       </c>
@@ -9830,8 +10232,11 @@
       <c r="V131" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="132" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W131" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="8" t="s">
         <v>137</v>
       </c>
@@ -9886,8 +10291,11 @@
       <c r="V132" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="133" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W132" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="8" t="s">
         <v>137</v>
       </c>
@@ -9942,8 +10350,11 @@
       <c r="V133" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="134" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W133" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="8" t="s">
         <v>137</v>
       </c>
@@ -9998,8 +10409,11 @@
       <c r="V134" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="135" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W134" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="8" t="s">
         <v>137</v>
       </c>
@@ -10054,8 +10468,11 @@
       <c r="V135" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="136" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W135" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="8" t="s">
         <v>137</v>
       </c>
@@ -10110,8 +10527,11 @@
       <c r="V136" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="137" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W136" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="8" t="s">
         <v>137</v>
       </c>
@@ -10166,8 +10586,11 @@
       <c r="V137" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="138" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W137" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="8" t="s">
         <v>137</v>
       </c>
@@ -10222,8 +10645,11 @@
       <c r="V138" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="139" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W138" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="8" t="s">
         <v>137</v>
       </c>
@@ -10278,8 +10704,11 @@
       <c r="V139" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="140" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W139" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="8" t="s">
         <v>137</v>
       </c>
@@ -10334,8 +10763,11 @@
       <c r="V140" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="141" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W140" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="8" t="s">
         <v>137</v>
       </c>
@@ -10390,8 +10822,11 @@
       <c r="V141" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="142" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W141" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="8" t="s">
         <v>137</v>
       </c>
@@ -10446,8 +10881,11 @@
       <c r="V142" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="143" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W142" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="8" t="s">
         <v>137</v>
       </c>
@@ -10502,8 +10940,11 @@
       <c r="V143" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="144" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W143" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="8" t="s">
         <v>137</v>
       </c>
@@ -10558,8 +10999,11 @@
       <c r="V144" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="145" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W144" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="8" t="s">
         <v>137</v>
       </c>
@@ -10614,8 +11058,11 @@
       <c r="V145" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="146" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W145" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="8" t="s">
         <v>137</v>
       </c>
@@ -10670,8 +11117,11 @@
       <c r="V146" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="147" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W146" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="8" t="s">
         <v>137</v>
       </c>
@@ -10726,8 +11176,11 @@
       <c r="V147" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="148" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W147" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="8" t="s">
         <v>137</v>
       </c>
@@ -10782,8 +11235,11 @@
       <c r="V148" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="149" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W148" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="8" t="s">
         <v>137</v>
       </c>
@@ -10838,8 +11294,11 @@
       <c r="V149" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="150" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W149" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="8" t="s">
         <v>137</v>
       </c>
@@ -10894,8 +11353,11 @@
       <c r="V150" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="151" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W150" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="8" t="s">
         <v>137</v>
       </c>
@@ -10950,8 +11412,11 @@
       <c r="V151" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="152" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W151" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="8" t="s">
         <v>137</v>
       </c>
@@ -11006,8 +11471,11 @@
       <c r="V152" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="153" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W152" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="8" t="s">
         <v>137</v>
       </c>
@@ -11062,8 +11530,11 @@
       <c r="V153" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="154" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W153" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="8" t="s">
         <v>137</v>
       </c>
@@ -11118,8 +11589,11 @@
       <c r="V154" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="155" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W154" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="8" t="s">
         <v>137</v>
       </c>
@@ -11174,8 +11648,11 @@
       <c r="V155" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="156" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W155" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="8" t="s">
         <v>137</v>
       </c>
@@ -11230,8 +11707,11 @@
       <c r="V156" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="157" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W156" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="157" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="8" t="s">
         <v>137</v>
       </c>
@@ -11286,8 +11766,11 @@
       <c r="V157" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="158" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W157" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="8" t="s">
         <v>137</v>
       </c>
@@ -11342,8 +11825,11 @@
       <c r="V158" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="159" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W158" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="8" t="s">
         <v>137</v>
       </c>
@@ -11398,8 +11884,11 @@
       <c r="V159" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="160" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W159" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="8" t="s">
         <v>137</v>
       </c>
@@ -11454,8 +11943,11 @@
       <c r="V160" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="161" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W160" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="8" t="s">
         <v>137</v>
       </c>
@@ -11510,8 +12002,11 @@
       <c r="V161" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="162" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W161" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="8" t="s">
         <v>137</v>
       </c>
@@ -11566,8 +12061,11 @@
       <c r="V162" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="163" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W162" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="163" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="8" t="s">
         <v>137</v>
       </c>
@@ -11622,8 +12120,11 @@
       <c r="V163" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="164" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W163" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="8" t="s">
         <v>137</v>
       </c>
@@ -11678,8 +12179,11 @@
       <c r="V164" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="165" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W164" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="165" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="8" t="s">
         <v>137</v>
       </c>
@@ -11734,8 +12238,11 @@
       <c r="V165" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="166" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W165" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="166" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="8" t="s">
         <v>137</v>
       </c>
@@ -11790,8 +12297,11 @@
       <c r="V166" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="167" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W166" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="167" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="8" t="s">
         <v>137</v>
       </c>
@@ -11846,8 +12356,11 @@
       <c r="V167" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="168" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W167" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="168" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="8" t="s">
         <v>137</v>
       </c>
@@ -11902,8 +12415,11 @@
       <c r="V168" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="169" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W168" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="169" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="8" t="s">
         <v>137</v>
       </c>
@@ -11958,8 +12474,11 @@
       <c r="V169" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="170" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W169" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="8" t="s">
         <v>137</v>
       </c>
@@ -12014,8 +12533,11 @@
       <c r="V170" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="171" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W170" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="171" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="8" t="s">
         <v>137</v>
       </c>
@@ -12070,8 +12592,11 @@
       <c r="V171" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="172" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W171" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="8" t="s">
         <v>137</v>
       </c>
@@ -12126,8 +12651,11 @@
       <c r="V172" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="173" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W172" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="8" t="s">
         <v>137</v>
       </c>
@@ -12182,8 +12710,11 @@
       <c r="V173" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="174" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W173" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="174" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="8" t="s">
         <v>137</v>
       </c>
@@ -12238,8 +12769,11 @@
       <c r="V174" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="175" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W174" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="22" t="s">
         <v>138</v>
       </c>
@@ -12296,8 +12830,11 @@
       <c r="V175" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="176" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W175" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="176" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="22" t="s">
         <v>138</v>
       </c>
@@ -12354,8 +12891,11 @@
       <c r="V176" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="177" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W176" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="22" t="s">
         <v>138</v>
       </c>
@@ -12412,8 +12952,11 @@
       <c r="V177" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="178" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W177" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="178" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="22" t="s">
         <v>138</v>
       </c>
@@ -12470,8 +13013,11 @@
       <c r="V178" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="179" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W178" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="179" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="22" t="s">
         <v>138</v>
       </c>
@@ -12528,8 +13074,11 @@
       <c r="V179" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="180" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W179" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="180" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="22" t="s">
         <v>138</v>
       </c>
@@ -12586,8 +13135,11 @@
       <c r="V180" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="181" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W180" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="181" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="8" t="s">
         <v>139</v>
       </c>
@@ -12642,8 +13194,11 @@
       <c r="V181" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="182" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W181" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="182" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="8" t="s">
         <v>139</v>
       </c>
@@ -12698,8 +13253,11 @@
       <c r="V182" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="183" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W182" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="183" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="8" t="s">
         <v>139</v>
       </c>
@@ -12754,8 +13312,11 @@
       <c r="V183" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="184" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W183" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="184" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="8" t="s">
         <v>139</v>
       </c>
@@ -12810,8 +13371,11 @@
       <c r="V184" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="185" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W184" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="185" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="8" t="s">
         <v>139</v>
       </c>
@@ -12866,8 +13430,11 @@
       <c r="V185" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="186" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W185" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="8" t="s">
         <v>139</v>
       </c>
@@ -12922,8 +13489,11 @@
       <c r="V186" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="187" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W186" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="187" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="8" t="s">
         <v>139</v>
       </c>
@@ -12978,8 +13548,11 @@
       <c r="V187" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="188" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W187" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="188" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="8" t="s">
         <v>139</v>
       </c>
@@ -13034,8 +13607,11 @@
       <c r="V188" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="189" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W188" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="189" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189" s="8" t="s">
         <v>139</v>
       </c>
@@ -13090,8 +13666,11 @@
       <c r="V189" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="190" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W189" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="190" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="8" t="s">
         <v>139</v>
       </c>
@@ -13146,8 +13725,11 @@
       <c r="V190" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="191" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W190" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="191" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A191" s="8" t="s">
         <v>139</v>
       </c>
@@ -13202,8 +13784,11 @@
       <c r="V191" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="192" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W191" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="192" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="8" t="s">
         <v>139</v>
       </c>
@@ -13258,8 +13843,11 @@
       <c r="V192" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="193" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W192" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="193" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="8" t="s">
         <v>139</v>
       </c>
@@ -13314,8 +13902,11 @@
       <c r="V193" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="194" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W193" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="194" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="8" t="s">
         <v>139</v>
       </c>
@@ -13370,8 +13961,11 @@
       <c r="V194" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="195" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W194" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="195" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="8" t="s">
         <v>139</v>
       </c>
@@ -13426,8 +14020,11 @@
       <c r="V195" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="196" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W195" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="196" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="8" t="s">
         <v>139</v>
       </c>
@@ -13482,8 +14079,11 @@
       <c r="V196" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="197" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W196" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="197" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="8" t="s">
         <v>139</v>
       </c>
@@ -13538,8 +14138,11 @@
       <c r="V197" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="198" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W197" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="198" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="8" t="s">
         <v>139</v>
       </c>
@@ -13594,8 +14197,11 @@
       <c r="V198" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="199" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W198" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="199" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="8" t="s">
         <v>139</v>
       </c>
@@ -13650,8 +14256,11 @@
       <c r="V199" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="200" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W199" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="200" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="8" t="s">
         <v>139</v>
       </c>
@@ -13706,8 +14315,11 @@
       <c r="V200" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="201" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W200" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="201" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A201" s="8" t="s">
         <v>139</v>
       </c>
@@ -13762,8 +14374,11 @@
       <c r="V201" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="202" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W201" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="202" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A202" s="8" t="s">
         <v>139</v>
       </c>
@@ -13818,8 +14433,11 @@
       <c r="V202" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="203" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W202" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="203" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="8" t="s">
         <v>139</v>
       </c>
@@ -13874,8 +14492,11 @@
       <c r="V203" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="204" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W203" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="204" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="8" t="s">
         <v>139</v>
       </c>
@@ -13930,8 +14551,11 @@
       <c r="V204" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="205" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W204" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="205" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="8" t="s">
         <v>139</v>
       </c>
@@ -13986,8 +14610,11 @@
       <c r="V205" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="206" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W205" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="206" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="8" t="s">
         <v>139</v>
       </c>
@@ -14042,8 +14669,11 @@
       <c r="V206" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="207" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W206" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="207" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="8" t="s">
         <v>139</v>
       </c>
@@ -14098,8 +14728,11 @@
       <c r="V207" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="208" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W207" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="208" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="8" t="s">
         <v>139</v>
       </c>
@@ -14154,8 +14787,11 @@
       <c r="V208" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="209" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W208" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="209" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="8" t="s">
         <v>139</v>
       </c>
@@ -14210,8 +14846,11 @@
       <c r="V209" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="210" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W209" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="210" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="8" t="s">
         <v>139</v>
       </c>
@@ -14266,8 +14905,11 @@
       <c r="V210" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="211" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W210" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="211" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="8" t="s">
         <v>139</v>
       </c>
@@ -14322,8 +14964,11 @@
       <c r="V211" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="212" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W211" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="212" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="8" t="s">
         <v>139</v>
       </c>
@@ -14378,8 +15023,11 @@
       <c r="V212" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="213" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W212" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="213" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="8" t="s">
         <v>139</v>
       </c>
@@ -14434,8 +15082,11 @@
       <c r="V213" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="214" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W213" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="214" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="8" t="s">
         <v>139</v>
       </c>
@@ -14490,8 +15141,11 @@
       <c r="V214" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="215" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W214" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="215" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215" s="8" t="s">
         <v>139</v>
       </c>
@@ -14546,8 +15200,11 @@
       <c r="V215" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="216" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W215" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="216" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216" s="8" t="s">
         <v>139</v>
       </c>
@@ -14602,8 +15259,11 @@
       <c r="V216" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="217" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W216" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="217" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217" s="8" t="s">
         <v>139</v>
       </c>
@@ -14658,8 +15318,11 @@
       <c r="V217" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="218" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W217" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="218" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A218" s="8" t="s">
         <v>139</v>
       </c>
@@ -14714,8 +15377,11 @@
       <c r="V218" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="219" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W218" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="219" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A219" s="8" t="s">
         <v>139</v>
       </c>
@@ -14770,8 +15436,11 @@
       <c r="V219" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="220" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W219" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="220" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A220" s="8" t="s">
         <v>139</v>
       </c>
@@ -14826,8 +15495,11 @@
       <c r="V220" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="221" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W220" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="221" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A221" s="8" t="s">
         <v>139</v>
       </c>
@@ -14882,8 +15554,11 @@
       <c r="V221" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="222" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W221" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A222" s="8" t="s">
         <v>139</v>
       </c>
@@ -14938,8 +15613,11 @@
       <c r="V222" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="223" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W222" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A223" s="8" t="s">
         <v>139</v>
       </c>
@@ -14994,8 +15672,11 @@
       <c r="V223" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="224" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W223" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="224" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A224" s="8" t="s">
         <v>139</v>
       </c>
@@ -15050,8 +15731,11 @@
       <c r="V224" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="225" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W224" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="225" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A225" s="8" t="s">
         <v>139</v>
       </c>
@@ -15106,8 +15790,11 @@
       <c r="V225" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="226" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W225" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A226" s="22" t="s">
         <v>140</v>
       </c>
@@ -15162,8 +15849,11 @@
       <c r="V226" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="227" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W226" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="227" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A227" s="22" t="s">
         <v>140</v>
       </c>
@@ -15218,8 +15908,11 @@
       <c r="V227" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="228" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W227" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="228" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228" s="22" t="s">
         <v>140</v>
       </c>
@@ -15274,8 +15967,11 @@
       <c r="V228" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="229" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W228" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="229" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="22" t="s">
         <v>140</v>
       </c>
@@ -15330,8 +16026,11 @@
       <c r="V229" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="230" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W229" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="230" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A230" s="22" t="s">
         <v>140</v>
       </c>
@@ -15386,8 +16085,11 @@
       <c r="V230" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="231" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W230" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="231" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A231" s="22" t="s">
         <v>140</v>
       </c>
@@ -15442,8 +16144,11 @@
       <c r="V231" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="232" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W231" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="232" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232" s="22" t="s">
         <v>140</v>
       </c>
@@ -15498,8 +16203,11 @@
       <c r="V232" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="233" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W232" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="233" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A233" s="22" t="s">
         <v>140</v>
       </c>
@@ -15554,8 +16262,11 @@
       <c r="V233" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="234" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W233" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="234" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A234" s="22" t="s">
         <v>140</v>
       </c>
@@ -15610,8 +16321,11 @@
       <c r="V234" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="235" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W234" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A235" s="22" t="s">
         <v>140</v>
       </c>
@@ -15666,8 +16380,11 @@
       <c r="V235" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="236" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W235" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="236" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A236" s="22" t="s">
         <v>140</v>
       </c>
@@ -15722,8 +16439,11 @@
       <c r="V236" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="237" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W236" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="237" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A237" s="22" t="s">
         <v>140</v>
       </c>
@@ -15778,8 +16498,11 @@
       <c r="V237" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="238" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W237" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="238" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A238" s="22" t="s">
         <v>140</v>
       </c>
@@ -15834,8 +16557,11 @@
       <c r="V238" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="239" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W238" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="239" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239" s="22" t="s">
         <v>140</v>
       </c>
@@ -15890,8 +16616,11 @@
       <c r="V239" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="240" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W239" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="240" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A240" s="22" t="s">
         <v>140</v>
       </c>
@@ -15946,8 +16675,11 @@
       <c r="V240" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="241" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W240" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="241" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A241" s="22" t="s">
         <v>140</v>
       </c>
@@ -16002,8 +16734,11 @@
       <c r="V241" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="242" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W241" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="242" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="22" t="s">
         <v>140</v>
       </c>
@@ -16058,8 +16793,11 @@
       <c r="V242" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="243" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W242" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="243" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A243" s="22" t="s">
         <v>140</v>
       </c>
@@ -16114,8 +16852,11 @@
       <c r="V243" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="244" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W243" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="244" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A244" s="22" t="s">
         <v>140</v>
       </c>
@@ -16170,8 +16911,11 @@
       <c r="V244" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="245" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W244" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="245" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A245" s="22" t="s">
         <v>140</v>
       </c>
@@ -16226,8 +16970,11 @@
       <c r="V245" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="246" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W245" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="246" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A246" s="22" t="s">
         <v>140</v>
       </c>
@@ -16282,8 +17029,11 @@
       <c r="V246" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="247" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W246" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="247" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A247" s="22" t="s">
         <v>140</v>
       </c>
@@ -16338,8 +17088,11 @@
       <c r="V247" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="248" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W247" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="248" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A248" s="22" t="s">
         <v>140</v>
       </c>
@@ -16394,8 +17147,11 @@
       <c r="V248" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="249" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W248" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="249" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A249" s="22" t="s">
         <v>140</v>
       </c>
@@ -16450,8 +17206,11 @@
       <c r="V249" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="250" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W249" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="250" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250" s="22" t="s">
         <v>140</v>
       </c>
@@ -16506,8 +17265,11 @@
       <c r="V250" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="251" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W250" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="251" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251" s="8" t="s">
         <v>141</v>
       </c>
@@ -16562,8 +17324,11 @@
       <c r="V251" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="252" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W251" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="252" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252" s="8" t="s">
         <v>141</v>
       </c>
@@ -16618,8 +17383,11 @@
       <c r="V252" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="253" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W252" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="253" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A253" s="8" t="s">
         <v>141</v>
       </c>
@@ -16674,8 +17442,11 @@
       <c r="V253" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="254" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W253" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A254" s="8" t="s">
         <v>141</v>
       </c>
@@ -16730,8 +17501,11 @@
       <c r="V254" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="255" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W254" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255" s="8" t="s">
         <v>141</v>
       </c>
@@ -16786,8 +17560,11 @@
       <c r="V255" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="256" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W255" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256" s="8" t="s">
         <v>141</v>
       </c>
@@ -16842,8 +17619,11 @@
       <c r="V256" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="257" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W256" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257" s="8" t="s">
         <v>141</v>
       </c>
@@ -16898,8 +17678,11 @@
       <c r="V257" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="258" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W257" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258" s="8" t="s">
         <v>141</v>
       </c>
@@ -16954,8 +17737,11 @@
       <c r="V258" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="259" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W258" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="259" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="22" t="s">
         <v>142</v>
       </c>
@@ -17010,8 +17796,11 @@
       <c r="V259" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="260" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W259" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="260" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A260" s="22" t="s">
         <v>142</v>
       </c>
@@ -17066,8 +17855,11 @@
       <c r="V260" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="261" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W260" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="261" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A261" s="22" t="s">
         <v>142</v>
       </c>
@@ -17122,8 +17914,11 @@
       <c r="V261" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="262" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W261" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262" s="22" t="s">
         <v>142</v>
       </c>
@@ -17178,8 +17973,11 @@
       <c r="V262" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="263" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W262" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263" s="22" t="s">
         <v>142</v>
       </c>
@@ -17234,8 +18032,11 @@
       <c r="V263" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="264" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W263" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="264" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A264" s="22" t="s">
         <v>142</v>
       </c>
@@ -17290,8 +18091,11 @@
       <c r="V264" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="265" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W264" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A265" s="22" t="s">
         <v>142</v>
       </c>
@@ -17346,8 +18150,11 @@
       <c r="V265" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="266" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W265" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="266" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A266" s="8" t="s">
         <v>143</v>
       </c>
@@ -17402,8 +18209,11 @@
       <c r="V266" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="267" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W266" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="267" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A267" s="8" t="s">
         <v>143</v>
       </c>
@@ -17458,8 +18268,11 @@
       <c r="V267" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="268" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W267" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="268" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A268" s="8" t="s">
         <v>143</v>
       </c>
@@ -17514,8 +18327,11 @@
       <c r="V268" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="269" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W268" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="269" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A269" s="8" t="s">
         <v>143</v>
       </c>
@@ -17570,8 +18386,11 @@
       <c r="V269" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="270" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W269" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="270" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270" s="8" t="s">
         <v>143</v>
       </c>
@@ -17626,8 +18445,11 @@
       <c r="V270" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="271" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W270" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="271" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A271" s="8" t="s">
         <v>143</v>
       </c>
@@ -17682,8 +18504,11 @@
       <c r="V271" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="272" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W271" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="272" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A272" s="8" t="s">
         <v>143</v>
       </c>
@@ -17738,8 +18563,11 @@
       <c r="V272" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="273" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W272" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="273" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A273" s="8" t="s">
         <v>143</v>
       </c>
@@ -17794,8 +18622,11 @@
       <c r="V273" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="274" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W273" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="274" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A274" s="22" t="s">
         <v>144</v>
       </c>
@@ -17854,8 +18685,11 @@
       <c r="V274" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="275" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W274" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="275" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A275" s="22" t="s">
         <v>144</v>
       </c>
@@ -17914,8 +18748,11 @@
       <c r="V275" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="276" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W275" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="276" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A276" s="22" t="s">
         <v>144</v>
       </c>
@@ -17974,8 +18811,11 @@
       <c r="V276" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="277" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W276" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="277" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A277" s="22" t="s">
         <v>144</v>
       </c>
@@ -18034,8 +18874,11 @@
       <c r="V277" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="278" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W277" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="278" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A278" s="22" t="s">
         <v>144</v>
       </c>
@@ -18094,8 +18937,11 @@
       <c r="V278" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="279" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W278" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="279" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A279" s="22" t="s">
         <v>144</v>
       </c>
@@ -18154,8 +19000,11 @@
       <c r="V279" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="280" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W279" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="280" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A280" s="22" t="s">
         <v>144</v>
       </c>
@@ -18214,8 +19063,11 @@
       <c r="V280" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="281" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W280" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="281" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A281" s="8" t="s">
         <v>145</v>
       </c>
@@ -18272,8 +19124,11 @@
       <c r="V281" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="282" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W281" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="282" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A282" s="8" t="s">
         <v>145</v>
       </c>
@@ -18330,8 +19185,11 @@
       <c r="V282" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="283" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W282" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="283" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A283" s="8" t="s">
         <v>145</v>
       </c>
@@ -18388,8 +19246,11 @@
       <c r="V283" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="284" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W283" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="284" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A284" s="8" t="s">
         <v>145</v>
       </c>
@@ -18446,8 +19307,11 @@
       <c r="V284" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="285" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W284" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="285" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A285" s="8" t="s">
         <v>145</v>
       </c>
@@ -18504,8 +19368,11 @@
       <c r="V285" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="286" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W285" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="286" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A286" s="8" t="s">
         <v>145</v>
       </c>
@@ -18562,8 +19429,11 @@
       <c r="V286" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="287" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W286" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="287" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A287" s="22" t="s">
         <v>146</v>
       </c>
@@ -18620,8 +19490,11 @@
       <c r="V287" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="288" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W287" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="288" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A288" s="22" t="s">
         <v>146</v>
       </c>
@@ -18678,8 +19551,11 @@
       <c r="V288" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="289" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W288" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="289" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A289" s="22" t="s">
         <v>146</v>
       </c>
@@ -18736,8 +19612,11 @@
       <c r="V289" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="290" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W289" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="290" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A290" s="22" t="s">
         <v>146</v>
       </c>
@@ -18794,8 +19673,11 @@
       <c r="V290" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="291" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W290" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="291" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A291" s="22" t="s">
         <v>146</v>
       </c>
@@ -18852,8 +19734,11 @@
       <c r="V291" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="292" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W291" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A292" s="22" t="s">
         <v>146</v>
       </c>
@@ -18910,8 +19795,11 @@
       <c r="V292" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="293" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W292" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="293" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A293" s="8" t="s">
         <v>147</v>
       </c>
@@ -18968,8 +19856,11 @@
       <c r="V293" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="294" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W293" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A294" s="8" t="s">
         <v>147</v>
       </c>
@@ -19026,8 +19917,11 @@
       <c r="V294" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="295" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W294" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="295" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A295" s="8" t="s">
         <v>147</v>
       </c>
@@ -19084,8 +19978,11 @@
       <c r="V295" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="296" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W295" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="296" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A296" s="8" t="s">
         <v>147</v>
       </c>
@@ -19142,8 +20039,11 @@
       <c r="V296" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="297" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W296" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="297" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A297" s="22" t="s">
         <v>148</v>
       </c>
@@ -19198,8 +20098,11 @@
       <c r="V297" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="298" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W297" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A298" s="22" t="s">
         <v>148</v>
       </c>
@@ -19254,8 +20157,11 @@
       <c r="V298" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="299" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W298" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="299" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A299" s="22" t="s">
         <v>148</v>
       </c>
@@ -19310,8 +20216,11 @@
       <c r="V299" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="300" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W299" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="300" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A300" s="22" t="s">
         <v>148</v>
       </c>
@@ -19366,8 +20275,11 @@
       <c r="V300" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="301" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W300" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="301" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A301" s="22" t="s">
         <v>148</v>
       </c>
@@ -19422,8 +20334,11 @@
       <c r="V301" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="302" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W301" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="302" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A302" s="22" t="s">
         <v>148</v>
       </c>
@@ -19478,8 +20393,11 @@
       <c r="V302" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="303" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W302" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="303" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A303" s="22" t="s">
         <v>148</v>
       </c>
@@ -19534,8 +20452,11 @@
       <c r="V303" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="304" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W303" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="304" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A304" s="8" t="s">
         <v>149</v>
       </c>
@@ -19592,8 +20513,11 @@
       <c r="V304" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="305" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W304" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="305" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A305" s="8" t="s">
         <v>149</v>
       </c>
@@ -19650,8 +20574,11 @@
       <c r="V305" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="306" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W305" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="306" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A306" s="8" t="s">
         <v>149</v>
       </c>
@@ -19708,8 +20635,11 @@
       <c r="V306" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="307" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W306" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="307" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A307" s="8" t="s">
         <v>149</v>
       </c>
@@ -19766,8 +20696,11 @@
       <c r="V307" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="308" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W307" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="308" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A308" s="22" t="s">
         <v>150</v>
       </c>
@@ -19822,8 +20755,11 @@
       <c r="V308" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="309" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W308" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="309" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A309" s="22" t="s">
         <v>150</v>
       </c>
@@ -19878,8 +20814,11 @@
       <c r="V309" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="310" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W309" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="310" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A310" s="22" t="s">
         <v>150</v>
       </c>
@@ -19934,8 +20873,11 @@
       <c r="V310" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="311" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W310" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="311" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A311" s="22" t="s">
         <v>150</v>
       </c>
@@ -19990,8 +20932,11 @@
       <c r="V311" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="312" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W311" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="312" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A312" s="22" t="s">
         <v>150</v>
       </c>
@@ -20046,8 +20991,11 @@
       <c r="V312" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="313" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W312" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="313" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A313" s="22" t="s">
         <v>150</v>
       </c>
@@ -20102,8 +21050,11 @@
       <c r="V313" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="314" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W313" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="314" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A314" s="22" t="s">
         <v>150</v>
       </c>
@@ -20158,8 +21109,11 @@
       <c r="V314" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="315" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W314" s="90" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="315" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A315" s="8" t="s">
         <v>151</v>
       </c>
@@ -20214,8 +21168,11 @@
       <c r="V315" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="316" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W315" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="316" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A316" s="8" t="s">
         <v>151</v>
       </c>
@@ -20270,8 +21227,11 @@
       <c r="V316" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="317" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W316" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="317" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A317" s="8" t="s">
         <v>151</v>
       </c>
@@ -20326,8 +21286,11 @@
       <c r="V317" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="318" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W317" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="318" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A318" s="8" t="s">
         <v>151</v>
       </c>
@@ -20382,8 +21345,11 @@
       <c r="V318" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="319" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W318" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="319" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A319" s="8" t="s">
         <v>151</v>
       </c>
@@ -20438,8 +21404,11 @@
       <c r="V319" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="320" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W319" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="320" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A320" s="8" t="s">
         <v>151</v>
       </c>
@@ -20494,8 +21463,11 @@
       <c r="V320" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="321" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W320" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="321" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A321" s="8" t="s">
         <v>151</v>
       </c>
@@ -20550,8 +21522,11 @@
       <c r="V321" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="322" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W321" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="322" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A322" s="8" t="s">
         <v>151</v>
       </c>
@@ -20606,8 +21581,11 @@
       <c r="V322" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="323" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W322" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="323" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A323" s="8" t="s">
         <v>151</v>
       </c>
@@ -20662,8 +21640,11 @@
       <c r="V323" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="324" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W323" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="324" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A324" s="8" t="s">
         <v>151</v>
       </c>
@@ -20718,8 +21699,11 @@
       <c r="V324" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="325" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W324" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="325" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A325" s="8" t="s">
         <v>151</v>
       </c>
@@ -20774,8 +21758,11 @@
       <c r="V325" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="326" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W325" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="326" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A326" s="8" t="s">
         <v>151</v>
       </c>
@@ -20830,8 +21817,11 @@
       <c r="V326" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="327" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W326" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="327" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A327" s="8" t="s">
         <v>151</v>
       </c>
@@ -20886,8 +21876,11 @@
       <c r="V327" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="328" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W327" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="328" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A328" s="8" t="s">
         <v>151</v>
       </c>
@@ -20942,8 +21935,11 @@
       <c r="V328" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="329" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W328" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="329" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A329" s="8" t="s">
         <v>151</v>
       </c>
@@ -20998,8 +21994,11 @@
       <c r="V329" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="330" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W329" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="330" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A330" s="8" t="s">
         <v>151</v>
       </c>
@@ -21054,8 +22053,11 @@
       <c r="V330" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="331" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W330" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="331" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A331" s="8" t="s">
         <v>151</v>
       </c>
@@ -21110,8 +22112,11 @@
       <c r="V331" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="332" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W331" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="332" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A332" s="8" t="s">
         <v>151</v>
       </c>
@@ -21166,8 +22171,11 @@
       <c r="V332" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="333" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W332" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="333" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A333" s="8" t="s">
         <v>151</v>
       </c>
@@ -21222,8 +22230,11 @@
       <c r="V333" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="334" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W333" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="334" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A334" s="8" t="s">
         <v>151</v>
       </c>
@@ -21278,8 +22289,11 @@
       <c r="V334" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="335" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W334" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="335" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A335" s="22" t="s">
         <v>152</v>
       </c>
@@ -21336,8 +22350,11 @@
       <c r="V335" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="336" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W335" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="336" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A336" s="22" t="s">
         <v>152</v>
       </c>
@@ -21394,8 +22411,11 @@
       <c r="V336" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="337" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W336" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="337" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A337" s="22" t="s">
         <v>152</v>
       </c>
@@ -21452,8 +22472,11 @@
       <c r="V337" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="338" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W337" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="338" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A338" s="22" t="s">
         <v>152</v>
       </c>
@@ -21510,8 +22533,11 @@
       <c r="V338" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="339" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W338" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="339" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A339" s="22" t="s">
         <v>152</v>
       </c>
@@ -21568,8 +22594,11 @@
       <c r="V339" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="340" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W339" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="340" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A340" s="8" t="s">
         <v>202</v>
       </c>
@@ -21626,8 +22655,11 @@
       <c r="V340" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="341" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W340" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="341" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A341" s="8" t="s">
         <v>202</v>
       </c>
@@ -21684,8 +22716,11 @@
       <c r="V341" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="342" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W341" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="342" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A342" s="8" t="s">
         <v>202</v>
       </c>
@@ -21742,8 +22777,11 @@
       <c r="V342" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="343" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W342" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="343" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A343" s="8" t="s">
         <v>202</v>
       </c>
@@ -21800,8 +22838,11 @@
       <c r="V343" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="344" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W343" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="344" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A344" s="8" t="s">
         <v>202</v>
       </c>
@@ -21858,8 +22899,11 @@
       <c r="V344" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="345" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W344" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="345" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A345" s="22" t="s">
         <v>203</v>
       </c>
@@ -21916,8 +22960,11 @@
       <c r="V345" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="346" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W345" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="346" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A346" s="22" t="s">
         <v>203</v>
       </c>
@@ -21974,8 +23021,11 @@
       <c r="V346" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="347" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W346" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="347" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A347" s="22" t="s">
         <v>203</v>
       </c>
@@ -22032,8 +23082,11 @@
       <c r="V347" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="348" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W347" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="348" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A348" s="22" t="s">
         <v>203</v>
       </c>
@@ -22090,8 +23143,11 @@
       <c r="V348" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="349" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W348" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="349" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A349" s="22" t="s">
         <v>203</v>
       </c>
@@ -22148,8 +23204,11 @@
       <c r="V349" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="350" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W349" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="350" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A350" s="8" t="s">
         <v>155</v>
       </c>
@@ -22206,8 +23265,11 @@
       <c r="V350" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="351" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W350" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="351" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A351" s="8" t="s">
         <v>155</v>
       </c>
@@ -22264,8 +23326,11 @@
       <c r="V351" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="352" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W351" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="352" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A352" s="8" t="s">
         <v>155</v>
       </c>
@@ -22322,8 +23387,11 @@
       <c r="V352" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="353" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W352" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="353" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A353" s="8" t="s">
         <v>155</v>
       </c>
@@ -22380,8 +23448,11 @@
       <c r="V353" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="354" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W353" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="354" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A354" s="8" t="s">
         <v>155</v>
       </c>
@@ -22438,8 +23509,11 @@
       <c r="V354" s="11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="355" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W354" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="355" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A355" s="22" t="s">
         <v>157</v>
       </c>
@@ -22496,8 +23570,11 @@
       <c r="V355" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="356" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W355" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="356" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A356" s="22" t="s">
         <v>157</v>
       </c>
@@ -22554,8 +23631,11 @@
       <c r="V356" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="357" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W356" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="357" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A357" s="22" t="s">
         <v>157</v>
       </c>
@@ -22612,8 +23692,11 @@
       <c r="V357" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="358" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W357" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="358" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A358" s="22" t="s">
         <v>157</v>
       </c>
@@ -22670,8 +23753,11 @@
       <c r="V358" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="359" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W358" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="359" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A359" s="22" t="s">
         <v>157</v>
       </c>
@@ -22728,8 +23814,11 @@
       <c r="V359" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="360" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W359" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="360" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A360" s="22" t="s">
         <v>157</v>
       </c>
@@ -22786,8 +23875,11 @@
       <c r="V360" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="361" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W360" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="361" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A361" s="22" t="s">
         <v>157</v>
       </c>
@@ -22844,8 +23936,11 @@
       <c r="V361" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="362" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W361" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="362" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A362" s="22" t="s">
         <v>157</v>
       </c>
@@ -22902,8 +23997,11 @@
       <c r="V362" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="363" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W362" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="363" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A363" s="22" t="s">
         <v>157</v>
       </c>
@@ -22960,8 +24058,11 @@
       <c r="V363" s="25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="364" spans="1:22" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W363" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="364" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A364" s="56" t="s">
         <v>162</v>
       </c>
@@ -23016,8 +24117,11 @@
       <c r="V364" s="40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="365" spans="1:22" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W364" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="365" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A365" s="56" t="s">
         <v>162</v>
       </c>
@@ -23072,8 +24176,11 @@
       <c r="V365" s="40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="366" spans="1:22" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W365" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="366" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A366" s="56" t="s">
         <v>162</v>
       </c>
@@ -23128,8 +24235,11 @@
       <c r="V366" s="40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="367" spans="1:22" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W366" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="367" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A367" s="56" t="s">
         <v>162</v>
       </c>
@@ -23184,8 +24294,11 @@
       <c r="V367" s="40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="368" spans="1:22" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W367" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="368" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A368" s="56" t="s">
         <v>162</v>
       </c>
@@ -23240,8 +24353,11 @@
       <c r="V368" s="40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="369" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W368" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="369" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A369" s="56" t="s">
         <v>162</v>
       </c>
@@ -23296,8 +24412,11 @@
       <c r="V369" s="40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="370" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W369" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="370" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A370" s="22" t="s">
         <v>169</v>
       </c>
@@ -23354,8 +24473,11 @@
       <c r="V370" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="371" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W370" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="371" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A371" s="22" t="s">
         <v>169</v>
       </c>
@@ -23412,8 +24534,11 @@
       <c r="V371" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="372" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W371" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="372" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A372" s="22" t="s">
         <v>169</v>
       </c>
@@ -23470,8 +24595,11 @@
       <c r="V372" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="373" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W372" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="373" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A373" s="22" t="s">
         <v>169</v>
       </c>
@@ -23528,8 +24656,11 @@
       <c r="V373" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="374" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W373" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="374" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A374" s="22" t="s">
         <v>169</v>
       </c>
@@ -23586,8 +24717,11 @@
       <c r="V374" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="375" spans="1:22" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W374" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="375" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A375" s="22" t="s">
         <v>169</v>
       </c>
@@ -23644,8 +24778,11 @@
       <c r="V375" s="24" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="376" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W375" s="90" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="376" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A376" s="8" t="s">
         <v>175</v>
       </c>
@@ -23702,8 +24839,11 @@
       <c r="V376" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="377" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W376" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="377" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A377" s="8" t="s">
         <v>175</v>
       </c>
@@ -23760,8 +24900,11 @@
       <c r="V377" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="378" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W377" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="378" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A378" s="8" t="s">
         <v>175</v>
       </c>
@@ -23818,8 +24961,11 @@
       <c r="V378" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="379" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W378" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="379" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A379" s="8" t="s">
         <v>175</v>
       </c>
@@ -23876,8 +25022,11 @@
       <c r="V379" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="380" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W379" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="380" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A380" s="8" t="s">
         <v>175</v>
       </c>
@@ -23934,8 +25083,11 @@
       <c r="V380" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="381" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W380" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="381" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A381" s="8" t="s">
         <v>175</v>
       </c>
@@ -23992,8 +25144,11 @@
       <c r="V381" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="382" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W381" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="382" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A382" s="8" t="s">
         <v>175</v>
       </c>
@@ -24050,8 +25205,11 @@
       <c r="V382" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="383" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W382" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="383" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A383" s="8" t="s">
         <v>175</v>
       </c>
@@ -24108,8 +25266,11 @@
       <c r="V383" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="384" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W383" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="384" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A384" s="8" t="s">
         <v>175</v>
       </c>
@@ -24166,8 +25327,11 @@
       <c r="V384" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="385" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W384" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="385" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A385" s="8" t="s">
         <v>175</v>
       </c>
@@ -24224,8 +25388,11 @@
       <c r="V385" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="386" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W385" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="386" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A386" s="8" t="s">
         <v>175</v>
       </c>
@@ -24282,8 +25449,11 @@
       <c r="V386" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="387" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W386" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="387" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A387" s="8" t="s">
         <v>175</v>
       </c>
@@ -24340,8 +25510,11 @@
       <c r="V387" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="388" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W387" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="388" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A388" s="8" t="s">
         <v>175</v>
       </c>
@@ -24398,8 +25571,11 @@
       <c r="V388" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="389" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W388" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="389" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A389" s="8" t="s">
         <v>175</v>
       </c>
@@ -24456,8 +25632,11 @@
       <c r="V389" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="390" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W389" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="390" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A390" s="8" t="s">
         <v>175</v>
       </c>
@@ -24514,8 +25693,11 @@
       <c r="V390" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="391" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W390" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="391" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A391" s="8" t="s">
         <v>175</v>
       </c>
@@ -24572,8 +25754,11 @@
       <c r="V391" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="392" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W391" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="392" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A392" s="8" t="s">
         <v>175</v>
       </c>
@@ -24630,8 +25815,11 @@
       <c r="V392" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="393" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W392" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="393" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A393" s="8" t="s">
         <v>175</v>
       </c>
@@ -24688,8 +25876,11 @@
       <c r="V393" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="394" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W393" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="394" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A394" s="8" t="s">
         <v>175</v>
       </c>
@@ -24746,8 +25937,11 @@
       <c r="V394" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="395" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W394" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="395" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A395" s="8" t="s">
         <v>175</v>
       </c>
@@ -24804,8 +25998,11 @@
       <c r="V395" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="396" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W395" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="396" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A396" s="8" t="s">
         <v>175</v>
       </c>
@@ -24862,8 +26059,11 @@
       <c r="V396" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="397" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W396" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="397" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A397" s="8" t="s">
         <v>175</v>
       </c>
@@ -24920,8 +26120,11 @@
       <c r="V397" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="398" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W397" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="398" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A398" s="8" t="s">
         <v>175</v>
       </c>
@@ -24978,8 +26181,11 @@
       <c r="V398" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="399" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W398" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="399" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A399" s="8" t="s">
         <v>175</v>
       </c>
@@ -25036,8 +26242,11 @@
       <c r="V399" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="400" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W399" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="400" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A400" s="8" t="s">
         <v>175</v>
       </c>
@@ -25094,8 +26303,11 @@
       <c r="V400" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="401" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W400" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="401" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A401" s="8" t="s">
         <v>175</v>
       </c>
@@ -25152,8 +26364,11 @@
       <c r="V401" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="402" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W401" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="402" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A402" s="8" t="s">
         <v>175</v>
       </c>
@@ -25210,8 +26425,11 @@
       <c r="V402" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="403" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W402" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="403" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A403" s="8" t="s">
         <v>175</v>
       </c>
@@ -25268,8 +26486,11 @@
       <c r="V403" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="404" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W403" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="404" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A404" s="8" t="s">
         <v>175</v>
       </c>
@@ -25326,8 +26547,11 @@
       <c r="V404" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="405" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W404" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="405" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A405" s="8" t="s">
         <v>175</v>
       </c>
@@ -25384,8 +26608,11 @@
       <c r="V405" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="406" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W405" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="406" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A406" s="8" t="s">
         <v>175</v>
       </c>
@@ -25442,8 +26669,11 @@
       <c r="V406" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="407" spans="1:22" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W406" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="407" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A407" s="8" t="s">
         <v>175</v>
       </c>
@@ -25500,8 +26730,11 @@
       <c r="V407" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="408" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W407" s="89" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="408" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A408" s="61" t="s">
         <v>178</v>
       </c>
@@ -25558,8 +26791,11 @@
       <c r="V408" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="409" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W408" s="55" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="409" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A409" s="61" t="s">
         <v>178</v>
       </c>
@@ -25616,8 +26852,11 @@
       <c r="V409" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="410" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W409" s="55" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="410" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A410" s="61" t="s">
         <v>178</v>
       </c>
@@ -25674,8 +26913,11 @@
       <c r="V410" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="411" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W410" s="55" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="411" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A411" s="61" t="s">
         <v>178</v>
       </c>
@@ -25732,8 +26974,11 @@
       <c r="V411" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="412" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W411" s="55" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="412" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A412" s="56" t="s">
         <v>198</v>
       </c>
@@ -25792,8 +27037,11 @@
       <c r="V412" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="413" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W412" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="413" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A413" s="56" t="s">
         <v>198</v>
       </c>
@@ -25852,8 +27100,11 @@
       <c r="V413" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="414" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W413" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="414" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A414" s="56" t="s">
         <v>198</v>
       </c>
@@ -25912,8 +27163,11 @@
       <c r="V414" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="415" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W414" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="415" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A415" s="56" t="s">
         <v>198</v>
       </c>
@@ -25972,8 +27226,11 @@
       <c r="V415" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="416" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W415" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="416" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A416" s="56" t="s">
         <v>198</v>
       </c>
@@ -26032,8 +27289,11 @@
       <c r="V416" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="417" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W416" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="417" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A417" s="56" t="s">
         <v>198</v>
       </c>
@@ -26092,8 +27352,11 @@
       <c r="V417" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="418" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W417" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="418" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A418" s="56" t="s">
         <v>198</v>
       </c>
@@ -26152,8 +27415,11 @@
       <c r="V418" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="419" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W418" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="419" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A419" s="56" t="s">
         <v>198</v>
       </c>
@@ -26212,8 +27478,11 @@
       <c r="V419" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="420" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W419" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="420" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A420" s="64" t="s">
         <v>199</v>
       </c>
@@ -26272,8 +27541,11 @@
       <c r="V420" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="421" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W420" s="55" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="421" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A421" s="64" t="s">
         <v>199</v>
       </c>
@@ -26332,8 +27604,11 @@
       <c r="V421" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="422" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W421" s="55" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="422" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A422" s="64" t="s">
         <v>199</v>
       </c>
@@ -26392,8 +27667,11 @@
       <c r="V422" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="423" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W422" s="55" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="423" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A423" s="64" t="s">
         <v>199</v>
       </c>
@@ -26452,8 +27730,11 @@
       <c r="V423" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="424" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W423" s="55" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="424" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A424" s="64" t="s">
         <v>199</v>
       </c>
@@ -26512,8 +27793,11 @@
       <c r="V424" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="425" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W424" s="55" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="425" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A425" s="64" t="s">
         <v>199</v>
       </c>
@@ -26572,8 +27856,11 @@
       <c r="V425" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="426" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W425" s="55" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="426" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A426" s="64" t="s">
         <v>199</v>
       </c>
@@ -26632,8 +27919,11 @@
       <c r="V426" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="427" spans="1:22" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W426" s="55" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="427" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A427" s="64" t="s">
         <v>199</v>
       </c>
@@ -26692,8 +27982,11 @@
       <c r="V427" s="24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="428" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W427" s="55" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="428" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A428" s="56" t="s">
         <v>200</v>
       </c>
@@ -26752,8 +28045,11 @@
       <c r="V428" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="429" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W428" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="429" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A429" s="56" t="s">
         <v>200</v>
       </c>
@@ -26812,8 +28108,11 @@
       <c r="V429" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="430" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W429" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="430" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A430" s="56" t="s">
         <v>200</v>
       </c>
@@ -26872,8 +28171,11 @@
       <c r="V430" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="431" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W430" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="431" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A431" s="56" t="s">
         <v>200</v>
       </c>
@@ -26932,8 +28234,11 @@
       <c r="V431" s="10" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="432" spans="1:22" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W431" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="432" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A432" s="56" t="s">
         <v>200</v>
       </c>
@@ -26992,6 +28297,9 @@
       <c r="V432" s="10" t="s">
         <v>197</v>
       </c>
+      <c r="W432" s="48" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="433" spans="1:41" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A433" s="56" t="s">
@@ -27052,6 +28360,9 @@
       <c r="V433" s="10" t="s">
         <v>197</v>
       </c>
+      <c r="W433" s="48" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="434" spans="1:41" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A434" s="56" t="s">
@@ -27112,6 +28423,9 @@
       <c r="V434" s="10" t="s">
         <v>197</v>
       </c>
+      <c r="W434" s="48" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="435" spans="1:41" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A435" s="56" t="s">
@@ -27172,6 +28486,9 @@
       <c r="V435" s="10" t="s">
         <v>197</v>
       </c>
+      <c r="W435" s="48" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="436" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A436" s="64" t="s">
@@ -27232,6 +28549,9 @@
       <c r="V436" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W436" s="55" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="437" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A437" s="64" t="s">
@@ -27292,6 +28612,9 @@
       <c r="V437" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W437" s="55" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="438" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A438" s="64" t="s">
@@ -27352,6 +28675,9 @@
       <c r="V438" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W438" s="55" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="439" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A439" s="64" t="s">
@@ -27412,6 +28738,9 @@
       <c r="V439" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W439" s="55" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="440" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A440" s="64" t="s">
@@ -27472,6 +28801,9 @@
       <c r="V440" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W440" s="55" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="441" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A441" s="64" t="s">
@@ -27532,6 +28864,9 @@
       <c r="V441" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W441" s="55" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="442" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A442" s="64" t="s">
@@ -27592,6 +28927,9 @@
       <c r="V442" s="24" t="s">
         <v>197</v>
       </c>
+      <c r="W442" s="55" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="443" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A443" s="64" t="s">
@@ -27651,6 +28989,9 @@
       </c>
       <c r="V443" s="24" t="s">
         <v>197</v>
+      </c>
+      <c r="W443" s="55" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="444" spans="1:41" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27712,7 +29053,9 @@
       <c r="V444" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W444" s="14"/>
+      <c r="W444" s="31" t="s">
+        <v>226</v>
+      </c>
       <c r="X444" s="20"/>
       <c r="Y444" s="20"/>
       <c r="Z444" s="20"/>
@@ -27791,7 +29134,9 @@
       <c r="V445" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W445" s="14"/>
+      <c r="W445" s="31" t="s">
+        <v>226</v>
+      </c>
       <c r="X445" s="20"/>
       <c r="Y445" s="20"/>
       <c r="Z445" s="20"/>
@@ -27870,7 +29215,9 @@
       <c r="V446" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W446" s="14"/>
+      <c r="W446" s="31" t="s">
+        <v>226</v>
+      </c>
       <c r="X446" s="20"/>
       <c r="Y446" s="20"/>
       <c r="Z446" s="20"/>
@@ -27949,7 +29296,9 @@
       <c r="V447" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W447" s="14"/>
+      <c r="W447" s="31" t="s">
+        <v>226</v>
+      </c>
       <c r="X447" s="20"/>
       <c r="Y447" s="20"/>
       <c r="Z447" s="20"/>
@@ -28028,7 +29377,9 @@
       <c r="V448" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W448" s="14"/>
+      <c r="W448" s="31" t="s">
+        <v>226</v>
+      </c>
       <c r="X448" s="20"/>
       <c r="Y448" s="20"/>
       <c r="Z448" s="20"/>
@@ -28107,7 +29458,9 @@
       <c r="V449" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W449" s="14"/>
+      <c r="W449" s="31" t="s">
+        <v>226</v>
+      </c>
       <c r="X449" s="20"/>
       <c r="Y449" s="20"/>
       <c r="Z449" s="20"/>
@@ -28186,7 +29539,9 @@
       <c r="V450" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W450" s="14"/>
+      <c r="W450" s="31" t="s">
+        <v>226</v>
+      </c>
       <c r="X450" s="20"/>
       <c r="Y450" s="20"/>
       <c r="Z450" s="20"/>
@@ -28265,7 +29620,9 @@
       <c r="V451" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="W451" s="14"/>
+      <c r="W451" s="31" t="s">
+        <v>226</v>
+      </c>
       <c r="X451" s="20"/>
       <c r="Y451" s="20"/>
       <c r="Z451" s="20"/>
@@ -28344,7 +29701,9 @@
       <c r="V452" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W452" s="27"/>
+      <c r="W452" s="55" t="s">
+        <v>226</v>
+      </c>
       <c r="X452" s="28"/>
       <c r="Y452" s="28"/>
       <c r="Z452" s="28"/>
@@ -28423,7 +29782,9 @@
       <c r="V453" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W453" s="27"/>
+      <c r="W453" s="55" t="s">
+        <v>226</v>
+      </c>
       <c r="X453" s="28"/>
       <c r="Y453" s="28"/>
       <c r="Z453" s="28"/>
@@ -28502,7 +29863,9 @@
       <c r="V454" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W454" s="27"/>
+      <c r="W454" s="55" t="s">
+        <v>226</v>
+      </c>
       <c r="X454" s="28"/>
       <c r="Y454" s="28"/>
       <c r="Z454" s="28"/>
@@ -28581,7 +29944,9 @@
       <c r="V455" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W455" s="27"/>
+      <c r="W455" s="55" t="s">
+        <v>226</v>
+      </c>
       <c r="X455" s="28"/>
       <c r="Y455" s="28"/>
       <c r="Z455" s="28"/>
@@ -28660,7 +30025,9 @@
       <c r="V456" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W456" s="27"/>
+      <c r="W456" s="55" t="s">
+        <v>226</v>
+      </c>
       <c r="X456" s="28"/>
       <c r="Y456" s="28"/>
       <c r="Z456" s="28"/>
@@ -28739,7 +30106,9 @@
       <c r="V457" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W457" s="27"/>
+      <c r="W457" s="55" t="s">
+        <v>226</v>
+      </c>
       <c r="X457" s="28"/>
       <c r="Y457" s="28"/>
       <c r="Z457" s="28"/>
@@ -28818,7 +30187,9 @@
       <c r="V458" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W458" s="27"/>
+      <c r="W458" s="55" t="s">
+        <v>226</v>
+      </c>
       <c r="X458" s="28"/>
       <c r="Y458" s="28"/>
       <c r="Z458" s="28"/>
@@ -28897,7 +30268,9 @@
       <c r="V459" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W459" s="27"/>
+      <c r="W459" s="55" t="s">
+        <v>226</v>
+      </c>
       <c r="X459" s="28"/>
       <c r="Y459" s="28"/>
       <c r="Z459" s="28"/>
@@ -28976,7 +30349,9 @@
       <c r="V460" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W460" s="27"/>
+      <c r="W460" s="55" t="s">
+        <v>226</v>
+      </c>
       <c r="X460" s="28"/>
       <c r="Y460" s="28"/>
       <c r="Z460" s="28"/>
@@ -29055,7 +30430,9 @@
       <c r="V461" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W461" s="27"/>
+      <c r="W461" s="55" t="s">
+        <v>226</v>
+      </c>
       <c r="X461" s="28"/>
       <c r="Y461" s="28"/>
       <c r="Z461" s="28"/>
@@ -29134,7 +30511,9 @@
       <c r="V462" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W462" s="27"/>
+      <c r="W462" s="55" t="s">
+        <v>226</v>
+      </c>
       <c r="X462" s="28"/>
       <c r="Y462" s="28"/>
       <c r="Z462" s="28"/>
@@ -29213,7 +30592,9 @@
       <c r="V463" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="W463" s="27"/>
+      <c r="W463" s="55" t="s">
+        <v>226</v>
+      </c>
       <c r="X463" s="28"/>
       <c r="Y463" s="28"/>
       <c r="Z463" s="28"/>
@@ -29292,7 +30673,9 @@
       <c r="V464" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W464" s="20"/>
+      <c r="W464" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X464" s="20"/>
       <c r="Y464" s="20"/>
       <c r="Z464" s="20"/>
@@ -29374,7 +30757,9 @@
       <c r="V465" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W465" s="20"/>
+      <c r="W465" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X465" s="20"/>
       <c r="Y465" s="20"/>
       <c r="Z465" s="20"/>
@@ -29456,7 +30841,9 @@
       <c r="V466" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W466" s="20"/>
+      <c r="W466" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X466" s="20"/>
       <c r="Y466" s="20"/>
       <c r="Z466" s="20"/>
@@ -29538,7 +30925,9 @@
       <c r="V467" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W467" s="20"/>
+      <c r="W467" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X467" s="20"/>
       <c r="Y467" s="20"/>
       <c r="Z467" s="20"/>
@@ -29620,7 +31009,9 @@
       <c r="V468" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W468" s="20"/>
+      <c r="W468" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X468" s="20"/>
       <c r="Y468" s="20"/>
       <c r="Z468" s="20"/>
@@ -29702,7 +31093,9 @@
       <c r="V469" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W469" s="20"/>
+      <c r="W469" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X469" s="20"/>
       <c r="Y469" s="20"/>
       <c r="Z469" s="20"/>
@@ -29784,7 +31177,9 @@
       <c r="V470" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W470" s="20"/>
+      <c r="W470" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X470" s="20"/>
       <c r="Y470" s="20"/>
       <c r="Z470" s="20"/>
@@ -29866,7 +31261,9 @@
       <c r="V471" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W471" s="20"/>
+      <c r="W471" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X471" s="20"/>
       <c r="Y471" s="20"/>
       <c r="Z471" s="20"/>
@@ -29948,7 +31345,9 @@
       <c r="V472" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W472" s="20"/>
+      <c r="W472" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X472" s="20"/>
       <c r="Y472" s="20"/>
       <c r="Z472" s="20"/>
@@ -30030,7 +31429,9 @@
       <c r="V473" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W473" s="20"/>
+      <c r="W473" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X473" s="20"/>
       <c r="Y473" s="20"/>
       <c r="Z473" s="20"/>
@@ -30112,7 +31513,9 @@
       <c r="V474" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W474" s="20"/>
+      <c r="W474" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X474" s="20"/>
       <c r="Y474" s="20"/>
       <c r="Z474" s="20"/>
@@ -30194,7 +31597,9 @@
       <c r="V475" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W475" s="20"/>
+      <c r="W475" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X475" s="20"/>
       <c r="Y475" s="20"/>
       <c r="Z475" s="20"/>
@@ -30276,7 +31681,9 @@
       <c r="V476" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W476" s="20"/>
+      <c r="W476" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X476" s="20"/>
       <c r="Y476" s="20"/>
       <c r="Z476" s="20"/>
@@ -30358,7 +31765,9 @@
       <c r="V477" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W477" s="20"/>
+      <c r="W477" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X477" s="20"/>
       <c r="Y477" s="20"/>
       <c r="Z477" s="20"/>
@@ -30440,7 +31849,9 @@
       <c r="V478" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W478" s="20"/>
+      <c r="W478" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X478" s="20"/>
       <c r="Y478" s="20"/>
       <c r="Z478" s="20"/>
@@ -30522,7 +31933,9 @@
       <c r="V479" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W479" s="20"/>
+      <c r="W479" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X479" s="20"/>
       <c r="Y479" s="20"/>
       <c r="Z479" s="20"/>
@@ -30604,7 +32017,9 @@
       <c r="V480" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W480" s="20"/>
+      <c r="W480" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X480" s="20"/>
       <c r="Y480" s="20"/>
       <c r="Z480" s="20"/>
@@ -30686,7 +32101,9 @@
       <c r="V481" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W481" s="20"/>
+      <c r="W481" s="91" t="s">
+        <v>227</v>
+      </c>
       <c r="X481" s="20"/>
       <c r="Y481" s="20"/>
       <c r="Z481" s="20"/>
@@ -30709,966 +32126,6 @@
         <v>220</v>
       </c>
     </row>
-    <row r="482" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A482" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B482" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C482" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D482" s="50"/>
-      <c r="E482" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F482" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G482" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H482" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I482" s="63"/>
-      <c r="J482" s="52"/>
-      <c r="K482" s="54">
-        <v>1</v>
-      </c>
-      <c r="L482" s="88">
-        <v>35947</v>
-      </c>
-      <c r="M482" s="50"/>
-      <c r="N482" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O482" s="54">
-        <v>1</v>
-      </c>
-      <c r="P482" s="53"/>
-      <c r="Q482" s="54">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="R482" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S482" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T482" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U482" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V482" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W482" s="54"/>
-      <c r="X482" s="54"/>
-      <c r="Y482" s="54"/>
-      <c r="Z482" s="54"/>
-      <c r="AA482" s="52"/>
-      <c r="AB482" s="52"/>
-      <c r="AC482" s="52"/>
-      <c r="AD482" s="52"/>
-      <c r="AE482" s="52"/>
-      <c r="AF482" s="52"/>
-      <c r="AG482" s="52"/>
-      <c r="AH482" s="52"/>
-      <c r="AI482" s="52"/>
-      <c r="AJ482" s="52"/>
-      <c r="AK482" s="52"/>
-      <c r="AL482" s="52"/>
-      <c r="AM482" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN482" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="483" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A483" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B483" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C483" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D483" s="50"/>
-      <c r="E483" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F483" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G483" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H483" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I483" s="63"/>
-      <c r="J483" s="52"/>
-      <c r="K483" s="54">
-        <v>2</v>
-      </c>
-      <c r="L483" s="88">
-        <v>36069</v>
-      </c>
-      <c r="M483" s="52"/>
-      <c r="N483" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O483" s="54">
-        <v>1</v>
-      </c>
-      <c r="P483" s="53"/>
-      <c r="Q483" s="54">
-        <v>49.7</v>
-      </c>
-      <c r="R483" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S483" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T483" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U483" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V483" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W483" s="54"/>
-      <c r="X483" s="54"/>
-      <c r="Y483" s="54"/>
-      <c r="Z483" s="54"/>
-      <c r="AA483" s="52"/>
-      <c r="AB483" s="52"/>
-      <c r="AC483" s="52"/>
-      <c r="AD483" s="52"/>
-      <c r="AE483" s="52"/>
-      <c r="AF483" s="52"/>
-      <c r="AG483" s="52"/>
-      <c r="AH483" s="52"/>
-      <c r="AI483" s="52"/>
-      <c r="AJ483" s="52"/>
-      <c r="AK483" s="52"/>
-      <c r="AL483" s="52"/>
-      <c r="AM483" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN483" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="484" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A484" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B484" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C484" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D484" s="50"/>
-      <c r="E484" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F484" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G484" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H484" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I484" s="63"/>
-      <c r="J484" s="52"/>
-      <c r="K484" s="54">
-        <v>3</v>
-      </c>
-      <c r="L484" s="88">
-        <v>36161</v>
-      </c>
-      <c r="M484" s="52"/>
-      <c r="N484" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O484" s="54">
-        <v>1</v>
-      </c>
-      <c r="P484" s="53"/>
-      <c r="Q484" s="54">
-        <v>59.5</v>
-      </c>
-      <c r="R484" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S484" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T484" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U484" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V484" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W484" s="54"/>
-      <c r="X484" s="54"/>
-      <c r="Y484" s="54"/>
-      <c r="Z484" s="54"/>
-      <c r="AA484" s="52"/>
-      <c r="AB484" s="52"/>
-      <c r="AC484" s="52"/>
-      <c r="AD484" s="52"/>
-      <c r="AE484" s="52"/>
-      <c r="AF484" s="52"/>
-      <c r="AG484" s="52"/>
-      <c r="AH484" s="52"/>
-      <c r="AI484" s="52"/>
-      <c r="AJ484" s="52"/>
-      <c r="AK484" s="52"/>
-      <c r="AL484" s="52"/>
-      <c r="AM484" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN484" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="485" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A485" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B485" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C485" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D485" s="50"/>
-      <c r="E485" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F485" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G485" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H485" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I485" s="63"/>
-      <c r="J485" s="52"/>
-      <c r="K485" s="54">
-        <v>4</v>
-      </c>
-      <c r="L485" s="88">
-        <v>36281</v>
-      </c>
-      <c r="M485" s="52"/>
-      <c r="N485" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O485" s="53">
-        <v>0</v>
-      </c>
-      <c r="P485" s="53"/>
-      <c r="Q485" s="54">
-        <v>47.5</v>
-      </c>
-      <c r="R485" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S485" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T485" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U485" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V485" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W485" s="54"/>
-      <c r="X485" s="54"/>
-      <c r="Y485" s="54"/>
-      <c r="Z485" s="54"/>
-      <c r="AA485" s="52"/>
-      <c r="AB485" s="52"/>
-      <c r="AC485" s="52"/>
-      <c r="AD485" s="52"/>
-      <c r="AE485" s="52"/>
-      <c r="AF485" s="52"/>
-      <c r="AG485" s="52"/>
-      <c r="AH485" s="52"/>
-      <c r="AI485" s="52"/>
-      <c r="AJ485" s="52"/>
-      <c r="AK485" s="52"/>
-      <c r="AL485" s="52"/>
-      <c r="AM485" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN485" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="486" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A486" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B486" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C486" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D486" s="50"/>
-      <c r="E486" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F486" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G486" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H486" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I486" s="63"/>
-      <c r="J486" s="52"/>
-      <c r="K486" s="54">
-        <v>5</v>
-      </c>
-      <c r="L486" s="88">
-        <v>36342</v>
-      </c>
-      <c r="M486" s="52"/>
-      <c r="N486" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O486" s="53">
-        <v>0</v>
-      </c>
-      <c r="P486" s="53"/>
-      <c r="Q486" s="54">
-        <v>38</v>
-      </c>
-      <c r="R486" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S486" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T486" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U486" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V486" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W486" s="54"/>
-      <c r="X486" s="54"/>
-      <c r="Y486" s="54"/>
-      <c r="Z486" s="54"/>
-      <c r="AA486" s="52"/>
-      <c r="AB486" s="52"/>
-      <c r="AC486" s="52"/>
-      <c r="AD486" s="52"/>
-      <c r="AE486" s="52"/>
-      <c r="AF486" s="52"/>
-      <c r="AG486" s="52"/>
-      <c r="AH486" s="52"/>
-      <c r="AI486" s="52"/>
-      <c r="AJ486" s="52"/>
-      <c r="AK486" s="52"/>
-      <c r="AL486" s="52"/>
-      <c r="AM486" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN486" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="487" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A487" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B487" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C487" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D487" s="50"/>
-      <c r="E487" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F487" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G487" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H487" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I487" s="63"/>
-      <c r="J487" s="52"/>
-      <c r="K487" s="54">
-        <v>6</v>
-      </c>
-      <c r="L487" s="88">
-        <v>36404</v>
-      </c>
-      <c r="M487" s="52"/>
-      <c r="N487" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O487" s="53">
-        <v>0</v>
-      </c>
-      <c r="P487" s="53"/>
-      <c r="Q487" s="54">
-        <v>94.3</v>
-      </c>
-      <c r="R487" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S487" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T487" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U487" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V487" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W487" s="54"/>
-      <c r="X487" s="54"/>
-      <c r="Y487" s="54"/>
-      <c r="Z487" s="54"/>
-      <c r="AA487" s="52"/>
-      <c r="AB487" s="52"/>
-      <c r="AC487" s="52"/>
-      <c r="AD487" s="52"/>
-      <c r="AE487" s="52"/>
-      <c r="AF487" s="52"/>
-      <c r="AG487" s="52"/>
-      <c r="AH487" s="52"/>
-      <c r="AI487" s="52"/>
-      <c r="AJ487" s="52"/>
-      <c r="AK487" s="52"/>
-      <c r="AL487" s="52"/>
-      <c r="AM487" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN487" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="488" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A488" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B488" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C488" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D488" s="50"/>
-      <c r="E488" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F488" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G488" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H488" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I488" s="63"/>
-      <c r="J488" s="52"/>
-      <c r="K488" s="54">
-        <v>7</v>
-      </c>
-      <c r="L488" s="88">
-        <v>36495</v>
-      </c>
-      <c r="M488" s="52"/>
-      <c r="N488" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O488" s="53">
-        <v>0</v>
-      </c>
-      <c r="P488" s="53"/>
-      <c r="Q488" s="54">
-        <v>51.5</v>
-      </c>
-      <c r="R488" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S488" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T488" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U488" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V488" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W488" s="54"/>
-      <c r="X488" s="54"/>
-      <c r="Y488" s="54"/>
-      <c r="Z488" s="54"/>
-      <c r="AA488" s="52"/>
-      <c r="AB488" s="52"/>
-      <c r="AC488" s="52"/>
-      <c r="AD488" s="52"/>
-      <c r="AE488" s="52"/>
-      <c r="AF488" s="52"/>
-      <c r="AG488" s="52"/>
-      <c r="AH488" s="52"/>
-      <c r="AI488" s="52"/>
-      <c r="AJ488" s="52"/>
-      <c r="AK488" s="52"/>
-      <c r="AL488" s="52"/>
-      <c r="AM488" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN488" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="489" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A489" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B489" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C489" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D489" s="50"/>
-      <c r="E489" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F489" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G489" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H489" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I489" s="63"/>
-      <c r="J489" s="52"/>
-      <c r="K489" s="54">
-        <v>8</v>
-      </c>
-      <c r="L489" s="88">
-        <v>36557</v>
-      </c>
-      <c r="M489" s="52"/>
-      <c r="N489" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O489" s="53">
-        <v>0</v>
-      </c>
-      <c r="P489" s="53"/>
-      <c r="Q489" s="54">
-        <v>60.7</v>
-      </c>
-      <c r="R489" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S489" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T489" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U489" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V489" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W489" s="54"/>
-      <c r="X489" s="54"/>
-      <c r="Y489" s="54"/>
-      <c r="Z489" s="54"/>
-      <c r="AA489" s="52"/>
-      <c r="AB489" s="52"/>
-      <c r="AC489" s="52"/>
-      <c r="AD489" s="52"/>
-      <c r="AE489" s="52"/>
-      <c r="AF489" s="52"/>
-      <c r="AG489" s="52"/>
-      <c r="AH489" s="52"/>
-      <c r="AI489" s="52"/>
-      <c r="AJ489" s="52"/>
-      <c r="AK489" s="52"/>
-      <c r="AL489" s="52"/>
-      <c r="AM489" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN489" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="490" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A490" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B490" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C490" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D490" s="50"/>
-      <c r="E490" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F490" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G490" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H490" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I490" s="63"/>
-      <c r="J490" s="52"/>
-      <c r="K490" s="54">
-        <v>9</v>
-      </c>
-      <c r="L490" s="88">
-        <v>36770</v>
-      </c>
-      <c r="M490" s="52"/>
-      <c r="N490" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O490" s="53">
-        <v>0</v>
-      </c>
-      <c r="P490" s="53"/>
-      <c r="Q490" s="54">
-        <v>55.2</v>
-      </c>
-      <c r="R490" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S490" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T490" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U490" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V490" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W490" s="54"/>
-      <c r="X490" s="54"/>
-      <c r="Y490" s="54"/>
-      <c r="Z490" s="54"/>
-      <c r="AA490" s="52"/>
-      <c r="AB490" s="52"/>
-      <c r="AC490" s="52"/>
-      <c r="AD490" s="52"/>
-      <c r="AE490" s="52"/>
-      <c r="AF490" s="52"/>
-      <c r="AG490" s="52"/>
-      <c r="AH490" s="52"/>
-      <c r="AI490" s="52"/>
-      <c r="AJ490" s="52"/>
-      <c r="AK490" s="52"/>
-      <c r="AL490" s="52"/>
-      <c r="AM490" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN490" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="491" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A491" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B491" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C491" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D491" s="50"/>
-      <c r="E491" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F491" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G491" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H491" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I491" s="63"/>
-      <c r="J491" s="52"/>
-      <c r="K491" s="54">
-        <v>10</v>
-      </c>
-      <c r="L491" s="88">
-        <v>36982</v>
-      </c>
-      <c r="M491" s="52"/>
-      <c r="N491" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O491" s="53">
-        <v>0</v>
-      </c>
-      <c r="P491" s="53"/>
-      <c r="Q491" s="54">
-        <v>38</v>
-      </c>
-      <c r="R491" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S491" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T491" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U491" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V491" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W491" s="54"/>
-      <c r="X491" s="54"/>
-      <c r="Y491" s="54"/>
-      <c r="Z491" s="54"/>
-      <c r="AA491" s="52"/>
-      <c r="AB491" s="52"/>
-      <c r="AC491" s="52"/>
-      <c r="AD491" s="52"/>
-      <c r="AE491" s="52"/>
-      <c r="AF491" s="52"/>
-      <c r="AG491" s="52"/>
-      <c r="AH491" s="52"/>
-      <c r="AI491" s="52"/>
-      <c r="AJ491" s="52"/>
-      <c r="AK491" s="52"/>
-      <c r="AL491" s="52"/>
-      <c r="AM491" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN491" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="492" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A492" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B492" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C492" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D492" s="50"/>
-      <c r="E492" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F492" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G492" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H492" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I492" s="63"/>
-      <c r="J492" s="52"/>
-      <c r="K492" s="54">
-        <v>11</v>
-      </c>
-      <c r="L492" s="88">
-        <v>37073</v>
-      </c>
-      <c r="M492" s="52"/>
-      <c r="N492" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O492" s="53">
-        <v>0</v>
-      </c>
-      <c r="P492" s="53"/>
-      <c r="Q492" s="54">
-        <v>30.8</v>
-      </c>
-      <c r="R492" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S492" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T492" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U492" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V492" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W492" s="54"/>
-      <c r="X492" s="54"/>
-      <c r="Y492" s="54"/>
-      <c r="Z492" s="54"/>
-      <c r="AA492" s="52"/>
-      <c r="AB492" s="52"/>
-      <c r="AC492" s="52"/>
-      <c r="AD492" s="52"/>
-      <c r="AE492" s="52"/>
-      <c r="AF492" s="52"/>
-      <c r="AG492" s="52"/>
-      <c r="AH492" s="52"/>
-      <c r="AI492" s="52"/>
-      <c r="AJ492" s="52"/>
-      <c r="AK492" s="52"/>
-      <c r="AL492" s="52"/>
-      <c r="AM492" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN492" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="493" spans="1:40" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A493" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="B493" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C493" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D493" s="50"/>
-      <c r="E493" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="F493" s="51">
-        <v>26.1191</v>
-      </c>
-      <c r="G493" s="51">
-        <v>-111.2756</v>
-      </c>
-      <c r="H493" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="I493" s="63"/>
-      <c r="J493" s="52"/>
-      <c r="K493" s="54">
-        <v>12</v>
-      </c>
-      <c r="L493" s="88">
-        <v>37165</v>
-      </c>
-      <c r="M493" s="52"/>
-      <c r="N493" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="O493" s="53">
-        <v>0</v>
-      </c>
-      <c r="P493" s="53"/>
-      <c r="Q493" s="54">
-        <v>15.6</v>
-      </c>
-      <c r="R493" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="S493" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="T493" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="U493" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V493" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W493" s="54"/>
-      <c r="X493" s="54"/>
-      <c r="Y493" s="54"/>
-      <c r="Z493" s="54"/>
-      <c r="AA493" s="52"/>
-      <c r="AB493" s="52"/>
-      <c r="AC493" s="52"/>
-      <c r="AD493" s="52"/>
-      <c r="AE493" s="52"/>
-      <c r="AF493" s="52"/>
-      <c r="AG493" s="52"/>
-      <c r="AH493" s="52"/>
-      <c r="AI493" s="52"/>
-      <c r="AJ493" s="52"/>
-      <c r="AK493" s="52"/>
-      <c r="AL493" s="52"/>
-      <c r="AM493" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN493" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/data/meta_analysis/Cat meta-analysis - correlations.xlsx
+++ b/data/meta_analysis/Cat meta-analysis - correlations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wallacha@qut.edu.au/Documents/Research/Manuscripts/Death Star/Cats vs vertebrates/Datasets/Meta-analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ejlundgren/Dropbox/Projects/iucn_evidence/cat_evidence_review/data/meta_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2313D25-3F2E-3540-B07B-45353F44CC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A6740A-6F0A-6841-A6B7-0F9917DAB7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29380" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29380" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Correlations" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6034" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5998" uniqueCount="226">
   <si>
     <t>scientificName</t>
   </si>
@@ -692,12 +692,6 @@
     <t>Howland</t>
   </si>
   <si>
-    <t>SMD</t>
-  </si>
-  <si>
-    <t>Before-after eradication abundance</t>
-  </si>
-  <si>
     <t>ES_47b</t>
   </si>
   <si>
@@ -1164,7 +1158,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
@@ -2387,7 +2381,7 @@
         <v>12</v>
       </c>
       <c r="W1" s="88" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2446,7 +2440,7 @@
         <v>77</v>
       </c>
       <c r="W2" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2505,7 +2499,7 @@
         <v>77</v>
       </c>
       <c r="W3" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2564,7 +2558,7 @@
         <v>77</v>
       </c>
       <c r="W4" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2623,7 +2617,7 @@
         <v>77</v>
       </c>
       <c r="W5" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2682,7 +2676,7 @@
         <v>77</v>
       </c>
       <c r="W6" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2741,7 +2735,7 @@
         <v>77</v>
       </c>
       <c r="W7" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2800,7 +2794,7 @@
         <v>77</v>
       </c>
       <c r="W8" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2859,7 +2853,7 @@
         <v>77</v>
       </c>
       <c r="W9" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2918,7 +2912,7 @@
         <v>77</v>
       </c>
       <c r="W10" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2977,7 +2971,7 @@
         <v>77</v>
       </c>
       <c r="W11" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3036,7 +3030,7 @@
         <v>77</v>
       </c>
       <c r="W12" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3095,7 +3089,7 @@
         <v>77</v>
       </c>
       <c r="W13" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3154,7 +3148,7 @@
         <v>77</v>
       </c>
       <c r="W14" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3213,7 +3207,7 @@
         <v>77</v>
       </c>
       <c r="W15" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3272,7 +3266,7 @@
         <v>77</v>
       </c>
       <c r="W16" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3331,7 +3325,7 @@
         <v>77</v>
       </c>
       <c r="W17" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3390,7 +3384,7 @@
         <v>77</v>
       </c>
       <c r="W18" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3449,7 +3443,7 @@
         <v>77</v>
       </c>
       <c r="W19" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3508,7 +3502,7 @@
         <v>77</v>
       </c>
       <c r="W20" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3567,7 +3561,7 @@
         <v>77</v>
       </c>
       <c r="W21" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3626,7 +3620,7 @@
         <v>77</v>
       </c>
       <c r="W22" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3685,7 +3679,7 @@
         <v>77</v>
       </c>
       <c r="W23" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3744,7 +3738,7 @@
         <v>77</v>
       </c>
       <c r="W24" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3803,7 +3797,7 @@
         <v>77</v>
       </c>
       <c r="W25" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3862,7 +3856,7 @@
         <v>77</v>
       </c>
       <c r="W26" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3921,7 +3915,7 @@
         <v>77</v>
       </c>
       <c r="W27" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3980,7 +3974,7 @@
         <v>77</v>
       </c>
       <c r="W28" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4039,7 +4033,7 @@
         <v>77</v>
       </c>
       <c r="W29" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4098,7 +4092,7 @@
         <v>77</v>
       </c>
       <c r="W30" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4157,7 +4151,7 @@
         <v>77</v>
       </c>
       <c r="W31" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4216,7 +4210,7 @@
         <v>77</v>
       </c>
       <c r="W32" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4277,7 +4271,7 @@
         <v>77</v>
       </c>
       <c r="W33" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4338,7 +4332,7 @@
         <v>77</v>
       </c>
       <c r="W34" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4399,7 +4393,7 @@
         <v>77</v>
       </c>
       <c r="W35" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4460,7 +4454,7 @@
         <v>77</v>
       </c>
       <c r="W36" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4521,7 +4515,7 @@
         <v>77</v>
       </c>
       <c r="W37" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4582,7 +4576,7 @@
         <v>77</v>
       </c>
       <c r="W38" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4643,7 +4637,7 @@
         <v>77</v>
       </c>
       <c r="W39" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4704,7 +4698,7 @@
         <v>77</v>
       </c>
       <c r="W40" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4765,7 +4759,7 @@
         <v>77</v>
       </c>
       <c r="W41" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4826,7 +4820,7 @@
         <v>77</v>
       </c>
       <c r="W42" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4887,7 +4881,7 @@
         <v>77</v>
       </c>
       <c r="W43" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4948,7 +4942,7 @@
         <v>77</v>
       </c>
       <c r="W44" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5009,7 +5003,7 @@
         <v>77</v>
       </c>
       <c r="W45" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5070,7 +5064,7 @@
         <v>77</v>
       </c>
       <c r="W46" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5131,7 +5125,7 @@
         <v>77</v>
       </c>
       <c r="W47" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5192,7 +5186,7 @@
         <v>77</v>
       </c>
       <c r="W48" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="49" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5253,7 +5247,7 @@
         <v>77</v>
       </c>
       <c r="W49" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="50" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5314,7 +5308,7 @@
         <v>77</v>
       </c>
       <c r="W50" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="51" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5375,7 +5369,7 @@
         <v>77</v>
       </c>
       <c r="W51" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5436,7 +5430,7 @@
         <v>77</v>
       </c>
       <c r="W52" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="53" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5497,7 +5491,7 @@
         <v>77</v>
       </c>
       <c r="W53" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="54" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5558,7 +5552,7 @@
         <v>77</v>
       </c>
       <c r="W54" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="55" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5619,7 +5613,7 @@
         <v>77</v>
       </c>
       <c r="W55" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="56" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5680,7 +5674,7 @@
         <v>77</v>
       </c>
       <c r="W56" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="57" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5741,7 +5735,7 @@
         <v>77</v>
       </c>
       <c r="W57" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="58" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5802,7 +5796,7 @@
         <v>77</v>
       </c>
       <c r="W58" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5863,7 +5857,7 @@
         <v>77</v>
       </c>
       <c r="W59" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="60" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5924,7 +5918,7 @@
         <v>77</v>
       </c>
       <c r="W60" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5985,7 +5979,7 @@
         <v>77</v>
       </c>
       <c r="W61" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="62" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6046,7 +6040,7 @@
         <v>77</v>
       </c>
       <c r="W62" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="63" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6107,7 +6101,7 @@
         <v>77</v>
       </c>
       <c r="W63" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6168,7 +6162,7 @@
         <v>77</v>
       </c>
       <c r="W64" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="65" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6229,7 +6223,7 @@
         <v>77</v>
       </c>
       <c r="W65" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6290,7 +6284,7 @@
         <v>77</v>
       </c>
       <c r="W66" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6351,7 +6345,7 @@
         <v>77</v>
       </c>
       <c r="W67" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6412,7 +6406,7 @@
         <v>77</v>
       </c>
       <c r="W68" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="69" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6473,7 +6467,7 @@
         <v>77</v>
       </c>
       <c r="W69" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="70" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6534,7 +6528,7 @@
         <v>77</v>
       </c>
       <c r="W70" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="71" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6595,7 +6589,7 @@
         <v>77</v>
       </c>
       <c r="W71" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="72" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6656,7 +6650,7 @@
         <v>77</v>
       </c>
       <c r="W72" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="73" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6717,7 +6711,7 @@
         <v>77</v>
       </c>
       <c r="W73" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="74" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6778,7 +6772,7 @@
         <v>77</v>
       </c>
       <c r="W74" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="75" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6839,7 +6833,7 @@
         <v>77</v>
       </c>
       <c r="W75" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="76" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6900,7 +6894,7 @@
         <v>77</v>
       </c>
       <c r="W76" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="77" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6961,7 +6955,7 @@
         <v>77</v>
       </c>
       <c r="W77" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7022,7 +7016,7 @@
         <v>77</v>
       </c>
       <c r="W78" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="79" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7083,7 +7077,7 @@
         <v>77</v>
       </c>
       <c r="W79" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="80" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7144,7 +7138,7 @@
         <v>77</v>
       </c>
       <c r="W80" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="81" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7205,7 +7199,7 @@
         <v>77</v>
       </c>
       <c r="W81" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="82" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7266,7 +7260,7 @@
         <v>77</v>
       </c>
       <c r="W82" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="83" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7327,7 +7321,7 @@
         <v>77</v>
       </c>
       <c r="W83" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="84" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7388,7 +7382,7 @@
         <v>77</v>
       </c>
       <c r="W84" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="85" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7449,7 +7443,7 @@
         <v>77</v>
       </c>
       <c r="W85" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="86" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7510,7 +7504,7 @@
         <v>77</v>
       </c>
       <c r="W86" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="87" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7571,7 +7565,7 @@
         <v>77</v>
       </c>
       <c r="W87" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="88" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7632,7 +7626,7 @@
         <v>77</v>
       </c>
       <c r="W88" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="89" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7693,7 +7687,7 @@
         <v>77</v>
       </c>
       <c r="W89" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="90" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7754,7 +7748,7 @@
         <v>77</v>
       </c>
       <c r="W90" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="91" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7815,7 +7809,7 @@
         <v>77</v>
       </c>
       <c r="W91" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="92" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7876,7 +7870,7 @@
         <v>77</v>
       </c>
       <c r="W92" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="93" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7937,7 +7931,7 @@
         <v>77</v>
       </c>
       <c r="W93" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="94" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7998,7 +7992,7 @@
         <v>77</v>
       </c>
       <c r="W94" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="95" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8059,7 +8053,7 @@
         <v>77</v>
       </c>
       <c r="W95" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="96" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8120,7 +8114,7 @@
         <v>77</v>
       </c>
       <c r="W96" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="97" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8181,7 +8175,7 @@
         <v>77</v>
       </c>
       <c r="W97" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="98" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8242,7 +8236,7 @@
         <v>77</v>
       </c>
       <c r="W98" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="99" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8303,7 +8297,7 @@
         <v>77</v>
       </c>
       <c r="W99" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="100" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8364,7 +8358,7 @@
         <v>77</v>
       </c>
       <c r="W100" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="101" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8425,7 +8419,7 @@
         <v>77</v>
       </c>
       <c r="W101" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="102" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8486,7 +8480,7 @@
         <v>77</v>
       </c>
       <c r="W102" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="103" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8547,7 +8541,7 @@
         <v>77</v>
       </c>
       <c r="W103" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="104" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8608,7 +8602,7 @@
         <v>77</v>
       </c>
       <c r="W104" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="105" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8669,7 +8663,7 @@
         <v>77</v>
       </c>
       <c r="W105" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="106" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8730,7 +8724,7 @@
         <v>77</v>
       </c>
       <c r="W106" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="107" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8791,7 +8785,7 @@
         <v>77</v>
       </c>
       <c r="W107" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="108" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8852,7 +8846,7 @@
         <v>77</v>
       </c>
       <c r="W108" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="109" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8913,7 +8907,7 @@
         <v>77</v>
       </c>
       <c r="W109" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="110" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8974,7 +8968,7 @@
         <v>77</v>
       </c>
       <c r="W110" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="111" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9035,7 +9029,7 @@
         <v>77</v>
       </c>
       <c r="W111" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="112" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9096,7 +9090,7 @@
         <v>77</v>
       </c>
       <c r="W112" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="113" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9157,7 +9151,7 @@
         <v>77</v>
       </c>
       <c r="W113" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="114" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9218,7 +9212,7 @@
         <v>77</v>
       </c>
       <c r="W114" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="115" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9279,7 +9273,7 @@
         <v>77</v>
       </c>
       <c r="W115" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="116" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9340,7 +9334,7 @@
         <v>77</v>
       </c>
       <c r="W116" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="117" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9401,7 +9395,7 @@
         <v>77</v>
       </c>
       <c r="W117" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="118" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9462,7 +9456,7 @@
         <v>77</v>
       </c>
       <c r="W118" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="119" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9523,7 +9517,7 @@
         <v>77</v>
       </c>
       <c r="W119" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="120" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9584,7 +9578,7 @@
         <v>77</v>
       </c>
       <c r="W120" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="121" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9643,7 +9637,7 @@
         <v>77</v>
       </c>
       <c r="W121" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="122" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9702,7 +9696,7 @@
         <v>77</v>
       </c>
       <c r="W122" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="123" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9761,7 +9755,7 @@
         <v>77</v>
       </c>
       <c r="W123" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="124" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9820,7 +9814,7 @@
         <v>77</v>
       </c>
       <c r="W124" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="125" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9879,7 +9873,7 @@
         <v>77</v>
       </c>
       <c r="W125" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="126" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9938,7 +9932,7 @@
         <v>77</v>
       </c>
       <c r="W126" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="127" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9997,7 +9991,7 @@
         <v>77</v>
       </c>
       <c r="W127" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="128" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10056,7 +10050,7 @@
         <v>77</v>
       </c>
       <c r="W128" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="129" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10115,7 +10109,7 @@
         <v>77</v>
       </c>
       <c r="W129" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="130" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10174,7 +10168,7 @@
         <v>77</v>
       </c>
       <c r="W130" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="131" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10233,7 +10227,7 @@
         <v>77</v>
       </c>
       <c r="W131" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="132" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10292,7 +10286,7 @@
         <v>77</v>
       </c>
       <c r="W132" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="133" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10351,7 +10345,7 @@
         <v>77</v>
       </c>
       <c r="W133" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="134" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10410,7 +10404,7 @@
         <v>77</v>
       </c>
       <c r="W134" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="135" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10469,7 +10463,7 @@
         <v>77</v>
       </c>
       <c r="W135" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="136" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10528,7 +10522,7 @@
         <v>77</v>
       </c>
       <c r="W136" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="137" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10587,7 +10581,7 @@
         <v>77</v>
       </c>
       <c r="W137" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="138" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10646,7 +10640,7 @@
         <v>77</v>
       </c>
       <c r="W138" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="139" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10705,7 +10699,7 @@
         <v>77</v>
       </c>
       <c r="W139" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="140" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10764,7 +10758,7 @@
         <v>77</v>
       </c>
       <c r="W140" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="141" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10823,7 +10817,7 @@
         <v>77</v>
       </c>
       <c r="W141" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="142" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10882,7 +10876,7 @@
         <v>77</v>
       </c>
       <c r="W142" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="143" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10941,7 +10935,7 @@
         <v>77</v>
       </c>
       <c r="W143" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="144" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11000,7 +10994,7 @@
         <v>77</v>
       </c>
       <c r="W144" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="145" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11059,7 +11053,7 @@
         <v>77</v>
       </c>
       <c r="W145" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="146" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11118,7 +11112,7 @@
         <v>77</v>
       </c>
       <c r="W146" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11177,7 +11171,7 @@
         <v>77</v>
       </c>
       <c r="W147" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="148" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11236,7 +11230,7 @@
         <v>77</v>
       </c>
       <c r="W148" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="149" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11295,7 +11289,7 @@
         <v>77</v>
       </c>
       <c r="W149" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="150" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11354,7 +11348,7 @@
         <v>77</v>
       </c>
       <c r="W150" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="151" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11413,7 +11407,7 @@
         <v>77</v>
       </c>
       <c r="W151" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="152" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11472,7 +11466,7 @@
         <v>77</v>
       </c>
       <c r="W152" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="153" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11531,7 +11525,7 @@
         <v>77</v>
       </c>
       <c r="W153" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="154" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11590,7 +11584,7 @@
         <v>77</v>
       </c>
       <c r="W154" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="155" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11649,7 +11643,7 @@
         <v>77</v>
       </c>
       <c r="W155" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="156" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11708,7 +11702,7 @@
         <v>77</v>
       </c>
       <c r="W156" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="157" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11767,7 +11761,7 @@
         <v>77</v>
       </c>
       <c r="W157" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="158" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11826,7 +11820,7 @@
         <v>77</v>
       </c>
       <c r="W158" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="159" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11885,7 +11879,7 @@
         <v>77</v>
       </c>
       <c r="W159" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="160" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11944,7 +11938,7 @@
         <v>77</v>
       </c>
       <c r="W160" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="161" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12003,7 +11997,7 @@
         <v>77</v>
       </c>
       <c r="W161" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="162" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12062,7 +12056,7 @@
         <v>77</v>
       </c>
       <c r="W162" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="163" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12121,7 +12115,7 @@
         <v>77</v>
       </c>
       <c r="W163" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="164" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12180,7 +12174,7 @@
         <v>77</v>
       </c>
       <c r="W164" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="165" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12239,7 +12233,7 @@
         <v>77</v>
       </c>
       <c r="W165" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="166" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12298,7 +12292,7 @@
         <v>77</v>
       </c>
       <c r="W166" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="167" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12357,7 +12351,7 @@
         <v>77</v>
       </c>
       <c r="W167" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="168" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12416,7 +12410,7 @@
         <v>77</v>
       </c>
       <c r="W168" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="169" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12475,7 +12469,7 @@
         <v>77</v>
       </c>
       <c r="W169" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="170" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12534,7 +12528,7 @@
         <v>77</v>
       </c>
       <c r="W170" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="171" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12593,7 +12587,7 @@
         <v>77</v>
       </c>
       <c r="W171" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="172" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12652,7 +12646,7 @@
         <v>77</v>
       </c>
       <c r="W172" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="173" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12711,7 +12705,7 @@
         <v>77</v>
       </c>
       <c r="W173" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="174" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12770,7 +12764,7 @@
         <v>77</v>
       </c>
       <c r="W174" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="175" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12831,7 +12825,7 @@
         <v>77</v>
       </c>
       <c r="W175" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="176" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12892,7 +12886,7 @@
         <v>77</v>
       </c>
       <c r="W176" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="177" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12953,7 +12947,7 @@
         <v>77</v>
       </c>
       <c r="W177" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="178" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13014,7 +13008,7 @@
         <v>77</v>
       </c>
       <c r="W178" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="179" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13075,7 +13069,7 @@
         <v>77</v>
       </c>
       <c r="W179" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="180" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13136,7 +13130,7 @@
         <v>77</v>
       </c>
       <c r="W180" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="181" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13195,7 +13189,7 @@
         <v>77</v>
       </c>
       <c r="W181" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="182" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13254,7 +13248,7 @@
         <v>77</v>
       </c>
       <c r="W182" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="183" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13313,7 +13307,7 @@
         <v>77</v>
       </c>
       <c r="W183" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="184" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13372,7 +13366,7 @@
         <v>77</v>
       </c>
       <c r="W184" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="185" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13431,7 +13425,7 @@
         <v>77</v>
       </c>
       <c r="W185" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="186" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13490,7 +13484,7 @@
         <v>77</v>
       </c>
       <c r="W186" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="187" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13549,7 +13543,7 @@
         <v>77</v>
       </c>
       <c r="W187" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="188" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13608,7 +13602,7 @@
         <v>77</v>
       </c>
       <c r="W188" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="189" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13667,7 +13661,7 @@
         <v>77</v>
       </c>
       <c r="W189" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="190" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13726,7 +13720,7 @@
         <v>77</v>
       </c>
       <c r="W190" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="191" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13785,7 +13779,7 @@
         <v>77</v>
       </c>
       <c r="W191" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="192" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13844,7 +13838,7 @@
         <v>77</v>
       </c>
       <c r="W192" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="193" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13903,7 +13897,7 @@
         <v>77</v>
       </c>
       <c r="W193" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="194" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13962,7 +13956,7 @@
         <v>77</v>
       </c>
       <c r="W194" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="195" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14021,7 +14015,7 @@
         <v>77</v>
       </c>
       <c r="W195" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="196" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14080,7 +14074,7 @@
         <v>77</v>
       </c>
       <c r="W196" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="197" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14139,7 +14133,7 @@
         <v>77</v>
       </c>
       <c r="W197" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="198" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14198,7 +14192,7 @@
         <v>77</v>
       </c>
       <c r="W198" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="199" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14257,7 +14251,7 @@
         <v>77</v>
       </c>
       <c r="W199" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="200" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14316,7 +14310,7 @@
         <v>77</v>
       </c>
       <c r="W200" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="201" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14375,7 +14369,7 @@
         <v>77</v>
       </c>
       <c r="W201" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="202" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14434,7 +14428,7 @@
         <v>77</v>
       </c>
       <c r="W202" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="203" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14493,7 +14487,7 @@
         <v>77</v>
       </c>
       <c r="W203" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="204" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14552,7 +14546,7 @@
         <v>77</v>
       </c>
       <c r="W204" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="205" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14611,7 +14605,7 @@
         <v>77</v>
       </c>
       <c r="W205" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="206" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14670,7 +14664,7 @@
         <v>77</v>
       </c>
       <c r="W206" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="207" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14729,7 +14723,7 @@
         <v>77</v>
       </c>
       <c r="W207" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="208" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14788,7 +14782,7 @@
         <v>77</v>
       </c>
       <c r="W208" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="209" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14847,7 +14841,7 @@
         <v>77</v>
       </c>
       <c r="W209" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="210" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14906,7 +14900,7 @@
         <v>77</v>
       </c>
       <c r="W210" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="211" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14965,7 +14959,7 @@
         <v>77</v>
       </c>
       <c r="W211" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="212" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15024,7 +15018,7 @@
         <v>77</v>
       </c>
       <c r="W212" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="213" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15083,7 +15077,7 @@
         <v>77</v>
       </c>
       <c r="W213" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="214" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15142,7 +15136,7 @@
         <v>77</v>
       </c>
       <c r="W214" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="215" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15201,7 +15195,7 @@
         <v>77</v>
       </c>
       <c r="W215" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="216" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15260,7 +15254,7 @@
         <v>77</v>
       </c>
       <c r="W216" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="217" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15319,7 +15313,7 @@
         <v>77</v>
       </c>
       <c r="W217" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="218" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15378,7 +15372,7 @@
         <v>77</v>
       </c>
       <c r="W218" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="219" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15437,7 +15431,7 @@
         <v>77</v>
       </c>
       <c r="W219" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="220" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15496,7 +15490,7 @@
         <v>77</v>
       </c>
       <c r="W220" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="221" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15555,7 +15549,7 @@
         <v>77</v>
       </c>
       <c r="W221" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="222" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15614,7 +15608,7 @@
         <v>77</v>
       </c>
       <c r="W222" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="223" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15673,7 +15667,7 @@
         <v>77</v>
       </c>
       <c r="W223" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="224" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15732,7 +15726,7 @@
         <v>77</v>
       </c>
       <c r="W224" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="225" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15791,7 +15785,7 @@
         <v>77</v>
       </c>
       <c r="W225" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="226" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15850,7 +15844,7 @@
         <v>77</v>
       </c>
       <c r="W226" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="227" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15909,7 +15903,7 @@
         <v>77</v>
       </c>
       <c r="W227" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="228" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15968,7 +15962,7 @@
         <v>77</v>
       </c>
       <c r="W228" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="229" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16027,7 +16021,7 @@
         <v>77</v>
       </c>
       <c r="W229" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="230" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16086,7 +16080,7 @@
         <v>77</v>
       </c>
       <c r="W230" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="231" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16145,7 +16139,7 @@
         <v>77</v>
       </c>
       <c r="W231" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="232" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16204,7 +16198,7 @@
         <v>77</v>
       </c>
       <c r="W232" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="233" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16263,7 +16257,7 @@
         <v>77</v>
       </c>
       <c r="W233" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="234" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16322,7 +16316,7 @@
         <v>77</v>
       </c>
       <c r="W234" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="235" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16381,7 +16375,7 @@
         <v>77</v>
       </c>
       <c r="W235" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="236" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16440,7 +16434,7 @@
         <v>77</v>
       </c>
       <c r="W236" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="237" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16499,7 +16493,7 @@
         <v>77</v>
       </c>
       <c r="W237" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="238" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16558,7 +16552,7 @@
         <v>77</v>
       </c>
       <c r="W238" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="239" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16617,7 +16611,7 @@
         <v>77</v>
       </c>
       <c r="W239" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="240" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16676,7 +16670,7 @@
         <v>77</v>
       </c>
       <c r="W240" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="241" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16735,7 +16729,7 @@
         <v>77</v>
       </c>
       <c r="W241" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="242" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16794,7 +16788,7 @@
         <v>77</v>
       </c>
       <c r="W242" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="243" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16853,7 +16847,7 @@
         <v>77</v>
       </c>
       <c r="W243" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="244" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16912,7 +16906,7 @@
         <v>77</v>
       </c>
       <c r="W244" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="245" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16971,7 +16965,7 @@
         <v>77</v>
       </c>
       <c r="W245" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="246" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17030,7 +17024,7 @@
         <v>77</v>
       </c>
       <c r="W246" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="247" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17089,7 +17083,7 @@
         <v>77</v>
       </c>
       <c r="W247" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="248" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17148,7 +17142,7 @@
         <v>77</v>
       </c>
       <c r="W248" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="249" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17207,7 +17201,7 @@
         <v>77</v>
       </c>
       <c r="W249" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="250" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17266,7 +17260,7 @@
         <v>77</v>
       </c>
       <c r="W250" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="251" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17325,7 +17319,7 @@
         <v>77</v>
       </c>
       <c r="W251" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="252" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17384,7 +17378,7 @@
         <v>77</v>
       </c>
       <c r="W252" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="253" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17443,7 +17437,7 @@
         <v>77</v>
       </c>
       <c r="W253" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="254" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17502,7 +17496,7 @@
         <v>77</v>
       </c>
       <c r="W254" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="255" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17561,7 +17555,7 @@
         <v>77</v>
       </c>
       <c r="W255" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="256" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17620,7 +17614,7 @@
         <v>77</v>
       </c>
       <c r="W256" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="257" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17679,7 +17673,7 @@
         <v>77</v>
       </c>
       <c r="W257" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="258" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17738,7 +17732,7 @@
         <v>77</v>
       </c>
       <c r="W258" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="259" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17797,7 +17791,7 @@
         <v>77</v>
       </c>
       <c r="W259" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="260" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17856,7 +17850,7 @@
         <v>77</v>
       </c>
       <c r="W260" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="261" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17915,7 +17909,7 @@
         <v>77</v>
       </c>
       <c r="W261" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="262" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17974,7 +17968,7 @@
         <v>77</v>
       </c>
       <c r="W262" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="263" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18033,7 +18027,7 @@
         <v>77</v>
       </c>
       <c r="W263" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="264" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18092,7 +18086,7 @@
         <v>77</v>
       </c>
       <c r="W264" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="265" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18151,7 +18145,7 @@
         <v>77</v>
       </c>
       <c r="W265" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="266" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18210,7 +18204,7 @@
         <v>77</v>
       </c>
       <c r="W266" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="267" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18269,7 +18263,7 @@
         <v>77</v>
       </c>
       <c r="W267" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="268" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18328,7 +18322,7 @@
         <v>77</v>
       </c>
       <c r="W268" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="269" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18387,7 +18381,7 @@
         <v>77</v>
       </c>
       <c r="W269" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="270" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18446,7 +18440,7 @@
         <v>77</v>
       </c>
       <c r="W270" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="271" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18505,7 +18499,7 @@
         <v>77</v>
       </c>
       <c r="W271" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="272" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18564,7 +18558,7 @@
         <v>77</v>
       </c>
       <c r="W272" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="273" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18623,7 +18617,7 @@
         <v>77</v>
       </c>
       <c r="W273" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="274" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18686,7 +18680,7 @@
         <v>77</v>
       </c>
       <c r="W274" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="275" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18749,7 +18743,7 @@
         <v>77</v>
       </c>
       <c r="W275" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="276" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18812,7 +18806,7 @@
         <v>77</v>
       </c>
       <c r="W276" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="277" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18875,7 +18869,7 @@
         <v>77</v>
       </c>
       <c r="W277" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="278" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18938,7 +18932,7 @@
         <v>77</v>
       </c>
       <c r="W278" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="279" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19001,7 +18995,7 @@
         <v>77</v>
       </c>
       <c r="W279" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="280" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19064,7 +19058,7 @@
         <v>77</v>
       </c>
       <c r="W280" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="281" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19125,7 +19119,7 @@
         <v>77</v>
       </c>
       <c r="W281" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="282" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19186,7 +19180,7 @@
         <v>77</v>
       </c>
       <c r="W282" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="283" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19247,7 +19241,7 @@
         <v>77</v>
       </c>
       <c r="W283" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="284" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19308,7 +19302,7 @@
         <v>77</v>
       </c>
       <c r="W284" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="285" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19369,7 +19363,7 @@
         <v>77</v>
       </c>
       <c r="W285" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="286" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19430,7 +19424,7 @@
         <v>77</v>
       </c>
       <c r="W286" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="287" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19491,7 +19485,7 @@
         <v>77</v>
       </c>
       <c r="W287" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="288" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19552,7 +19546,7 @@
         <v>77</v>
       </c>
       <c r="W288" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="289" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19613,7 +19607,7 @@
         <v>77</v>
       </c>
       <c r="W289" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="290" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19674,7 +19668,7 @@
         <v>77</v>
       </c>
       <c r="W290" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="291" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19735,7 +19729,7 @@
         <v>77</v>
       </c>
       <c r="W291" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="292" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19796,7 +19790,7 @@
         <v>77</v>
       </c>
       <c r="W292" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="293" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19857,7 +19851,7 @@
         <v>77</v>
       </c>
       <c r="W293" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="294" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19918,7 +19912,7 @@
         <v>77</v>
       </c>
       <c r="W294" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="295" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19979,7 +19973,7 @@
         <v>77</v>
       </c>
       <c r="W295" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="296" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20040,7 +20034,7 @@
         <v>77</v>
       </c>
       <c r="W296" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="297" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20099,7 +20093,7 @@
         <v>77</v>
       </c>
       <c r="W297" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="298" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20158,7 +20152,7 @@
         <v>77</v>
       </c>
       <c r="W298" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="299" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20217,7 +20211,7 @@
         <v>77</v>
       </c>
       <c r="W299" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="300" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20276,7 +20270,7 @@
         <v>77</v>
       </c>
       <c r="W300" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="301" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20335,7 +20329,7 @@
         <v>77</v>
       </c>
       <c r="W301" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="302" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20394,7 +20388,7 @@
         <v>77</v>
       </c>
       <c r="W302" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="303" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20453,7 +20447,7 @@
         <v>77</v>
       </c>
       <c r="W303" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="304" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20514,7 +20508,7 @@
         <v>77</v>
       </c>
       <c r="W304" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="305" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20575,7 +20569,7 @@
         <v>77</v>
       </c>
       <c r="W305" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="306" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20636,7 +20630,7 @@
         <v>77</v>
       </c>
       <c r="W306" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="307" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20697,7 +20691,7 @@
         <v>77</v>
       </c>
       <c r="W307" s="89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="308" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20756,7 +20750,7 @@
         <v>77</v>
       </c>
       <c r="W308" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="309" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20815,7 +20809,7 @@
         <v>77</v>
       </c>
       <c r="W309" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="310" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20874,7 +20868,7 @@
         <v>77</v>
       </c>
       <c r="W310" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="311" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20933,7 +20927,7 @@
         <v>77</v>
       </c>
       <c r="W311" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="312" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20992,7 +20986,7 @@
         <v>77</v>
       </c>
       <c r="W312" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="313" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21051,7 +21045,7 @@
         <v>77</v>
       </c>
       <c r="W313" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="314" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21110,7 +21104,7 @@
         <v>77</v>
       </c>
       <c r="W314" s="90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="315" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21169,7 +21163,7 @@
         <v>77</v>
       </c>
       <c r="W315" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="316" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21228,7 +21222,7 @@
         <v>77</v>
       </c>
       <c r="W316" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="317" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21287,7 +21281,7 @@
         <v>77</v>
       </c>
       <c r="W317" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="318" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21346,7 +21340,7 @@
         <v>77</v>
       </c>
       <c r="W318" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="319" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21405,7 +21399,7 @@
         <v>77</v>
       </c>
       <c r="W319" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="320" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21464,7 +21458,7 @@
         <v>77</v>
       </c>
       <c r="W320" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="321" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21523,7 +21517,7 @@
         <v>77</v>
       </c>
       <c r="W321" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="322" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21582,7 +21576,7 @@
         <v>77</v>
       </c>
       <c r="W322" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="323" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21641,7 +21635,7 @@
         <v>77</v>
       </c>
       <c r="W323" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="324" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21700,7 +21694,7 @@
         <v>77</v>
       </c>
       <c r="W324" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="325" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21759,7 +21753,7 @@
         <v>77</v>
       </c>
       <c r="W325" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="326" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21818,7 +21812,7 @@
         <v>77</v>
       </c>
       <c r="W326" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="327" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21877,7 +21871,7 @@
         <v>77</v>
       </c>
       <c r="W327" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="328" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21936,7 +21930,7 @@
         <v>77</v>
       </c>
       <c r="W328" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="329" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21995,7 +21989,7 @@
         <v>77</v>
       </c>
       <c r="W329" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="330" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22054,7 +22048,7 @@
         <v>77</v>
       </c>
       <c r="W330" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="331" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22113,7 +22107,7 @@
         <v>77</v>
       </c>
       <c r="W331" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="332" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22172,7 +22166,7 @@
         <v>77</v>
       </c>
       <c r="W332" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="333" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22231,7 +22225,7 @@
         <v>77</v>
       </c>
       <c r="W333" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="334" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22290,7 +22284,7 @@
         <v>77</v>
       </c>
       <c r="W334" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="335" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22351,7 +22345,7 @@
         <v>77</v>
       </c>
       <c r="W335" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="336" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22412,7 +22406,7 @@
         <v>77</v>
       </c>
       <c r="W336" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="337" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22473,7 +22467,7 @@
         <v>77</v>
       </c>
       <c r="W337" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="338" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22534,7 +22528,7 @@
         <v>77</v>
       </c>
       <c r="W338" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="339" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22595,7 +22589,7 @@
         <v>77</v>
       </c>
       <c r="W339" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="340" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22656,7 +22650,7 @@
         <v>77</v>
       </c>
       <c r="W340" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="341" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22717,7 +22711,7 @@
         <v>77</v>
       </c>
       <c r="W341" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="342" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22778,7 +22772,7 @@
         <v>77</v>
       </c>
       <c r="W342" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="343" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22839,7 +22833,7 @@
         <v>77</v>
       </c>
       <c r="W343" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="344" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22900,7 +22894,7 @@
         <v>77</v>
       </c>
       <c r="W344" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="345" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22961,7 +22955,7 @@
         <v>77</v>
       </c>
       <c r="W345" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="346" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23022,7 +23016,7 @@
         <v>77</v>
       </c>
       <c r="W346" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="347" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23083,7 +23077,7 @@
         <v>77</v>
       </c>
       <c r="W347" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="348" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23144,7 +23138,7 @@
         <v>77</v>
       </c>
       <c r="W348" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="349" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23205,7 +23199,7 @@
         <v>77</v>
       </c>
       <c r="W349" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="350" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23266,7 +23260,7 @@
         <v>77</v>
       </c>
       <c r="W350" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="351" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23327,7 +23321,7 @@
         <v>77</v>
       </c>
       <c r="W351" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="352" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23388,7 +23382,7 @@
         <v>77</v>
       </c>
       <c r="W352" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="353" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23449,7 +23443,7 @@
         <v>77</v>
       </c>
       <c r="W353" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="354" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23510,7 +23504,7 @@
         <v>77</v>
       </c>
       <c r="W354" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="355" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23571,7 +23565,7 @@
         <v>77</v>
       </c>
       <c r="W355" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="356" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23632,7 +23626,7 @@
         <v>77</v>
       </c>
       <c r="W356" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="357" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23693,7 +23687,7 @@
         <v>77</v>
       </c>
       <c r="W357" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="358" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23754,7 +23748,7 @@
         <v>77</v>
       </c>
       <c r="W358" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="359" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23815,7 +23809,7 @@
         <v>77</v>
       </c>
       <c r="W359" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="360" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23876,7 +23870,7 @@
         <v>77</v>
       </c>
       <c r="W360" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="361" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23937,7 +23931,7 @@
         <v>77</v>
       </c>
       <c r="W361" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="362" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23998,7 +23992,7 @@
         <v>77</v>
       </c>
       <c r="W362" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="363" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24059,7 +24053,7 @@
         <v>77</v>
       </c>
       <c r="W363" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="364" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24118,7 +24112,7 @@
         <v>77</v>
       </c>
       <c r="W364" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="365" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24177,7 +24171,7 @@
         <v>77</v>
       </c>
       <c r="W365" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="366" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24236,7 +24230,7 @@
         <v>77</v>
       </c>
       <c r="W366" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="367" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24295,7 +24289,7 @@
         <v>77</v>
       </c>
       <c r="W367" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="368" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24354,7 +24348,7 @@
         <v>77</v>
       </c>
       <c r="W368" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="369" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24413,7 +24407,7 @@
         <v>77</v>
       </c>
       <c r="W369" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="370" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24474,7 +24468,7 @@
         <v>77</v>
       </c>
       <c r="W370" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="371" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24535,7 +24529,7 @@
         <v>77</v>
       </c>
       <c r="W371" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="372" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24596,7 +24590,7 @@
         <v>77</v>
       </c>
       <c r="W372" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="373" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24657,7 +24651,7 @@
         <v>77</v>
       </c>
       <c r="W373" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="374" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24718,7 +24712,7 @@
         <v>77</v>
       </c>
       <c r="W374" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="375" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24779,7 +24773,7 @@
         <v>77</v>
       </c>
       <c r="W375" s="90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="376" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24840,7 +24834,7 @@
         <v>77</v>
       </c>
       <c r="W376" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="377" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24901,7 +24895,7 @@
         <v>77</v>
       </c>
       <c r="W377" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="378" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24962,7 +24956,7 @@
         <v>77</v>
       </c>
       <c r="W378" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="379" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25023,7 +25017,7 @@
         <v>77</v>
       </c>
       <c r="W379" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="380" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25084,7 +25078,7 @@
         <v>77</v>
       </c>
       <c r="W380" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="381" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25145,7 +25139,7 @@
         <v>77</v>
       </c>
       <c r="W381" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="382" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25206,7 +25200,7 @@
         <v>77</v>
       </c>
       <c r="W382" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="383" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25267,7 +25261,7 @@
         <v>77</v>
       </c>
       <c r="W383" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="384" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25328,7 +25322,7 @@
         <v>77</v>
       </c>
       <c r="W384" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="385" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25389,7 +25383,7 @@
         <v>77</v>
       </c>
       <c r="W385" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="386" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25450,7 +25444,7 @@
         <v>77</v>
       </c>
       <c r="W386" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="387" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25511,7 +25505,7 @@
         <v>77</v>
       </c>
       <c r="W387" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="388" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25572,7 +25566,7 @@
         <v>77</v>
       </c>
       <c r="W388" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="389" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25633,7 +25627,7 @@
         <v>77</v>
       </c>
       <c r="W389" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="390" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25694,7 +25688,7 @@
         <v>77</v>
       </c>
       <c r="W390" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="391" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25755,7 +25749,7 @@
         <v>77</v>
       </c>
       <c r="W391" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="392" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25816,7 +25810,7 @@
         <v>77</v>
       </c>
       <c r="W392" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="393" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25877,7 +25871,7 @@
         <v>77</v>
       </c>
       <c r="W393" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="394" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25938,7 +25932,7 @@
         <v>77</v>
       </c>
       <c r="W394" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="395" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25999,7 +25993,7 @@
         <v>77</v>
       </c>
       <c r="W395" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="396" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26060,7 +26054,7 @@
         <v>77</v>
       </c>
       <c r="W396" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="397" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26121,7 +26115,7 @@
         <v>77</v>
       </c>
       <c r="W397" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="398" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26182,7 +26176,7 @@
         <v>77</v>
       </c>
       <c r="W398" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="399" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26243,7 +26237,7 @@
         <v>77</v>
       </c>
       <c r="W399" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="400" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26304,7 +26298,7 @@
         <v>77</v>
       </c>
       <c r="W400" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="401" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26365,7 +26359,7 @@
         <v>77</v>
       </c>
       <c r="W401" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="402" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26426,7 +26420,7 @@
         <v>77</v>
       </c>
       <c r="W402" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="403" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26487,7 +26481,7 @@
         <v>77</v>
       </c>
       <c r="W403" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="404" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26548,7 +26542,7 @@
         <v>77</v>
       </c>
       <c r="W404" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="405" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26609,7 +26603,7 @@
         <v>77</v>
       </c>
       <c r="W405" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="406" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26670,7 +26664,7 @@
         <v>77</v>
       </c>
       <c r="W406" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="407" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26731,7 +26725,7 @@
         <v>77</v>
       </c>
       <c r="W407" s="89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="408" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26792,7 +26786,7 @@
         <v>197</v>
       </c>
       <c r="W408" s="55" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="409" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26853,7 +26847,7 @@
         <v>197</v>
       </c>
       <c r="W409" s="55" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="410" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26914,7 +26908,7 @@
         <v>197</v>
       </c>
       <c r="W410" s="55" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="411" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26975,7 +26969,7 @@
         <v>197</v>
       </c>
       <c r="W411" s="55" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="412" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27038,7 +27032,7 @@
         <v>197</v>
       </c>
       <c r="W412" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="413" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27101,7 +27095,7 @@
         <v>197</v>
       </c>
       <c r="W413" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="414" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27164,7 +27158,7 @@
         <v>197</v>
       </c>
       <c r="W414" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="415" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27227,7 +27221,7 @@
         <v>197</v>
       </c>
       <c r="W415" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="416" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27290,7 +27284,7 @@
         <v>197</v>
       </c>
       <c r="W416" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="417" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27353,7 +27347,7 @@
         <v>197</v>
       </c>
       <c r="W417" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="418" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27416,7 +27410,7 @@
         <v>197</v>
       </c>
       <c r="W418" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="419" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27479,7 +27473,7 @@
         <v>197</v>
       </c>
       <c r="W419" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="420" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27542,7 +27536,7 @@
         <v>197</v>
       </c>
       <c r="W420" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="421" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27605,7 +27599,7 @@
         <v>197</v>
       </c>
       <c r="W421" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="422" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27668,7 +27662,7 @@
         <v>197</v>
       </c>
       <c r="W422" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="423" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27731,7 +27725,7 @@
         <v>197</v>
       </c>
       <c r="W423" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="424" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27794,7 +27788,7 @@
         <v>197</v>
       </c>
       <c r="W424" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="425" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27857,7 +27851,7 @@
         <v>197</v>
       </c>
       <c r="W425" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="426" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27920,7 +27914,7 @@
         <v>197</v>
       </c>
       <c r="W426" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="427" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27983,7 +27977,7 @@
         <v>197</v>
       </c>
       <c r="W427" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="428" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28046,7 +28040,7 @@
         <v>197</v>
       </c>
       <c r="W428" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="429" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28109,7 +28103,7 @@
         <v>197</v>
       </c>
       <c r="W429" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="430" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28172,7 +28166,7 @@
         <v>197</v>
       </c>
       <c r="W430" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="431" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28235,7 +28229,7 @@
         <v>197</v>
       </c>
       <c r="W431" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="432" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28298,7 +28292,7 @@
         <v>197</v>
       </c>
       <c r="W432" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="433" spans="1:41" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28361,7 +28355,7 @@
         <v>197</v>
       </c>
       <c r="W433" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="434" spans="1:41" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28424,7 +28418,7 @@
         <v>197</v>
       </c>
       <c r="W434" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="435" spans="1:41" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28487,7 +28481,7 @@
         <v>197</v>
       </c>
       <c r="W435" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="436" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28550,7 +28544,7 @@
         <v>197</v>
       </c>
       <c r="W436" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="437" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28613,7 +28607,7 @@
         <v>197</v>
       </c>
       <c r="W437" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="438" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28676,7 +28670,7 @@
         <v>197</v>
       </c>
       <c r="W438" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="439" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28739,7 +28733,7 @@
         <v>197</v>
       </c>
       <c r="W439" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="440" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28802,7 +28796,7 @@
         <v>197</v>
       </c>
       <c r="W440" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="441" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28865,7 +28859,7 @@
         <v>197</v>
       </c>
       <c r="W441" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="442" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28928,7 +28922,7 @@
         <v>197</v>
       </c>
       <c r="W442" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="443" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28991,7 +28985,7 @@
         <v>197</v>
       </c>
       <c r="W443" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="444" spans="1:41" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -29054,7 +29048,7 @@
         <v>197</v>
       </c>
       <c r="W444" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X444" s="20"/>
       <c r="Y444" s="20"/>
@@ -29135,7 +29129,7 @@
         <v>197</v>
       </c>
       <c r="W445" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X445" s="20"/>
       <c r="Y445" s="20"/>
@@ -29216,7 +29210,7 @@
         <v>197</v>
       </c>
       <c r="W446" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X446" s="20"/>
       <c r="Y446" s="20"/>
@@ -29297,7 +29291,7 @@
         <v>197</v>
       </c>
       <c r="W447" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X447" s="20"/>
       <c r="Y447" s="20"/>
@@ -29378,7 +29372,7 @@
         <v>197</v>
       </c>
       <c r="W448" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X448" s="20"/>
       <c r="Y448" s="20"/>
@@ -29459,7 +29453,7 @@
         <v>197</v>
       </c>
       <c r="W449" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X449" s="20"/>
       <c r="Y449" s="20"/>
@@ -29540,7 +29534,7 @@
         <v>197</v>
       </c>
       <c r="W450" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X450" s="20"/>
       <c r="Y450" s="20"/>
@@ -29621,7 +29615,7 @@
         <v>197</v>
       </c>
       <c r="W451" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X451" s="20"/>
       <c r="Y451" s="20"/>
@@ -29702,7 +29696,7 @@
         <v>197</v>
       </c>
       <c r="W452" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X452" s="28"/>
       <c r="Y452" s="28"/>
@@ -29783,7 +29777,7 @@
         <v>197</v>
       </c>
       <c r="W453" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X453" s="28"/>
       <c r="Y453" s="28"/>
@@ -29864,7 +29858,7 @@
         <v>197</v>
       </c>
       <c r="W454" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X454" s="28"/>
       <c r="Y454" s="28"/>
@@ -29945,7 +29939,7 @@
         <v>197</v>
       </c>
       <c r="W455" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X455" s="28"/>
       <c r="Y455" s="28"/>
@@ -30026,7 +30020,7 @@
         <v>197</v>
       </c>
       <c r="W456" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X456" s="28"/>
       <c r="Y456" s="28"/>
@@ -30107,7 +30101,7 @@
         <v>197</v>
       </c>
       <c r="W457" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X457" s="28"/>
       <c r="Y457" s="28"/>
@@ -30188,7 +30182,7 @@
         <v>197</v>
       </c>
       <c r="W458" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X458" s="28"/>
       <c r="Y458" s="28"/>
@@ -30269,7 +30263,7 @@
         <v>197</v>
       </c>
       <c r="W459" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X459" s="28"/>
       <c r="Y459" s="28"/>
@@ -30350,7 +30344,7 @@
         <v>197</v>
       </c>
       <c r="W460" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X460" s="28"/>
       <c r="Y460" s="28"/>
@@ -30431,7 +30425,7 @@
         <v>197</v>
       </c>
       <c r="W461" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X461" s="28"/>
       <c r="Y461" s="28"/>
@@ -30512,7 +30506,7 @@
         <v>197</v>
       </c>
       <c r="W462" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X462" s="28"/>
       <c r="Y462" s="28"/>
@@ -30593,7 +30587,7 @@
         <v>197</v>
       </c>
       <c r="W463" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X463" s="28"/>
       <c r="Y463" s="28"/>
@@ -30674,7 +30668,7 @@
         <v>77</v>
       </c>
       <c r="W464" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X464" s="20"/>
       <c r="Y464" s="20"/>
@@ -30691,12 +30685,8 @@
       <c r="AJ464" s="14"/>
       <c r="AK464" s="14"/>
       <c r="AL464" s="14"/>
-      <c r="AM464" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN464" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM464" s="40"/>
+      <c r="AN464" s="40"/>
     </row>
     <row r="465" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A465" s="56" t="s">
@@ -30758,7 +30748,7 @@
         <v>77</v>
       </c>
       <c r="W465" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X465" s="20"/>
       <c r="Y465" s="20"/>
@@ -30775,12 +30765,8 @@
       <c r="AJ465" s="14"/>
       <c r="AK465" s="14"/>
       <c r="AL465" s="14"/>
-      <c r="AM465" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN465" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM465" s="40"/>
+      <c r="AN465" s="40"/>
     </row>
     <row r="466" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A466" s="56" t="s">
@@ -30842,7 +30828,7 @@
         <v>77</v>
       </c>
       <c r="W466" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X466" s="20"/>
       <c r="Y466" s="20"/>
@@ -30859,12 +30845,8 @@
       <c r="AJ466" s="14"/>
       <c r="AK466" s="14"/>
       <c r="AL466" s="14"/>
-      <c r="AM466" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN466" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM466" s="40"/>
+      <c r="AN466" s="40"/>
     </row>
     <row r="467" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A467" s="56" t="s">
@@ -30926,7 +30908,7 @@
         <v>77</v>
       </c>
       <c r="W467" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X467" s="20"/>
       <c r="Y467" s="20"/>
@@ -30943,12 +30925,8 @@
       <c r="AJ467" s="14"/>
       <c r="AK467" s="14"/>
       <c r="AL467" s="14"/>
-      <c r="AM467" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN467" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM467" s="40"/>
+      <c r="AN467" s="40"/>
     </row>
     <row r="468" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A468" s="56" t="s">
@@ -31010,7 +30988,7 @@
         <v>77</v>
       </c>
       <c r="W468" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X468" s="20"/>
       <c r="Y468" s="20"/>
@@ -31027,12 +31005,8 @@
       <c r="AJ468" s="14"/>
       <c r="AK468" s="14"/>
       <c r="AL468" s="14"/>
-      <c r="AM468" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN468" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM468" s="40"/>
+      <c r="AN468" s="40"/>
     </row>
     <row r="469" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A469" s="56" t="s">
@@ -31094,7 +31068,7 @@
         <v>77</v>
       </c>
       <c r="W469" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X469" s="20"/>
       <c r="Y469" s="20"/>
@@ -31111,12 +31085,8 @@
       <c r="AJ469" s="14"/>
       <c r="AK469" s="14"/>
       <c r="AL469" s="14"/>
-      <c r="AM469" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN469" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM469" s="40"/>
+      <c r="AN469" s="40"/>
     </row>
     <row r="470" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A470" s="56" t="s">
@@ -31178,7 +31148,7 @@
         <v>77</v>
       </c>
       <c r="W470" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X470" s="20"/>
       <c r="Y470" s="20"/>
@@ -31195,12 +31165,8 @@
       <c r="AJ470" s="14"/>
       <c r="AK470" s="14"/>
       <c r="AL470" s="14"/>
-      <c r="AM470" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN470" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM470" s="40"/>
+      <c r="AN470" s="40"/>
     </row>
     <row r="471" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A471" s="56" t="s">
@@ -31262,7 +31228,7 @@
         <v>77</v>
       </c>
       <c r="W471" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X471" s="20"/>
       <c r="Y471" s="20"/>
@@ -31279,12 +31245,8 @@
       <c r="AJ471" s="14"/>
       <c r="AK471" s="14"/>
       <c r="AL471" s="14"/>
-      <c r="AM471" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN471" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM471" s="40"/>
+      <c r="AN471" s="40"/>
     </row>
     <row r="472" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A472" s="56" t="s">
@@ -31346,7 +31308,7 @@
         <v>77</v>
       </c>
       <c r="W472" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X472" s="20"/>
       <c r="Y472" s="20"/>
@@ -31363,16 +31325,12 @@
       <c r="AJ472" s="14"/>
       <c r="AK472" s="14"/>
       <c r="AL472" s="14"/>
-      <c r="AM472" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN472" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM472" s="40"/>
+      <c r="AN472" s="40"/>
     </row>
     <row r="473" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A473" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B473" s="39" t="s">
         <v>215</v>
@@ -31394,7 +31352,7 @@
         <v>208</v>
       </c>
       <c r="I473" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J473" s="41"/>
       <c r="K473" s="59">
@@ -31430,7 +31388,7 @@
         <v>77</v>
       </c>
       <c r="W473" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X473" s="20"/>
       <c r="Y473" s="20"/>
@@ -31447,16 +31405,12 @@
       <c r="AJ473" s="14"/>
       <c r="AK473" s="14"/>
       <c r="AL473" s="14"/>
-      <c r="AM473" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN473" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM473" s="40"/>
+      <c r="AN473" s="40"/>
     </row>
     <row r="474" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A474" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B474" s="39" t="s">
         <v>215</v>
@@ -31478,7 +31432,7 @@
         <v>208</v>
       </c>
       <c r="I474" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J474" s="41"/>
       <c r="K474" s="59">
@@ -31514,7 +31468,7 @@
         <v>77</v>
       </c>
       <c r="W474" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X474" s="20"/>
       <c r="Y474" s="20"/>
@@ -31531,16 +31485,12 @@
       <c r="AJ474" s="14"/>
       <c r="AK474" s="14"/>
       <c r="AL474" s="14"/>
-      <c r="AM474" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN474" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM474" s="40"/>
+      <c r="AN474" s="40"/>
     </row>
     <row r="475" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A475" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B475" s="39" t="s">
         <v>215</v>
@@ -31562,7 +31512,7 @@
         <v>208</v>
       </c>
       <c r="I475" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J475" s="41"/>
       <c r="K475" s="59">
@@ -31598,7 +31548,7 @@
         <v>77</v>
       </c>
       <c r="W475" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X475" s="20"/>
       <c r="Y475" s="20"/>
@@ -31615,16 +31565,12 @@
       <c r="AJ475" s="14"/>
       <c r="AK475" s="14"/>
       <c r="AL475" s="14"/>
-      <c r="AM475" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN475" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM475" s="40"/>
+      <c r="AN475" s="40"/>
     </row>
     <row r="476" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A476" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B476" s="39" t="s">
         <v>215</v>
@@ -31646,7 +31592,7 @@
         <v>208</v>
       </c>
       <c r="I476" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J476" s="41"/>
       <c r="K476" s="59">
@@ -31682,7 +31628,7 @@
         <v>77</v>
       </c>
       <c r="W476" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X476" s="20"/>
       <c r="Y476" s="20"/>
@@ -31699,16 +31645,12 @@
       <c r="AJ476" s="14"/>
       <c r="AK476" s="14"/>
       <c r="AL476" s="14"/>
-      <c r="AM476" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN476" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM476" s="40"/>
+      <c r="AN476" s="40"/>
     </row>
     <row r="477" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A477" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B477" s="39" t="s">
         <v>215</v>
@@ -31730,7 +31672,7 @@
         <v>208</v>
       </c>
       <c r="I477" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J477" s="41"/>
       <c r="K477" s="59">
@@ -31766,7 +31708,7 @@
         <v>77</v>
       </c>
       <c r="W477" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X477" s="20"/>
       <c r="Y477" s="20"/>
@@ -31783,16 +31725,12 @@
       <c r="AJ477" s="14"/>
       <c r="AK477" s="14"/>
       <c r="AL477" s="14"/>
-      <c r="AM477" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN477" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM477" s="40"/>
+      <c r="AN477" s="40"/>
     </row>
     <row r="478" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A478" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B478" s="39" t="s">
         <v>215</v>
@@ -31814,7 +31752,7 @@
         <v>208</v>
       </c>
       <c r="I478" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J478" s="41"/>
       <c r="K478" s="59">
@@ -31850,7 +31788,7 @@
         <v>77</v>
       </c>
       <c r="W478" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X478" s="20"/>
       <c r="Y478" s="20"/>
@@ -31867,16 +31805,12 @@
       <c r="AJ478" s="14"/>
       <c r="AK478" s="14"/>
       <c r="AL478" s="14"/>
-      <c r="AM478" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN478" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM478" s="40"/>
+      <c r="AN478" s="40"/>
     </row>
     <row r="479" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A479" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B479" s="39" t="s">
         <v>215</v>
@@ -31898,7 +31832,7 @@
         <v>208</v>
       </c>
       <c r="I479" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J479" s="41"/>
       <c r="K479" s="59">
@@ -31934,7 +31868,7 @@
         <v>77</v>
       </c>
       <c r="W479" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X479" s="20"/>
       <c r="Y479" s="20"/>
@@ -31951,16 +31885,12 @@
       <c r="AJ479" s="14"/>
       <c r="AK479" s="14"/>
       <c r="AL479" s="14"/>
-      <c r="AM479" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN479" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM479" s="40"/>
+      <c r="AN479" s="40"/>
     </row>
     <row r="480" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A480" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B480" s="39" t="s">
         <v>215</v>
@@ -31982,7 +31912,7 @@
         <v>208</v>
       </c>
       <c r="I480" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J480" s="41"/>
       <c r="K480" s="59">
@@ -32018,7 +31948,7 @@
         <v>77</v>
       </c>
       <c r="W480" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X480" s="20"/>
       <c r="Y480" s="20"/>
@@ -32035,16 +31965,12 @@
       <c r="AJ480" s="14"/>
       <c r="AK480" s="14"/>
       <c r="AL480" s="14"/>
-      <c r="AM480" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN480" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM480" s="40"/>
+      <c r="AN480" s="40"/>
     </row>
     <row r="481" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A481" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B481" s="39" t="s">
         <v>215</v>
@@ -32066,7 +31992,7 @@
         <v>208</v>
       </c>
       <c r="I481" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J481" s="41"/>
       <c r="K481" s="59">
@@ -32102,7 +32028,7 @@
         <v>77</v>
       </c>
       <c r="W481" s="91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X481" s="20"/>
       <c r="Y481" s="20"/>
@@ -32119,12 +32045,8 @@
       <c r="AJ481" s="14"/>
       <c r="AK481" s="14"/>
       <c r="AL481" s="14"/>
-      <c r="AM481" s="40" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN481" s="40" t="s">
-        <v>220</v>
-      </c>
+      <c r="AM481" s="40"/>
+      <c r="AN481" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>

--- a/data/meta_analysis/Cat meta-analysis - correlations.xlsx
+++ b/data/meta_analysis/Cat meta-analysis - correlations.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ejlundgren/Dropbox/Projects/iucn_evidence/cat_evidence_review/data/meta_analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wallacha@qut.edu.au/Documents/Research/Manuscripts/Death Star/Cats vs vertebrates/Datasets/Meta-analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A6740A-6F0A-6841-A6B7-0F9917DAB7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B96379-8D69-AC46-97EB-DA2147BD1474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29380" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Correlations" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5998" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5524" uniqueCount="209">
   <si>
     <t>scientificName</t>
   </si>
@@ -647,55 +647,7 @@
     <t>ES_32_2</t>
   </si>
   <si>
-    <t>ES_43</t>
-  </si>
-  <si>
-    <t>Procellaria cinerea</t>
-  </si>
-  <si>
-    <t>Dilley, B.J., Schoombie, S., Stevens, K., Davies, D., Perold, V., Osborne, A., Schoombie, J., Brink, C.W., Carpenter-Kling, T. and Ryan, P.G., 2018. Mouse predation affects breeding success of burrow-nesting petrels at sub-Antarctic Marion Island. Antarctic Science, 30(2), pp.93-104.</t>
-  </si>
-  <si>
-    <t>Marion Island</t>
-  </si>
-  <si>
-    <t>Before/after</t>
-  </si>
-  <si>
-    <t>Presence-absence</t>
-  </si>
-  <si>
-    <t>Breeding success</t>
-  </si>
-  <si>
-    <t>ES_37</t>
-  </si>
-  <si>
-    <t>Procellaria aequinoctialis</t>
-  </si>
-  <si>
     <t>cat_presence</t>
-  </si>
-  <si>
-    <t>ES_47a</t>
-  </si>
-  <si>
-    <t>Numenius tahitiensis</t>
-  </si>
-  <si>
-    <t>Marks, J.S. and Redmond, R.L., 1994. Conservation problems and research needs for Bristle-thighed Curlews Numenius tahitiensis on their wintering grounds. Bird Conservation International, 4(4), pp.329-341.</t>
-  </si>
-  <si>
-    <t>Phoenix Islands</t>
-  </si>
-  <si>
-    <t>Howland</t>
-  </si>
-  <si>
-    <t>ES_47b</t>
-  </si>
-  <si>
-    <t>Baker</t>
   </si>
   <si>
     <t>unit_of_replication</t>
@@ -709,9 +661,6 @@
   <si>
     <t>Nests</t>
   </si>
-  <si>
-    <t>Surveys</t>
-  </si>
 </sst>
 </file>
 
@@ -720,7 +669,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -760,19 +709,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
@@ -872,13 +808,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1119,18 +1054,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1138,9 +1061,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1152,13 +1072,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
@@ -2286,7 +2202,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AO481"/>
+  <dimension ref="A1:W443"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
@@ -2357,7 +2273,7 @@
         <v>29</v>
       </c>
       <c r="O1" s="65" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>28</v>
@@ -2380,8 +2296,8 @@
       <c r="V1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="88" t="s">
-        <v>221</v>
+      <c r="W1" s="83" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2439,8 +2355,8 @@
       <c r="V2" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W2" s="89" t="s">
-        <v>222</v>
+      <c r="W2" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2498,8 +2414,8 @@
       <c r="V3" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W3" s="89" t="s">
-        <v>222</v>
+      <c r="W3" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2557,8 +2473,8 @@
       <c r="V4" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W4" s="89" t="s">
-        <v>222</v>
+      <c r="W4" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2616,8 +2532,8 @@
       <c r="V5" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W5" s="89" t="s">
-        <v>222</v>
+      <c r="W5" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2675,8 +2591,8 @@
       <c r="V6" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W6" s="89" t="s">
-        <v>222</v>
+      <c r="W6" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2734,8 +2650,8 @@
       <c r="V7" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W7" s="89" t="s">
-        <v>222</v>
+      <c r="W7" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2793,8 +2709,8 @@
       <c r="V8" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W8" s="90" t="s">
-        <v>222</v>
+      <c r="W8" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2852,8 +2768,8 @@
       <c r="V9" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W9" s="90" t="s">
-        <v>222</v>
+      <c r="W9" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2911,8 +2827,8 @@
       <c r="V10" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W10" s="90" t="s">
-        <v>222</v>
+      <c r="W10" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -2970,8 +2886,8 @@
       <c r="V11" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W11" s="90" t="s">
-        <v>222</v>
+      <c r="W11" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3029,8 +2945,8 @@
       <c r="V12" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W12" s="90" t="s">
-        <v>222</v>
+      <c r="W12" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3088,8 +3004,8 @@
       <c r="V13" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W13" s="90" t="s">
-        <v>222</v>
+      <c r="W13" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3147,8 +3063,8 @@
       <c r="V14" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W14" s="90" t="s">
-        <v>222</v>
+      <c r="W14" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3206,8 +3122,8 @@
       <c r="V15" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W15" s="90" t="s">
-        <v>222</v>
+      <c r="W15" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3265,8 +3181,8 @@
       <c r="V16" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W16" s="90" t="s">
-        <v>222</v>
+      <c r="W16" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3324,8 +3240,8 @@
       <c r="V17" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W17" s="90" t="s">
-        <v>222</v>
+      <c r="W17" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3383,8 +3299,8 @@
       <c r="V18" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W18" s="90" t="s">
-        <v>222</v>
+      <c r="W18" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3442,8 +3358,8 @@
       <c r="V19" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W19" s="90" t="s">
-        <v>222</v>
+      <c r="W19" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3501,8 +3417,8 @@
       <c r="V20" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W20" s="90" t="s">
-        <v>222</v>
+      <c r="W20" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3560,8 +3476,8 @@
       <c r="V21" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W21" s="89" t="s">
-        <v>222</v>
+      <c r="W21" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3619,8 +3535,8 @@
       <c r="V22" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W22" s="89" t="s">
-        <v>222</v>
+      <c r="W22" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="23" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3678,8 +3594,8 @@
       <c r="V23" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W23" s="89" t="s">
-        <v>222</v>
+      <c r="W23" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3737,8 +3653,8 @@
       <c r="V24" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W24" s="89" t="s">
-        <v>222</v>
+      <c r="W24" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3796,8 +3712,8 @@
       <c r="V25" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W25" s="89" t="s">
-        <v>222</v>
+      <c r="W25" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="26" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3855,8 +3771,8 @@
       <c r="V26" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W26" s="89" t="s">
-        <v>222</v>
+      <c r="W26" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="27" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3914,8 +3830,8 @@
       <c r="V27" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W27" s="89" t="s">
-        <v>222</v>
+      <c r="W27" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -3973,8 +3889,8 @@
       <c r="V28" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W28" s="89" t="s">
-        <v>222</v>
+      <c r="W28" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="29" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4032,8 +3948,8 @@
       <c r="V29" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W29" s="89" t="s">
-        <v>222</v>
+      <c r="W29" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4091,8 +4007,8 @@
       <c r="V30" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W30" s="89" t="s">
-        <v>222</v>
+      <c r="W30" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="31" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4150,8 +4066,8 @@
       <c r="V31" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W31" s="89" t="s">
-        <v>222</v>
+      <c r="W31" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="32" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4209,8 +4125,8 @@
       <c r="V32" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W32" s="89" t="s">
-        <v>222</v>
+      <c r="W32" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="33" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4270,8 +4186,8 @@
       <c r="V33" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W33" s="90" t="s">
-        <v>222</v>
+      <c r="W33" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="34" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4331,8 +4247,8 @@
       <c r="V34" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W34" s="90" t="s">
-        <v>222</v>
+      <c r="W34" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="35" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4392,8 +4308,8 @@
       <c r="V35" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W35" s="90" t="s">
-        <v>222</v>
+      <c r="W35" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="36" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4453,8 +4369,8 @@
       <c r="V36" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W36" s="90" t="s">
-        <v>222</v>
+      <c r="W36" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="37" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4514,8 +4430,8 @@
       <c r="V37" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W37" s="90" t="s">
-        <v>222</v>
+      <c r="W37" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="38" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4575,8 +4491,8 @@
       <c r="V38" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W38" s="90" t="s">
-        <v>222</v>
+      <c r="W38" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="39" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4636,8 +4552,8 @@
       <c r="V39" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W39" s="90" t="s">
-        <v>222</v>
+      <c r="W39" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="40" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4697,8 +4613,8 @@
       <c r="V40" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W40" s="90" t="s">
-        <v>222</v>
+      <c r="W40" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4758,8 +4674,8 @@
       <c r="V41" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W41" s="90" t="s">
-        <v>222</v>
+      <c r="W41" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="42" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4819,8 +4735,8 @@
       <c r="V42" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W42" s="90" t="s">
-        <v>222</v>
+      <c r="W42" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="43" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4880,8 +4796,8 @@
       <c r="V43" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W43" s="90" t="s">
-        <v>222</v>
+      <c r="W43" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="44" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4941,8 +4857,8 @@
       <c r="V44" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W44" s="90" t="s">
-        <v>222</v>
+      <c r="W44" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5002,8 +4918,8 @@
       <c r="V45" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W45" s="90" t="s">
-        <v>222</v>
+      <c r="W45" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5063,8 +4979,8 @@
       <c r="V46" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W46" s="90" t="s">
-        <v>222</v>
+      <c r="W46" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="47" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5124,8 +5040,8 @@
       <c r="V47" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W47" s="90" t="s">
-        <v>222</v>
+      <c r="W47" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5185,8 +5101,8 @@
       <c r="V48" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W48" s="90" t="s">
-        <v>222</v>
+      <c r="W48" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="49" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5246,8 +5162,8 @@
       <c r="V49" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W49" s="90" t="s">
-        <v>222</v>
+      <c r="W49" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="50" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5307,8 +5223,8 @@
       <c r="V50" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W50" s="90" t="s">
-        <v>222</v>
+      <c r="W50" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="51" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5368,8 +5284,8 @@
       <c r="V51" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W51" s="90" t="s">
-        <v>222</v>
+      <c r="W51" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="52" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5429,8 +5345,8 @@
       <c r="V52" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W52" s="90" t="s">
-        <v>222</v>
+      <c r="W52" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="53" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5490,8 +5406,8 @@
       <c r="V53" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W53" s="90" t="s">
-        <v>222</v>
+      <c r="W53" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="54" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5551,8 +5467,8 @@
       <c r="V54" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W54" s="90" t="s">
-        <v>222</v>
+      <c r="W54" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="55" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5612,8 +5528,8 @@
       <c r="V55" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W55" s="90" t="s">
-        <v>222</v>
+      <c r="W55" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="56" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5673,8 +5589,8 @@
       <c r="V56" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W56" s="90" t="s">
-        <v>222</v>
+      <c r="W56" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="57" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5734,8 +5650,8 @@
       <c r="V57" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W57" s="89" t="s">
-        <v>222</v>
+      <c r="W57" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="58" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5795,8 +5711,8 @@
       <c r="V58" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W58" s="89" t="s">
-        <v>222</v>
+      <c r="W58" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="59" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5856,8 +5772,8 @@
       <c r="V59" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W59" s="89" t="s">
-        <v>222</v>
+      <c r="W59" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5917,8 +5833,8 @@
       <c r="V60" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W60" s="89" t="s">
-        <v>222</v>
+      <c r="W60" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="61" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -5978,8 +5894,8 @@
       <c r="V61" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W61" s="89" t="s">
-        <v>222</v>
+      <c r="W61" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6039,8 +5955,8 @@
       <c r="V62" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W62" s="89" t="s">
-        <v>222</v>
+      <c r="W62" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="63" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6100,8 +6016,8 @@
       <c r="V63" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W63" s="89" t="s">
-        <v>222</v>
+      <c r="W63" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="64" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6161,8 +6077,8 @@
       <c r="V64" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W64" s="89" t="s">
-        <v>222</v>
+      <c r="W64" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="65" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6222,8 +6138,8 @@
       <c r="V65" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W65" s="89" t="s">
-        <v>222</v>
+      <c r="W65" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="66" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6283,8 +6199,8 @@
       <c r="V66" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W66" s="89" t="s">
-        <v>222</v>
+      <c r="W66" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="67" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6344,8 +6260,8 @@
       <c r="V67" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W67" s="89" t="s">
-        <v>222</v>
+      <c r="W67" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="68" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6405,8 +6321,8 @@
       <c r="V68" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W68" s="89" t="s">
-        <v>222</v>
+      <c r="W68" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="69" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6466,8 +6382,8 @@
       <c r="V69" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W69" s="89" t="s">
-        <v>222</v>
+      <c r="W69" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="70" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6527,8 +6443,8 @@
       <c r="V70" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W70" s="89" t="s">
-        <v>222</v>
+      <c r="W70" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="71" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6588,8 +6504,8 @@
       <c r="V71" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W71" s="89" t="s">
-        <v>222</v>
+      <c r="W71" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="72" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6649,8 +6565,8 @@
       <c r="V72" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W72" s="89" t="s">
-        <v>222</v>
+      <c r="W72" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6710,8 +6626,8 @@
       <c r="V73" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W73" s="89" t="s">
-        <v>222</v>
+      <c r="W73" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="74" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6771,8 +6687,8 @@
       <c r="V74" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W74" s="89" t="s">
-        <v>222</v>
+      <c r="W74" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6832,8 +6748,8 @@
       <c r="V75" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W75" s="89" t="s">
-        <v>222</v>
+      <c r="W75" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="76" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6893,8 +6809,8 @@
       <c r="V76" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W76" s="89" t="s">
-        <v>222</v>
+      <c r="W76" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -6954,8 +6870,8 @@
       <c r="V77" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W77" s="89" t="s">
-        <v>222</v>
+      <c r="W77" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="78" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7015,8 +6931,8 @@
       <c r="V78" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W78" s="89" t="s">
-        <v>222</v>
+      <c r="W78" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="79" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7076,8 +6992,8 @@
       <c r="V79" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W79" s="89" t="s">
-        <v>222</v>
+      <c r="W79" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="80" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7137,8 +7053,8 @@
       <c r="V80" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W80" s="89" t="s">
-        <v>222</v>
+      <c r="W80" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="81" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7198,8 +7114,8 @@
       <c r="V81" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W81" s="90" t="s">
-        <v>222</v>
+      <c r="W81" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="82" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7259,8 +7175,8 @@
       <c r="V82" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W82" s="90" t="s">
-        <v>222</v>
+      <c r="W82" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="83" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7320,8 +7236,8 @@
       <c r="V83" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W83" s="90" t="s">
-        <v>222</v>
+      <c r="W83" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="84" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7381,8 +7297,8 @@
       <c r="V84" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W84" s="90" t="s">
-        <v>222</v>
+      <c r="W84" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="85" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7442,8 +7358,8 @@
       <c r="V85" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W85" s="90" t="s">
-        <v>222</v>
+      <c r="W85" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="86" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7503,8 +7419,8 @@
       <c r="V86" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W86" s="90" t="s">
-        <v>222</v>
+      <c r="W86" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="87" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7564,8 +7480,8 @@
       <c r="V87" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W87" s="90" t="s">
-        <v>222</v>
+      <c r="W87" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="88" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7625,8 +7541,8 @@
       <c r="V88" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W88" s="90" t="s">
-        <v>222</v>
+      <c r="W88" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="89" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7686,8 +7602,8 @@
       <c r="V89" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W89" s="90" t="s">
-        <v>222</v>
+      <c r="W89" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7747,8 +7663,8 @@
       <c r="V90" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W90" s="90" t="s">
-        <v>222</v>
+      <c r="W90" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="91" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7808,8 +7724,8 @@
       <c r="V91" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W91" s="90" t="s">
-        <v>222</v>
+      <c r="W91" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="92" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7869,8 +7785,8 @@
       <c r="V92" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W92" s="90" t="s">
-        <v>222</v>
+      <c r="W92" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="93" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7930,8 +7846,8 @@
       <c r="V93" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W93" s="90" t="s">
-        <v>222</v>
+      <c r="W93" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="94" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -7991,8 +7907,8 @@
       <c r="V94" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W94" s="90" t="s">
-        <v>222</v>
+      <c r="W94" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="95" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8052,8 +7968,8 @@
       <c r="V95" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W95" s="90" t="s">
-        <v>222</v>
+      <c r="W95" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="96" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8113,8 +8029,8 @@
       <c r="V96" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W96" s="90" t="s">
-        <v>222</v>
+      <c r="W96" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="97" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8174,8 +8090,8 @@
       <c r="V97" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W97" s="90" t="s">
-        <v>222</v>
+      <c r="W97" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="98" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8235,8 +8151,8 @@
       <c r="V98" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W98" s="90" t="s">
-        <v>222</v>
+      <c r="W98" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="99" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8296,8 +8212,8 @@
       <c r="V99" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W99" s="90" t="s">
-        <v>222</v>
+      <c r="W99" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="100" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8357,8 +8273,8 @@
       <c r="V100" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W100" s="90" t="s">
-        <v>222</v>
+      <c r="W100" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="101" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8418,8 +8334,8 @@
       <c r="V101" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W101" s="90" t="s">
-        <v>222</v>
+      <c r="W101" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="102" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8479,8 +8395,8 @@
       <c r="V102" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W102" s="90" t="s">
-        <v>222</v>
+      <c r="W102" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="103" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8540,8 +8456,8 @@
       <c r="V103" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W103" s="90" t="s">
-        <v>222</v>
+      <c r="W103" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="104" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8601,8 +8517,8 @@
       <c r="V104" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W104" s="90" t="s">
-        <v>222</v>
+      <c r="W104" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="105" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8662,8 +8578,8 @@
       <c r="V105" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W105" s="89" t="s">
-        <v>222</v>
+      <c r="W105" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="106" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8723,8 +8639,8 @@
       <c r="V106" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W106" s="89" t="s">
-        <v>222</v>
+      <c r="W106" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="107" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8784,8 +8700,8 @@
       <c r="V107" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W107" s="89" t="s">
-        <v>222</v>
+      <c r="W107" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="108" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8845,8 +8761,8 @@
       <c r="V108" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W108" s="89" t="s">
-        <v>222</v>
+      <c r="W108" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="109" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8906,8 +8822,8 @@
       <c r="V109" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W109" s="89" t="s">
-        <v>222</v>
+      <c r="W109" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="110" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -8967,8 +8883,8 @@
       <c r="V110" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W110" s="89" t="s">
-        <v>222</v>
+      <c r="W110" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="111" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9028,8 +8944,8 @@
       <c r="V111" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W111" s="89" t="s">
-        <v>222</v>
+      <c r="W111" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="112" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9089,8 +9005,8 @@
       <c r="V112" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W112" s="89" t="s">
-        <v>222</v>
+      <c r="W112" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9121,7 +9037,7 @@
       <c r="K113" s="28">
         <v>1</v>
       </c>
-      <c r="L113" s="84" t="s">
+      <c r="L113" s="80" t="s">
         <v>56</v>
       </c>
       <c r="M113" s="24"/>
@@ -9150,8 +9066,8 @@
       <c r="V113" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W113" s="90" t="s">
-        <v>222</v>
+      <c r="W113" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="114" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9182,7 +9098,7 @@
       <c r="K114" s="28">
         <v>2</v>
       </c>
-      <c r="L114" s="84" t="s">
+      <c r="L114" s="80" t="s">
         <v>57</v>
       </c>
       <c r="M114" s="24"/>
@@ -9211,8 +9127,8 @@
       <c r="V114" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W114" s="90" t="s">
-        <v>222</v>
+      <c r="W114" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="115" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9243,7 +9159,7 @@
       <c r="K115" s="28">
         <v>3</v>
       </c>
-      <c r="L115" s="84" t="s">
+      <c r="L115" s="80" t="s">
         <v>58</v>
       </c>
       <c r="M115" s="24"/>
@@ -9272,8 +9188,8 @@
       <c r="V115" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W115" s="90" t="s">
-        <v>222</v>
+      <c r="W115" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="116" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9304,7 +9220,7 @@
       <c r="K116" s="28">
         <v>4</v>
       </c>
-      <c r="L116" s="84" t="s">
+      <c r="L116" s="80" t="s">
         <v>59</v>
       </c>
       <c r="M116" s="24"/>
@@ -9333,8 +9249,8 @@
       <c r="V116" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W116" s="90" t="s">
-        <v>222</v>
+      <c r="W116" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="117" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9365,7 +9281,7 @@
       <c r="K117" s="28">
         <v>5</v>
       </c>
-      <c r="L117" s="84" t="s">
+      <c r="L117" s="80" t="s">
         <v>60</v>
       </c>
       <c r="M117" s="24"/>
@@ -9394,8 +9310,8 @@
       <c r="V117" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W117" s="90" t="s">
-        <v>222</v>
+      <c r="W117" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="118" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9426,7 +9342,7 @@
       <c r="K118" s="28">
         <v>6</v>
       </c>
-      <c r="L118" s="84" t="s">
+      <c r="L118" s="80" t="s">
         <v>61</v>
       </c>
       <c r="M118" s="24"/>
@@ -9455,8 +9371,8 @@
       <c r="V118" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W118" s="90" t="s">
-        <v>222</v>
+      <c r="W118" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9487,7 +9403,7 @@
       <c r="K119" s="28">
         <v>7</v>
       </c>
-      <c r="L119" s="84" t="s">
+      <c r="L119" s="80" t="s">
         <v>62</v>
       </c>
       <c r="M119" s="24"/>
@@ -9516,8 +9432,8 @@
       <c r="V119" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W119" s="90" t="s">
-        <v>222</v>
+      <c r="W119" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="120" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9548,7 +9464,7 @@
       <c r="K120" s="28">
         <v>8</v>
       </c>
-      <c r="L120" s="84" t="s">
+      <c r="L120" s="80" t="s">
         <v>63</v>
       </c>
       <c r="M120" s="24"/>
@@ -9577,8 +9493,8 @@
       <c r="V120" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W120" s="90" t="s">
-        <v>222</v>
+      <c r="W120" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="121" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9636,8 +9552,8 @@
       <c r="V121" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W121" s="89" t="s">
-        <v>222</v>
+      <c r="W121" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="122" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9695,8 +9611,8 @@
       <c r="V122" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W122" s="89" t="s">
-        <v>222</v>
+      <c r="W122" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="123" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9754,8 +9670,8 @@
       <c r="V123" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W123" s="89" t="s">
-        <v>222</v>
+      <c r="W123" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="124" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9813,8 +9729,8 @@
       <c r="V124" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W124" s="89" t="s">
-        <v>222</v>
+      <c r="W124" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="125" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9872,8 +9788,8 @@
       <c r="V125" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W125" s="89" t="s">
-        <v>222</v>
+      <c r="W125" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="126" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9931,8 +9847,8 @@
       <c r="V126" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W126" s="89" t="s">
-        <v>222</v>
+      <c r="W126" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="127" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9990,8 +9906,8 @@
       <c r="V127" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W127" s="89" t="s">
-        <v>222</v>
+      <c r="W127" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="128" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10049,8 +9965,8 @@
       <c r="V128" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W128" s="89" t="s">
-        <v>222</v>
+      <c r="W128" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="129" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10108,8 +10024,8 @@
       <c r="V129" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W129" s="89" t="s">
-        <v>222</v>
+      <c r="W129" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="130" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10167,8 +10083,8 @@
       <c r="V130" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W130" s="89" t="s">
-        <v>222</v>
+      <c r="W130" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="131" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10226,8 +10142,8 @@
       <c r="V131" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W131" s="89" t="s">
-        <v>222</v>
+      <c r="W131" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="132" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10285,8 +10201,8 @@
       <c r="V132" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W132" s="89" t="s">
-        <v>222</v>
+      <c r="W132" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="133" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10344,8 +10260,8 @@
       <c r="V133" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W133" s="89" t="s">
-        <v>222</v>
+      <c r="W133" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="134" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10403,8 +10319,8 @@
       <c r="V134" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W134" s="89" t="s">
-        <v>222</v>
+      <c r="W134" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="135" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10462,8 +10378,8 @@
       <c r="V135" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W135" s="89" t="s">
-        <v>222</v>
+      <c r="W135" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="136" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10521,8 +10437,8 @@
       <c r="V136" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W136" s="89" t="s">
-        <v>222</v>
+      <c r="W136" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="137" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10580,8 +10496,8 @@
       <c r="V137" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W137" s="89" t="s">
-        <v>222</v>
+      <c r="W137" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="138" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10639,8 +10555,8 @@
       <c r="V138" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W138" s="89" t="s">
-        <v>222</v>
+      <c r="W138" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="139" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10698,8 +10614,8 @@
       <c r="V139" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W139" s="89" t="s">
-        <v>222</v>
+      <c r="W139" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="140" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10757,8 +10673,8 @@
       <c r="V140" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W140" s="89" t="s">
-        <v>222</v>
+      <c r="W140" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="141" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10816,8 +10732,8 @@
       <c r="V141" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W141" s="89" t="s">
-        <v>222</v>
+      <c r="W141" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="142" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10875,8 +10791,8 @@
       <c r="V142" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W142" s="89" t="s">
-        <v>222</v>
+      <c r="W142" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="143" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10934,8 +10850,8 @@
       <c r="V143" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W143" s="89" t="s">
-        <v>222</v>
+      <c r="W143" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="144" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10993,8 +10909,8 @@
       <c r="V144" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W144" s="89" t="s">
-        <v>222</v>
+      <c r="W144" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="145" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11052,8 +10968,8 @@
       <c r="V145" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W145" s="89" t="s">
-        <v>222</v>
+      <c r="W145" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="146" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11111,8 +11027,8 @@
       <c r="V146" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W146" s="89" t="s">
-        <v>222</v>
+      <c r="W146" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="147" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11170,8 +11086,8 @@
       <c r="V147" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W147" s="89" t="s">
-        <v>222</v>
+      <c r="W147" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="148" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11229,8 +11145,8 @@
       <c r="V148" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W148" s="89" t="s">
-        <v>222</v>
+      <c r="W148" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="149" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11288,8 +11204,8 @@
       <c r="V149" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W149" s="89" t="s">
-        <v>222</v>
+      <c r="W149" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="150" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11347,8 +11263,8 @@
       <c r="V150" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W150" s="89" t="s">
-        <v>222</v>
+      <c r="W150" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="151" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11406,8 +11322,8 @@
       <c r="V151" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W151" s="89" t="s">
-        <v>222</v>
+      <c r="W151" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="152" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11465,8 +11381,8 @@
       <c r="V152" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W152" s="89" t="s">
-        <v>222</v>
+      <c r="W152" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="153" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11524,8 +11440,8 @@
       <c r="V153" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W153" s="89" t="s">
-        <v>222</v>
+      <c r="W153" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="154" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11583,8 +11499,8 @@
       <c r="V154" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W154" s="89" t="s">
-        <v>222</v>
+      <c r="W154" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="155" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11642,8 +11558,8 @@
       <c r="V155" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W155" s="89" t="s">
-        <v>222</v>
+      <c r="W155" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="156" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11701,8 +11617,8 @@
       <c r="V156" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W156" s="89" t="s">
-        <v>222</v>
+      <c r="W156" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="157" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11760,8 +11676,8 @@
       <c r="V157" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W157" s="89" t="s">
-        <v>222</v>
+      <c r="W157" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="158" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11819,8 +11735,8 @@
       <c r="V158" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W158" s="89" t="s">
-        <v>222</v>
+      <c r="W158" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="159" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11878,8 +11794,8 @@
       <c r="V159" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W159" s="89" t="s">
-        <v>222</v>
+      <c r="W159" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="160" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11937,8 +11853,8 @@
       <c r="V160" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W160" s="89" t="s">
-        <v>222</v>
+      <c r="W160" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="161" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11996,8 +11912,8 @@
       <c r="V161" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W161" s="89" t="s">
-        <v>222</v>
+      <c r="W161" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12055,8 +11971,8 @@
       <c r="V162" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W162" s="89" t="s">
-        <v>222</v>
+      <c r="W162" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="163" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12114,8 +12030,8 @@
       <c r="V163" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W163" s="89" t="s">
-        <v>222</v>
+      <c r="W163" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="164" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12173,8 +12089,8 @@
       <c r="V164" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W164" s="89" t="s">
-        <v>222</v>
+      <c r="W164" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="165" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12232,8 +12148,8 @@
       <c r="V165" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W165" s="89" t="s">
-        <v>222</v>
+      <c r="W165" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="166" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12291,8 +12207,8 @@
       <c r="V166" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W166" s="89" t="s">
-        <v>222</v>
+      <c r="W166" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="167" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12350,8 +12266,8 @@
       <c r="V167" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W167" s="89" t="s">
-        <v>222</v>
+      <c r="W167" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="168" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12409,8 +12325,8 @@
       <c r="V168" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W168" s="89" t="s">
-        <v>222</v>
+      <c r="W168" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="169" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12468,8 +12384,8 @@
       <c r="V169" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W169" s="89" t="s">
-        <v>222</v>
+      <c r="W169" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="170" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12527,8 +12443,8 @@
       <c r="V170" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W170" s="89" t="s">
-        <v>222</v>
+      <c r="W170" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="171" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12586,8 +12502,8 @@
       <c r="V171" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W171" s="89" t="s">
-        <v>222</v>
+      <c r="W171" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="172" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12645,8 +12561,8 @@
       <c r="V172" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W172" s="89" t="s">
-        <v>222</v>
+      <c r="W172" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="173" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12704,8 +12620,8 @@
       <c r="V173" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W173" s="89" t="s">
-        <v>222</v>
+      <c r="W173" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="174" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12763,8 +12679,8 @@
       <c r="V174" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W174" s="89" t="s">
-        <v>222</v>
+      <c r="W174" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="175" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12795,7 +12711,7 @@
       <c r="K175" s="28">
         <v>1</v>
       </c>
-      <c r="L175" s="85" t="s">
+      <c r="L175" s="81" t="s">
         <v>84</v>
       </c>
       <c r="M175" s="29"/>
@@ -12824,8 +12740,8 @@
       <c r="V175" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W175" s="90" t="s">
-        <v>222</v>
+      <c r="W175" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="176" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12856,7 +12772,7 @@
       <c r="K176" s="28">
         <v>2</v>
       </c>
-      <c r="L176" s="85" t="s">
+      <c r="L176" s="81" t="s">
         <v>85</v>
       </c>
       <c r="M176" s="29"/>
@@ -12885,8 +12801,8 @@
       <c r="V176" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W176" s="90" t="s">
-        <v>222</v>
+      <c r="W176" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="177" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12917,7 +12833,7 @@
       <c r="K177" s="28">
         <v>3</v>
       </c>
-      <c r="L177" s="85" t="s">
+      <c r="L177" s="81" t="s">
         <v>86</v>
       </c>
       <c r="M177" s="29"/>
@@ -12946,8 +12862,8 @@
       <c r="V177" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W177" s="90" t="s">
-        <v>222</v>
+      <c r="W177" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="178" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12978,7 +12894,7 @@
       <c r="K178" s="28">
         <v>4</v>
       </c>
-      <c r="L178" s="85" t="s">
+      <c r="L178" s="81" t="s">
         <v>87</v>
       </c>
       <c r="M178" s="29"/>
@@ -13007,8 +12923,8 @@
       <c r="V178" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W178" s="90" t="s">
-        <v>222</v>
+      <c r="W178" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="179" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13039,7 +12955,7 @@
       <c r="K179" s="28">
         <v>5</v>
       </c>
-      <c r="L179" s="85" t="s">
+      <c r="L179" s="81" t="s">
         <v>88</v>
       </c>
       <c r="M179" s="29"/>
@@ -13068,8 +12984,8 @@
       <c r="V179" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W179" s="90" t="s">
-        <v>222</v>
+      <c r="W179" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="180" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13100,7 +13016,7 @@
       <c r="K180" s="28">
         <v>6</v>
       </c>
-      <c r="L180" s="85" t="s">
+      <c r="L180" s="81" t="s">
         <v>89</v>
       </c>
       <c r="M180" s="29"/>
@@ -13129,8 +13045,8 @@
       <c r="V180" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W180" s="90" t="s">
-        <v>222</v>
+      <c r="W180" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="181" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13188,8 +13104,8 @@
       <c r="V181" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W181" s="89" t="s">
-        <v>222</v>
+      <c r="W181" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="182" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13247,8 +13163,8 @@
       <c r="V182" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W182" s="89" t="s">
-        <v>222</v>
+      <c r="W182" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="183" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13306,8 +13222,8 @@
       <c r="V183" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W183" s="89" t="s">
-        <v>222</v>
+      <c r="W183" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="184" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13365,8 +13281,8 @@
       <c r="V184" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W184" s="89" t="s">
-        <v>222</v>
+      <c r="W184" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="185" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13424,8 +13340,8 @@
       <c r="V185" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W185" s="89" t="s">
-        <v>222</v>
+      <c r="W185" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="186" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13483,8 +13399,8 @@
       <c r="V186" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W186" s="89" t="s">
-        <v>222</v>
+      <c r="W186" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="187" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13542,8 +13458,8 @@
       <c r="V187" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W187" s="89" t="s">
-        <v>222</v>
+      <c r="W187" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="188" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13601,8 +13517,8 @@
       <c r="V188" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W188" s="89" t="s">
-        <v>222</v>
+      <c r="W188" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="189" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13660,8 +13576,8 @@
       <c r="V189" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W189" s="89" t="s">
-        <v>222</v>
+      <c r="W189" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="190" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13719,8 +13635,8 @@
       <c r="V190" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W190" s="89" t="s">
-        <v>222</v>
+      <c r="W190" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="191" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13778,8 +13694,8 @@
       <c r="V191" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W191" s="89" t="s">
-        <v>222</v>
+      <c r="W191" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="192" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13837,8 +13753,8 @@
       <c r="V192" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W192" s="89" t="s">
-        <v>222</v>
+      <c r="W192" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="193" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13896,8 +13812,8 @@
       <c r="V193" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W193" s="89" t="s">
-        <v>222</v>
+      <c r="W193" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="194" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13955,8 +13871,8 @@
       <c r="V194" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W194" s="89" t="s">
-        <v>222</v>
+      <c r="W194" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="195" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14014,8 +13930,8 @@
       <c r="V195" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W195" s="89" t="s">
-        <v>222</v>
+      <c r="W195" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="196" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14073,8 +13989,8 @@
       <c r="V196" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W196" s="89" t="s">
-        <v>222</v>
+      <c r="W196" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="197" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14132,8 +14048,8 @@
       <c r="V197" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W197" s="89" t="s">
-        <v>222</v>
+      <c r="W197" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="198" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14191,8 +14107,8 @@
       <c r="V198" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W198" s="89" t="s">
-        <v>222</v>
+      <c r="W198" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="199" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14250,8 +14166,8 @@
       <c r="V199" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W199" s="89" t="s">
-        <v>222</v>
+      <c r="W199" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="200" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14309,8 +14225,8 @@
       <c r="V200" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W200" s="89" t="s">
-        <v>222</v>
+      <c r="W200" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="201" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14368,8 +14284,8 @@
       <c r="V201" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W201" s="89" t="s">
-        <v>222</v>
+      <c r="W201" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="202" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14427,8 +14343,8 @@
       <c r="V202" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W202" s="89" t="s">
-        <v>222</v>
+      <c r="W202" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="203" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14486,8 +14402,8 @@
       <c r="V203" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W203" s="89" t="s">
-        <v>222</v>
+      <c r="W203" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="204" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14545,8 +14461,8 @@
       <c r="V204" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W204" s="89" t="s">
-        <v>222</v>
+      <c r="W204" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="205" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14604,8 +14520,8 @@
       <c r="V205" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W205" s="89" t="s">
-        <v>222</v>
+      <c r="W205" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="206" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14663,8 +14579,8 @@
       <c r="V206" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W206" s="89" t="s">
-        <v>222</v>
+      <c r="W206" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="207" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14722,8 +14638,8 @@
       <c r="V207" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W207" s="89" t="s">
-        <v>222</v>
+      <c r="W207" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="208" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14781,8 +14697,8 @@
       <c r="V208" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W208" s="89" t="s">
-        <v>222</v>
+      <c r="W208" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="209" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14840,8 +14756,8 @@
       <c r="V209" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W209" s="89" t="s">
-        <v>222</v>
+      <c r="W209" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="210" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14899,8 +14815,8 @@
       <c r="V210" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W210" s="89" t="s">
-        <v>222</v>
+      <c r="W210" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="211" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14958,8 +14874,8 @@
       <c r="V211" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W211" s="89" t="s">
-        <v>222</v>
+      <c r="W211" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="212" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15017,8 +14933,8 @@
       <c r="V212" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W212" s="89" t="s">
-        <v>222</v>
+      <c r="W212" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="213" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15076,8 +14992,8 @@
       <c r="V213" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W213" s="89" t="s">
-        <v>222</v>
+      <c r="W213" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="214" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15135,8 +15051,8 @@
       <c r="V214" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W214" s="89" t="s">
-        <v>222</v>
+      <c r="W214" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="215" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15194,8 +15110,8 @@
       <c r="V215" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W215" s="89" t="s">
-        <v>222</v>
+      <c r="W215" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="216" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15253,8 +15169,8 @@
       <c r="V216" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W216" s="89" t="s">
-        <v>222</v>
+      <c r="W216" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="217" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15312,8 +15228,8 @@
       <c r="V217" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W217" s="89" t="s">
-        <v>222</v>
+      <c r="W217" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="218" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15371,8 +15287,8 @@
       <c r="V218" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W218" s="89" t="s">
-        <v>222</v>
+      <c r="W218" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="219" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15430,8 +15346,8 @@
       <c r="V219" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W219" s="89" t="s">
-        <v>222</v>
+      <c r="W219" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="220" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15489,8 +15405,8 @@
       <c r="V220" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W220" s="89" t="s">
-        <v>222</v>
+      <c r="W220" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="221" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15548,8 +15464,8 @@
       <c r="V221" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W221" s="89" t="s">
-        <v>222</v>
+      <c r="W221" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="222" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15607,8 +15523,8 @@
       <c r="V222" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W222" s="89" t="s">
-        <v>222</v>
+      <c r="W222" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="223" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15666,8 +15582,8 @@
       <c r="V223" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W223" s="89" t="s">
-        <v>222</v>
+      <c r="W223" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="224" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15725,8 +15641,8 @@
       <c r="V224" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W224" s="89" t="s">
-        <v>222</v>
+      <c r="W224" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="225" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15784,8 +15700,8 @@
       <c r="V225" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W225" s="89" t="s">
-        <v>222</v>
+      <c r="W225" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="226" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15843,8 +15759,8 @@
       <c r="V226" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W226" s="90" t="s">
-        <v>222</v>
+      <c r="W226" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="227" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15902,8 +15818,8 @@
       <c r="V227" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W227" s="90" t="s">
-        <v>222</v>
+      <c r="W227" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="228" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15961,8 +15877,8 @@
       <c r="V228" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W228" s="90" t="s">
-        <v>222</v>
+      <c r="W228" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="229" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16020,8 +15936,8 @@
       <c r="V229" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W229" s="90" t="s">
-        <v>222</v>
+      <c r="W229" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="230" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16079,8 +15995,8 @@
       <c r="V230" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W230" s="90" t="s">
-        <v>222</v>
+      <c r="W230" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="231" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16138,8 +16054,8 @@
       <c r="V231" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W231" s="90" t="s">
-        <v>222</v>
+      <c r="W231" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="232" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16197,8 +16113,8 @@
       <c r="V232" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W232" s="90" t="s">
-        <v>222</v>
+      <c r="W232" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="233" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16256,8 +16172,8 @@
       <c r="V233" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W233" s="90" t="s">
-        <v>222</v>
+      <c r="W233" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="234" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16315,8 +16231,8 @@
       <c r="V234" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W234" s="90" t="s">
-        <v>222</v>
+      <c r="W234" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="235" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16374,8 +16290,8 @@
       <c r="V235" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W235" s="90" t="s">
-        <v>222</v>
+      <c r="W235" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="236" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16433,8 +16349,8 @@
       <c r="V236" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W236" s="90" t="s">
-        <v>222</v>
+      <c r="W236" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="237" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16492,8 +16408,8 @@
       <c r="V237" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W237" s="90" t="s">
-        <v>222</v>
+      <c r="W237" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="238" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16551,8 +16467,8 @@
       <c r="V238" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W238" s="90" t="s">
-        <v>222</v>
+      <c r="W238" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="239" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16610,8 +16526,8 @@
       <c r="V239" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W239" s="90" t="s">
-        <v>222</v>
+      <c r="W239" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="240" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16669,8 +16585,8 @@
       <c r="V240" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W240" s="90" t="s">
-        <v>222</v>
+      <c r="W240" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="241" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16728,8 +16644,8 @@
       <c r="V241" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W241" s="90" t="s">
-        <v>222</v>
+      <c r="W241" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="242" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16787,8 +16703,8 @@
       <c r="V242" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W242" s="90" t="s">
-        <v>222</v>
+      <c r="W242" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="243" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16846,8 +16762,8 @@
       <c r="V243" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W243" s="90" t="s">
-        <v>222</v>
+      <c r="W243" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="244" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16905,8 +16821,8 @@
       <c r="V244" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W244" s="90" t="s">
-        <v>222</v>
+      <c r="W244" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="245" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16964,8 +16880,8 @@
       <c r="V245" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W245" s="90" t="s">
-        <v>222</v>
+      <c r="W245" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="246" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17023,8 +16939,8 @@
       <c r="V246" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W246" s="90" t="s">
-        <v>222</v>
+      <c r="W246" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="247" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17082,8 +16998,8 @@
       <c r="V247" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W247" s="90" t="s">
-        <v>222</v>
+      <c r="W247" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="248" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17141,8 +17057,8 @@
       <c r="V248" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W248" s="90" t="s">
-        <v>222</v>
+      <c r="W248" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="249" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17200,8 +17116,8 @@
       <c r="V249" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W249" s="90" t="s">
-        <v>222</v>
+      <c r="W249" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="250" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17259,8 +17175,8 @@
       <c r="V250" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W250" s="90" t="s">
-        <v>222</v>
+      <c r="W250" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="251" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17318,8 +17234,8 @@
       <c r="V251" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W251" s="89" t="s">
-        <v>222</v>
+      <c r="W251" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="252" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17377,8 +17293,8 @@
       <c r="V252" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W252" s="89" t="s">
-        <v>222</v>
+      <c r="W252" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="253" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17436,8 +17352,8 @@
       <c r="V253" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W253" s="89" t="s">
-        <v>222</v>
+      <c r="W253" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="254" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17495,8 +17411,8 @@
       <c r="V254" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W254" s="89" t="s">
-        <v>222</v>
+      <c r="W254" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="255" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17554,8 +17470,8 @@
       <c r="V255" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W255" s="89" t="s">
-        <v>222</v>
+      <c r="W255" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="256" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17613,8 +17529,8 @@
       <c r="V256" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W256" s="89" t="s">
-        <v>222</v>
+      <c r="W256" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="257" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17672,8 +17588,8 @@
       <c r="V257" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W257" s="89" t="s">
-        <v>222</v>
+      <c r="W257" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="258" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17731,8 +17647,8 @@
       <c r="V258" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W258" s="89" t="s">
-        <v>222</v>
+      <c r="W258" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="259" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17790,8 +17706,8 @@
       <c r="V259" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W259" s="90" t="s">
-        <v>222</v>
+      <c r="W259" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="260" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17849,8 +17765,8 @@
       <c r="V260" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W260" s="90" t="s">
-        <v>222</v>
+      <c r="W260" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="261" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17908,8 +17824,8 @@
       <c r="V261" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W261" s="90" t="s">
-        <v>222</v>
+      <c r="W261" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="262" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -17967,8 +17883,8 @@
       <c r="V262" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W262" s="90" t="s">
-        <v>222</v>
+      <c r="W262" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="263" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18026,8 +17942,8 @@
       <c r="V263" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W263" s="90" t="s">
-        <v>222</v>
+      <c r="W263" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="264" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18085,8 +18001,8 @@
       <c r="V264" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W264" s="90" t="s">
-        <v>222</v>
+      <c r="W264" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="265" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18144,8 +18060,8 @@
       <c r="V265" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W265" s="90" t="s">
-        <v>222</v>
+      <c r="W265" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="266" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18203,8 +18119,8 @@
       <c r="V266" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W266" s="89" t="s">
-        <v>222</v>
+      <c r="W266" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="267" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18262,8 +18178,8 @@
       <c r="V267" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W267" s="89" t="s">
-        <v>222</v>
+      <c r="W267" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="268" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18321,8 +18237,8 @@
       <c r="V268" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W268" s="89" t="s">
-        <v>222</v>
+      <c r="W268" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="269" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18380,8 +18296,8 @@
       <c r="V269" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W269" s="89" t="s">
-        <v>222</v>
+      <c r="W269" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="270" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18439,8 +18355,8 @@
       <c r="V270" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W270" s="89" t="s">
-        <v>222</v>
+      <c r="W270" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="271" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18498,8 +18414,8 @@
       <c r="V271" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W271" s="89" t="s">
-        <v>222</v>
+      <c r="W271" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="272" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18557,8 +18473,8 @@
       <c r="V272" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W272" s="89" t="s">
-        <v>222</v>
+      <c r="W272" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="273" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18616,8 +18532,8 @@
       <c r="V273" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W273" s="89" t="s">
-        <v>222</v>
+      <c r="W273" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="274" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18650,7 +18566,7 @@
         <v>120</v>
       </c>
       <c r="K274" s="28"/>
-      <c r="L274" s="85"/>
+      <c r="L274" s="81"/>
       <c r="M274" s="29" t="s">
         <v>127</v>
       </c>
@@ -18679,8 +18595,8 @@
       <c r="V274" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W274" s="90" t="s">
-        <v>223</v>
+      <c r="W274" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="275" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18713,7 +18629,7 @@
         <v>121</v>
       </c>
       <c r="K275" s="28"/>
-      <c r="L275" s="85"/>
+      <c r="L275" s="81"/>
       <c r="M275" s="29" t="s">
         <v>127</v>
       </c>
@@ -18742,8 +18658,8 @@
       <c r="V275" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W275" s="90" t="s">
-        <v>223</v>
+      <c r="W275" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="276" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18776,7 +18692,7 @@
         <v>122</v>
       </c>
       <c r="K276" s="28"/>
-      <c r="L276" s="85"/>
+      <c r="L276" s="81"/>
       <c r="M276" s="29" t="s">
         <v>127</v>
       </c>
@@ -18805,8 +18721,8 @@
       <c r="V276" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W276" s="90" t="s">
-        <v>223</v>
+      <c r="W276" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="277" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18839,7 +18755,7 @@
         <v>94</v>
       </c>
       <c r="K277" s="28"/>
-      <c r="L277" s="85"/>
+      <c r="L277" s="81"/>
       <c r="M277" s="29" t="s">
         <v>127</v>
       </c>
@@ -18868,8 +18784,8 @@
       <c r="V277" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W277" s="90" t="s">
-        <v>223</v>
+      <c r="W277" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="278" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18902,7 +18818,7 @@
         <v>123</v>
       </c>
       <c r="K278" s="28"/>
-      <c r="L278" s="85"/>
+      <c r="L278" s="81"/>
       <c r="M278" s="29" t="s">
         <v>127</v>
       </c>
@@ -18931,8 +18847,8 @@
       <c r="V278" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W278" s="90" t="s">
-        <v>223</v>
+      <c r="W278" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="279" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -18965,7 +18881,7 @@
         <v>124</v>
       </c>
       <c r="K279" s="28"/>
-      <c r="L279" s="85"/>
+      <c r="L279" s="81"/>
       <c r="M279" s="29" t="s">
         <v>127</v>
       </c>
@@ -18994,8 +18910,8 @@
       <c r="V279" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W279" s="90" t="s">
-        <v>223</v>
+      <c r="W279" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="280" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19028,7 +18944,7 @@
         <v>125</v>
       </c>
       <c r="K280" s="28"/>
-      <c r="L280" s="85"/>
+      <c r="L280" s="81"/>
       <c r="M280" s="29" t="s">
         <v>127</v>
       </c>
@@ -19057,8 +18973,8 @@
       <c r="V280" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W280" s="90" t="s">
-        <v>223</v>
+      <c r="W280" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="281" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19118,8 +19034,8 @@
       <c r="V281" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W281" s="89" t="s">
-        <v>223</v>
+      <c r="W281" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="282" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19179,8 +19095,8 @@
       <c r="V282" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W282" s="89" t="s">
-        <v>223</v>
+      <c r="W282" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="283" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19240,8 +19156,8 @@
       <c r="V283" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W283" s="89" t="s">
-        <v>223</v>
+      <c r="W283" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="284" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19301,8 +19217,8 @@
       <c r="V284" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W284" s="89" t="s">
-        <v>223</v>
+      <c r="W284" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="285" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19362,8 +19278,8 @@
       <c r="V285" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W285" s="89" t="s">
-        <v>223</v>
+      <c r="W285" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="286" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19423,8 +19339,8 @@
       <c r="V286" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W286" s="89" t="s">
-        <v>223</v>
+      <c r="W286" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="287" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19484,8 +19400,8 @@
       <c r="V287" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W287" s="90" t="s">
-        <v>223</v>
+      <c r="W287" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="288" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19545,8 +19461,8 @@
       <c r="V288" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W288" s="90" t="s">
-        <v>223</v>
+      <c r="W288" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="289" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19606,8 +19522,8 @@
       <c r="V289" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W289" s="90" t="s">
-        <v>223</v>
+      <c r="W289" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="290" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19667,8 +19583,8 @@
       <c r="V290" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W290" s="90" t="s">
-        <v>223</v>
+      <c r="W290" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="291" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19728,8 +19644,8 @@
       <c r="V291" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W291" s="90" t="s">
-        <v>223</v>
+      <c r="W291" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="292" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19789,8 +19705,8 @@
       <c r="V292" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W292" s="90" t="s">
-        <v>223</v>
+      <c r="W292" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="293" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19850,8 +19766,8 @@
       <c r="V293" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W293" s="89" t="s">
-        <v>223</v>
+      <c r="W293" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="294" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19911,8 +19827,8 @@
       <c r="V294" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W294" s="89" t="s">
-        <v>223</v>
+      <c r="W294" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="295" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -19972,8 +19888,8 @@
       <c r="V295" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W295" s="89" t="s">
-        <v>223</v>
+      <c r="W295" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="296" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20033,8 +19949,8 @@
       <c r="V296" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W296" s="89" t="s">
-        <v>223</v>
+      <c r="W296" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="297" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20092,8 +20008,8 @@
       <c r="V297" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W297" s="90" t="s">
-        <v>223</v>
+      <c r="W297" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="298" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20151,8 +20067,8 @@
       <c r="V298" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W298" s="90" t="s">
-        <v>223</v>
+      <c r="W298" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="299" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20210,8 +20126,8 @@
       <c r="V299" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W299" s="90" t="s">
-        <v>223</v>
+      <c r="W299" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="300" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20269,8 +20185,8 @@
       <c r="V300" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W300" s="90" t="s">
-        <v>223</v>
+      <c r="W300" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="301" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20328,8 +20244,8 @@
       <c r="V301" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W301" s="90" t="s">
-        <v>223</v>
+      <c r="W301" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="302" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20387,8 +20303,8 @@
       <c r="V302" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W302" s="90" t="s">
-        <v>223</v>
+      <c r="W302" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="303" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20446,8 +20362,8 @@
       <c r="V303" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W303" s="90" t="s">
-        <v>223</v>
+      <c r="W303" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="304" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20507,8 +20423,8 @@
       <c r="V304" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W304" s="89" t="s">
-        <v>223</v>
+      <c r="W304" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="305" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20568,8 +20484,8 @@
       <c r="V305" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W305" s="89" t="s">
-        <v>223</v>
+      <c r="W305" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="306" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20629,8 +20545,8 @@
       <c r="V306" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W306" s="89" t="s">
-        <v>223</v>
+      <c r="W306" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="307" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20690,8 +20606,8 @@
       <c r="V307" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W307" s="89" t="s">
-        <v>223</v>
+      <c r="W307" s="84" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="308" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20749,8 +20665,8 @@
       <c r="V308" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W308" s="90" t="s">
-        <v>223</v>
+      <c r="W308" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="309" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20808,8 +20724,8 @@
       <c r="V309" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W309" s="90" t="s">
-        <v>223</v>
+      <c r="W309" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="310" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20867,8 +20783,8 @@
       <c r="V310" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W310" s="90" t="s">
-        <v>223</v>
+      <c r="W310" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="311" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20926,8 +20842,8 @@
       <c r="V311" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W311" s="90" t="s">
-        <v>223</v>
+      <c r="W311" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="312" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -20985,8 +20901,8 @@
       <c r="V312" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W312" s="90" t="s">
-        <v>223</v>
+      <c r="W312" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="313" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21044,8 +20960,8 @@
       <c r="V313" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W313" s="90" t="s">
-        <v>223</v>
+      <c r="W313" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="314" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21103,8 +21019,8 @@
       <c r="V314" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W314" s="90" t="s">
-        <v>223</v>
+      <c r="W314" s="85" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="315" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21162,8 +21078,8 @@
       <c r="V315" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W315" s="89" t="s">
-        <v>222</v>
+      <c r="W315" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="316" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21221,8 +21137,8 @@
       <c r="V316" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W316" s="89" t="s">
-        <v>222</v>
+      <c r="W316" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="317" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21280,8 +21196,8 @@
       <c r="V317" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W317" s="89" t="s">
-        <v>222</v>
+      <c r="W317" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="318" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21339,8 +21255,8 @@
       <c r="V318" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W318" s="89" t="s">
-        <v>222</v>
+      <c r="W318" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="319" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21398,8 +21314,8 @@
       <c r="V319" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W319" s="89" t="s">
-        <v>222</v>
+      <c r="W319" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="320" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21457,8 +21373,8 @@
       <c r="V320" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W320" s="89" t="s">
-        <v>222</v>
+      <c r="W320" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="321" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21516,8 +21432,8 @@
       <c r="V321" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W321" s="89" t="s">
-        <v>222</v>
+      <c r="W321" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="322" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21575,8 +21491,8 @@
       <c r="V322" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W322" s="89" t="s">
-        <v>222</v>
+      <c r="W322" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="323" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21634,8 +21550,8 @@
       <c r="V323" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W323" s="89" t="s">
-        <v>222</v>
+      <c r="W323" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="324" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21693,8 +21609,8 @@
       <c r="V324" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W324" s="89" t="s">
-        <v>222</v>
+      <c r="W324" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="325" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21752,8 +21668,8 @@
       <c r="V325" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W325" s="89" t="s">
-        <v>222</v>
+      <c r="W325" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="326" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21811,8 +21727,8 @@
       <c r="V326" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W326" s="89" t="s">
-        <v>222</v>
+      <c r="W326" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="327" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21870,8 +21786,8 @@
       <c r="V327" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W327" s="89" t="s">
-        <v>222</v>
+      <c r="W327" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="328" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21929,8 +21845,8 @@
       <c r="V328" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W328" s="89" t="s">
-        <v>222</v>
+      <c r="W328" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="329" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -21988,8 +21904,8 @@
       <c r="V329" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W329" s="89" t="s">
-        <v>222</v>
+      <c r="W329" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="330" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22047,8 +21963,8 @@
       <c r="V330" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W330" s="89" t="s">
-        <v>222</v>
+      <c r="W330" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="331" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22106,8 +22022,8 @@
       <c r="V331" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W331" s="89" t="s">
-        <v>222</v>
+      <c r="W331" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="332" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22165,8 +22081,8 @@
       <c r="V332" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W332" s="89" t="s">
-        <v>222</v>
+      <c r="W332" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="333" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22224,8 +22140,8 @@
       <c r="V333" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W333" s="89" t="s">
-        <v>222</v>
+      <c r="W333" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="334" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22283,8 +22199,8 @@
       <c r="V334" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W334" s="89" t="s">
-        <v>222</v>
+      <c r="W334" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="335" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22344,8 +22260,8 @@
       <c r="V335" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W335" s="90" t="s">
-        <v>222</v>
+      <c r="W335" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="336" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22405,8 +22321,8 @@
       <c r="V336" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W336" s="90" t="s">
-        <v>222</v>
+      <c r="W336" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="337" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22466,8 +22382,8 @@
       <c r="V337" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W337" s="90" t="s">
-        <v>222</v>
+      <c r="W337" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="338" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22527,8 +22443,8 @@
       <c r="V338" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W338" s="90" t="s">
-        <v>222</v>
+      <c r="W338" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="339" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22588,8 +22504,8 @@
       <c r="V339" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W339" s="90" t="s">
-        <v>222</v>
+      <c r="W339" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="340" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22649,8 +22565,8 @@
       <c r="V340" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W340" s="89" t="s">
-        <v>222</v>
+      <c r="W340" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="341" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22710,8 +22626,8 @@
       <c r="V341" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W341" s="89" t="s">
-        <v>222</v>
+      <c r="W341" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="342" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22771,8 +22687,8 @@
       <c r="V342" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W342" s="89" t="s">
-        <v>222</v>
+      <c r="W342" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="343" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22832,8 +22748,8 @@
       <c r="V343" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W343" s="89" t="s">
-        <v>222</v>
+      <c r="W343" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="344" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22893,8 +22809,8 @@
       <c r="V344" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W344" s="89" t="s">
-        <v>222</v>
+      <c r="W344" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="345" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -22954,8 +22870,8 @@
       <c r="V345" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W345" s="90" t="s">
-        <v>222</v>
+      <c r="W345" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="346" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23015,8 +22931,8 @@
       <c r="V346" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W346" s="90" t="s">
-        <v>222</v>
+      <c r="W346" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="347" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23076,8 +22992,8 @@
       <c r="V347" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W347" s="90" t="s">
-        <v>222</v>
+      <c r="W347" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="348" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23137,8 +23053,8 @@
       <c r="V348" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W348" s="90" t="s">
-        <v>222</v>
+      <c r="W348" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="349" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23198,8 +23114,8 @@
       <c r="V349" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W349" s="90" t="s">
-        <v>222</v>
+      <c r="W349" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="350" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23259,8 +23175,8 @@
       <c r="V350" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W350" s="89" t="s">
-        <v>222</v>
+      <c r="W350" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="351" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23320,8 +23236,8 @@
       <c r="V351" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W351" s="89" t="s">
-        <v>222</v>
+      <c r="W351" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="352" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23381,8 +23297,8 @@
       <c r="V352" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W352" s="89" t="s">
-        <v>222</v>
+      <c r="W352" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="353" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23442,8 +23358,8 @@
       <c r="V353" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W353" s="89" t="s">
-        <v>222</v>
+      <c r="W353" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="354" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23503,8 +23419,8 @@
       <c r="V354" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W354" s="89" t="s">
-        <v>222</v>
+      <c r="W354" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="355" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23535,7 +23451,7 @@
       <c r="K355" s="28">
         <v>1</v>
       </c>
-      <c r="L355" s="86">
+      <c r="L355" s="82">
         <v>39356</v>
       </c>
       <c r="M355" s="27"/>
@@ -23564,8 +23480,8 @@
       <c r="V355" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W355" s="90" t="s">
-        <v>222</v>
+      <c r="W355" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="356" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23596,7 +23512,7 @@
       <c r="K356" s="28">
         <v>2</v>
       </c>
-      <c r="L356" s="86">
+      <c r="L356" s="82">
         <v>39539</v>
       </c>
       <c r="M356" s="27"/>
@@ -23625,8 +23541,8 @@
       <c r="V356" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W356" s="90" t="s">
-        <v>222</v>
+      <c r="W356" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="357" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23657,7 +23573,7 @@
       <c r="K357" s="28">
         <v>3</v>
       </c>
-      <c r="L357" s="86">
+      <c r="L357" s="82">
         <v>39630</v>
       </c>
       <c r="M357" s="27"/>
@@ -23686,8 +23602,8 @@
       <c r="V357" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W357" s="90" t="s">
-        <v>222</v>
+      <c r="W357" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="358" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23718,7 +23634,7 @@
       <c r="K358" s="28">
         <v>4</v>
       </c>
-      <c r="L358" s="86">
+      <c r="L358" s="82">
         <v>39722</v>
       </c>
       <c r="M358" s="27"/>
@@ -23747,8 +23663,8 @@
       <c r="V358" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W358" s="90" t="s">
-        <v>222</v>
+      <c r="W358" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="359" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23779,7 +23695,7 @@
       <c r="K359" s="28">
         <v>5</v>
       </c>
-      <c r="L359" s="86">
+      <c r="L359" s="82">
         <v>39873</v>
       </c>
       <c r="M359" s="27"/>
@@ -23808,8 +23724,8 @@
       <c r="V359" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W359" s="90" t="s">
-        <v>222</v>
+      <c r="W359" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="360" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23840,7 +23756,7 @@
       <c r="K360" s="28">
         <v>6</v>
       </c>
-      <c r="L360" s="86">
+      <c r="L360" s="82">
         <v>39965</v>
       </c>
       <c r="M360" s="27"/>
@@ -23869,8 +23785,8 @@
       <c r="V360" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W360" s="90" t="s">
-        <v>222</v>
+      <c r="W360" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="361" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23901,7 +23817,7 @@
       <c r="K361" s="28">
         <v>7</v>
       </c>
-      <c r="L361" s="86">
+      <c r="L361" s="82">
         <v>40057</v>
       </c>
       <c r="M361" s="27"/>
@@ -23930,8 +23846,8 @@
       <c r="V361" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W361" s="90" t="s">
-        <v>222</v>
+      <c r="W361" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="362" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -23962,7 +23878,7 @@
       <c r="K362" s="28">
         <v>8</v>
       </c>
-      <c r="L362" s="86">
+      <c r="L362" s="82">
         <v>40210</v>
       </c>
       <c r="M362" s="27"/>
@@ -23991,8 +23907,8 @@
       <c r="V362" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W362" s="90" t="s">
-        <v>222</v>
+      <c r="W362" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="363" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24023,7 +23939,7 @@
       <c r="K363" s="28">
         <v>9</v>
       </c>
-      <c r="L363" s="86">
+      <c r="L363" s="82">
         <v>40299</v>
       </c>
       <c r="M363" s="27"/>
@@ -24052,8 +23968,8 @@
       <c r="V363" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="W363" s="90" t="s">
-        <v>222</v>
+      <c r="W363" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="364" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24111,8 +24027,8 @@
       <c r="V364" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="W364" s="89" t="s">
-        <v>222</v>
+      <c r="W364" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="365" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24170,8 +24086,8 @@
       <c r="V365" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="W365" s="89" t="s">
-        <v>222</v>
+      <c r="W365" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="366" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24229,8 +24145,8 @@
       <c r="V366" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="W366" s="89" t="s">
-        <v>222</v>
+      <c r="W366" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="367" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24288,8 +24204,8 @@
       <c r="V367" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="W367" s="89" t="s">
-        <v>222</v>
+      <c r="W367" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="368" spans="1:23" s="60" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24347,8 +24263,8 @@
       <c r="V368" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="W368" s="89" t="s">
-        <v>222</v>
+      <c r="W368" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="369" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24406,8 +24322,8 @@
       <c r="V369" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="W369" s="89" t="s">
-        <v>222</v>
+      <c r="W369" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="370" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24438,7 +24354,7 @@
       <c r="K370" s="28">
         <v>1</v>
       </c>
-      <c r="L370" s="86">
+      <c r="L370" s="82">
         <v>36678</v>
       </c>
       <c r="M370" s="27"/>
@@ -24467,8 +24383,8 @@
       <c r="V370" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W370" s="90" t="s">
-        <v>222</v>
+      <c r="W370" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="371" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24499,7 +24415,7 @@
       <c r="K371" s="28">
         <v>2</v>
       </c>
-      <c r="L371" s="86">
+      <c r="L371" s="82">
         <v>36800</v>
       </c>
       <c r="M371" s="27"/>
@@ -24528,8 +24444,8 @@
       <c r="V371" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W371" s="90" t="s">
-        <v>222</v>
+      <c r="W371" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="372" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24560,7 +24476,7 @@
       <c r="K372" s="28">
         <v>3</v>
       </c>
-      <c r="L372" s="86">
+      <c r="L372" s="82">
         <v>37043</v>
       </c>
       <c r="M372" s="27"/>
@@ -24589,8 +24505,8 @@
       <c r="V372" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W372" s="90" t="s">
-        <v>222</v>
+      <c r="W372" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="373" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24621,7 +24537,7 @@
       <c r="K373" s="28">
         <v>4</v>
       </c>
-      <c r="L373" s="86">
+      <c r="L373" s="82">
         <v>37104</v>
       </c>
       <c r="M373" s="27"/>
@@ -24650,8 +24566,8 @@
       <c r="V373" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W373" s="90" t="s">
-        <v>222</v>
+      <c r="W373" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="374" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24682,7 +24598,7 @@
       <c r="K374" s="28">
         <v>5</v>
       </c>
-      <c r="L374" s="86">
+      <c r="L374" s="82">
         <v>37316</v>
       </c>
       <c r="M374" s="27"/>
@@ -24711,8 +24627,8 @@
       <c r="V374" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W374" s="90" t="s">
-        <v>222</v>
+      <c r="W374" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="375" spans="1:23" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24743,7 +24659,7 @@
       <c r="K375" s="28">
         <v>6</v>
       </c>
-      <c r="L375" s="86">
+      <c r="L375" s="82">
         <v>37408</v>
       </c>
       <c r="M375" s="27"/>
@@ -24772,8 +24688,8 @@
       <c r="V375" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="W375" s="90" t="s">
-        <v>222</v>
+      <c r="W375" s="85" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="376" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24833,8 +24749,8 @@
       <c r="V376" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W376" s="89" t="s">
-        <v>222</v>
+      <c r="W376" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="377" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24894,8 +24810,8 @@
       <c r="V377" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W377" s="89" t="s">
-        <v>222</v>
+      <c r="W377" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="378" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -24955,8 +24871,8 @@
       <c r="V378" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W378" s="89" t="s">
-        <v>222</v>
+      <c r="W378" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="379" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25016,8 +24932,8 @@
       <c r="V379" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W379" s="89" t="s">
-        <v>222</v>
+      <c r="W379" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="380" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25077,8 +24993,8 @@
       <c r="V380" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W380" s="89" t="s">
-        <v>222</v>
+      <c r="W380" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="381" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25138,8 +25054,8 @@
       <c r="V381" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W381" s="89" t="s">
-        <v>222</v>
+      <c r="W381" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="382" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25199,8 +25115,8 @@
       <c r="V382" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W382" s="89" t="s">
-        <v>222</v>
+      <c r="W382" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="383" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25260,8 +25176,8 @@
       <c r="V383" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W383" s="89" t="s">
-        <v>222</v>
+      <c r="W383" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="384" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25321,8 +25237,8 @@
       <c r="V384" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W384" s="89" t="s">
-        <v>222</v>
+      <c r="W384" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="385" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25382,8 +25298,8 @@
       <c r="V385" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W385" s="89" t="s">
-        <v>222</v>
+      <c r="W385" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="386" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25443,8 +25359,8 @@
       <c r="V386" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W386" s="89" t="s">
-        <v>222</v>
+      <c r="W386" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="387" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25504,8 +25420,8 @@
       <c r="V387" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W387" s="89" t="s">
-        <v>222</v>
+      <c r="W387" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="388" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25565,8 +25481,8 @@
       <c r="V388" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W388" s="89" t="s">
-        <v>222</v>
+      <c r="W388" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="389" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25626,8 +25542,8 @@
       <c r="V389" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W389" s="89" t="s">
-        <v>222</v>
+      <c r="W389" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="390" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25687,8 +25603,8 @@
       <c r="V390" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W390" s="89" t="s">
-        <v>222</v>
+      <c r="W390" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="391" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25748,8 +25664,8 @@
       <c r="V391" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W391" s="89" t="s">
-        <v>222</v>
+      <c r="W391" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="392" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25809,8 +25725,8 @@
       <c r="V392" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W392" s="89" t="s">
-        <v>222</v>
+      <c r="W392" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="393" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25870,8 +25786,8 @@
       <c r="V393" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W393" s="89" t="s">
-        <v>222</v>
+      <c r="W393" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="394" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25931,8 +25847,8 @@
       <c r="V394" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W394" s="89" t="s">
-        <v>222</v>
+      <c r="W394" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="395" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -25992,8 +25908,8 @@
       <c r="V395" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W395" s="89" t="s">
-        <v>222</v>
+      <c r="W395" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="396" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26053,8 +25969,8 @@
       <c r="V396" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W396" s="89" t="s">
-        <v>222</v>
+      <c r="W396" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="397" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26114,8 +26030,8 @@
       <c r="V397" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W397" s="89" t="s">
-        <v>222</v>
+      <c r="W397" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="398" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26175,8 +26091,8 @@
       <c r="V398" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W398" s="89" t="s">
-        <v>222</v>
+      <c r="W398" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="399" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26236,8 +26152,8 @@
       <c r="V399" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W399" s="89" t="s">
-        <v>222</v>
+      <c r="W399" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="400" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26297,8 +26213,8 @@
       <c r="V400" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W400" s="89" t="s">
-        <v>222</v>
+      <c r="W400" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="401" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26358,8 +26274,8 @@
       <c r="V401" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W401" s="89" t="s">
-        <v>222</v>
+      <c r="W401" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="402" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26419,8 +26335,8 @@
       <c r="V402" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W402" s="89" t="s">
-        <v>222</v>
+      <c r="W402" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="403" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26480,8 +26396,8 @@
       <c r="V403" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W403" s="89" t="s">
-        <v>222</v>
+      <c r="W403" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="404" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26541,8 +26457,8 @@
       <c r="V404" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W404" s="89" t="s">
-        <v>222</v>
+      <c r="W404" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="405" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26602,8 +26518,8 @@
       <c r="V405" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W405" s="89" t="s">
-        <v>222</v>
+      <c r="W405" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="406" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26663,8 +26579,8 @@
       <c r="V406" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W406" s="89" t="s">
-        <v>222</v>
+      <c r="W406" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="407" spans="1:23" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26724,8 +26640,8 @@
       <c r="V407" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W407" s="89" t="s">
-        <v>222</v>
+      <c r="W407" s="84" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="408" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26786,7 +26702,7 @@
         <v>197</v>
       </c>
       <c r="W408" s="55" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
     </row>
     <row r="409" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26847,7 +26763,7 @@
         <v>197</v>
       </c>
       <c r="W409" s="55" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
     </row>
     <row r="410" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26908,7 +26824,7 @@
         <v>197</v>
       </c>
       <c r="W410" s="55" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
     </row>
     <row r="411" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -26969,7 +26885,7 @@
         <v>197</v>
       </c>
       <c r="W411" s="55" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
     </row>
     <row r="412" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27032,7 +26948,7 @@
         <v>197</v>
       </c>
       <c r="W412" s="48" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="413" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27095,7 +27011,7 @@
         <v>197</v>
       </c>
       <c r="W413" s="48" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="414" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27158,7 +27074,7 @@
         <v>197</v>
       </c>
       <c r="W414" s="48" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="415" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27221,7 +27137,7 @@
         <v>197</v>
       </c>
       <c r="W415" s="48" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="416" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27284,7 +27200,7 @@
         <v>197</v>
       </c>
       <c r="W416" s="48" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="417" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27347,7 +27263,7 @@
         <v>197</v>
       </c>
       <c r="W417" s="48" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="418" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27410,7 +27326,7 @@
         <v>197</v>
       </c>
       <c r="W418" s="48" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="419" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27473,7 +27389,7 @@
         <v>197</v>
       </c>
       <c r="W419" s="48" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="420" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27536,7 +27452,7 @@
         <v>197</v>
       </c>
       <c r="W420" s="55" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="421" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27599,7 +27515,7 @@
         <v>197</v>
       </c>
       <c r="W421" s="55" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="422" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27662,7 +27578,7 @@
         <v>197</v>
       </c>
       <c r="W422" s="55" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="423" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27725,7 +27641,7 @@
         <v>197</v>
       </c>
       <c r="W423" s="55" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="424" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27788,7 +27704,7 @@
         <v>197</v>
       </c>
       <c r="W424" s="55" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="425" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27851,7 +27767,7 @@
         <v>197</v>
       </c>
       <c r="W425" s="55" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="426" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27914,7 +27830,7 @@
         <v>197</v>
       </c>
       <c r="W426" s="55" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="427" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -27977,7 +27893,7 @@
         <v>197</v>
       </c>
       <c r="W427" s="55" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="428" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28040,7 +27956,7 @@
         <v>197</v>
       </c>
       <c r="W428" s="48" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="429" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28103,7 +28019,7 @@
         <v>197</v>
       </c>
       <c r="W429" s="48" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="430" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28166,7 +28082,7 @@
         <v>197</v>
       </c>
       <c r="W430" s="48" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="431" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28229,7 +28145,7 @@
         <v>197</v>
       </c>
       <c r="W431" s="48" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
     </row>
     <row r="432" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -28292,10 +28208,10 @@
         <v>197</v>
       </c>
       <c r="W432" s="48" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="433" spans="1:41" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="433" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A433" s="56" t="s">
         <v>200</v>
       </c>
@@ -28355,10 +28271,10 @@
         <v>197</v>
       </c>
       <c r="W433" s="48" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="434" spans="1:41" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="434" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A434" s="56" t="s">
         <v>200</v>
       </c>
@@ -28418,10 +28334,10 @@
         <v>197</v>
       </c>
       <c r="W434" s="48" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="435" spans="1:41" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="435" spans="1:23" s="48" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A435" s="56" t="s">
         <v>200</v>
       </c>
@@ -28481,10 +28397,10 @@
         <v>197</v>
       </c>
       <c r="W435" s="48" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="436" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="436" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A436" s="64" t="s">
         <v>201</v>
       </c>
@@ -28544,10 +28460,10 @@
         <v>197</v>
       </c>
       <c r="W436" s="55" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="437" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="437" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A437" s="64" t="s">
         <v>201</v>
       </c>
@@ -28607,10 +28523,10 @@
         <v>197</v>
       </c>
       <c r="W437" s="55" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="438" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="438" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A438" s="64" t="s">
         <v>201</v>
       </c>
@@ -28670,10 +28586,10 @@
         <v>197</v>
       </c>
       <c r="W438" s="55" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="439" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="439" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A439" s="64" t="s">
         <v>201</v>
       </c>
@@ -28733,10 +28649,10 @@
         <v>197</v>
       </c>
       <c r="W439" s="55" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="440" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="440" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A440" s="64" t="s">
         <v>201</v>
       </c>
@@ -28796,10 +28712,10 @@
         <v>197</v>
       </c>
       <c r="W440" s="55" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="441" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="441" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A441" s="64" t="s">
         <v>201</v>
       </c>
@@ -28859,10 +28775,10 @@
         <v>197</v>
       </c>
       <c r="W441" s="55" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="442" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="442" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A442" s="64" t="s">
         <v>201</v>
       </c>
@@ -28922,10 +28838,10 @@
         <v>197</v>
       </c>
       <c r="W442" s="55" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="443" spans="1:41" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="443" spans="1:23" s="55" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A443" s="64" t="s">
         <v>201</v>
       </c>
@@ -28985,3068 +28901,8 @@
         <v>197</v>
       </c>
       <c r="W443" s="55" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="444" spans="1:41" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A444" s="82" t="s">
-        <v>204</v>
-      </c>
-      <c r="B444" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="C444" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D444" s="11"/>
-      <c r="E444" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="F444" s="18">
-        <v>-46.875459999999997</v>
-      </c>
-      <c r="G444" s="18">
-        <v>37.858539999999998</v>
-      </c>
-      <c r="H444" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="I444" s="14"/>
-      <c r="J444" s="14"/>
-      <c r="K444" s="20">
-        <v>1</v>
-      </c>
-      <c r="L444" s="20">
-        <v>1979.0830000000001</v>
-      </c>
-      <c r="M444" s="83">
-        <v>0</v>
-      </c>
-      <c r="N444" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="O444" s="20">
-        <v>1</v>
-      </c>
-      <c r="P444" s="20"/>
-      <c r="Q444" s="20">
-        <v>0</v>
-      </c>
-      <c r="R444" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="S444" s="41" t="s">
-        <v>210</v>
-      </c>
-      <c r="T444" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="U444" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="V444" s="76" t="s">
-        <v>197</v>
-      </c>
-      <c r="W444" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="X444" s="20"/>
-      <c r="Y444" s="20"/>
-      <c r="Z444" s="20"/>
-      <c r="AA444" s="20"/>
-      <c r="AB444" s="14"/>
-      <c r="AC444" s="14"/>
-      <c r="AD444" s="14"/>
-      <c r="AE444" s="14"/>
-      <c r="AF444" s="14"/>
-      <c r="AG444" s="14"/>
-      <c r="AH444" s="14"/>
-      <c r="AI444" s="14"/>
-      <c r="AJ444" s="14"/>
-      <c r="AK444" s="14"/>
-      <c r="AL444" s="14"/>
-      <c r="AM444" s="14"/>
-      <c r="AN444" s="10"/>
-      <c r="AO444" s="40"/>
-    </row>
-    <row r="445" spans="1:41" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A445" s="82" t="s">
-        <v>204</v>
-      </c>
-      <c r="B445" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="C445" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D445" s="11"/>
-      <c r="E445" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="F445" s="18">
-        <v>-46.875459999999997</v>
-      </c>
-      <c r="G445" s="18">
-        <v>37.858539999999998</v>
-      </c>
-      <c r="H445" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I445" s="14"/>
-      <c r="J445" s="14"/>
-      <c r="K445" s="20">
-        <v>2</v>
-      </c>
-      <c r="L445" s="20">
-        <v>1981.979</v>
-      </c>
-      <c r="M445" s="83">
-        <v>0.47778999999999999</v>
-      </c>
-      <c r="N445" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="O445" s="20">
-        <v>1</v>
-      </c>
-      <c r="P445" s="20"/>
-      <c r="Q445" s="20">
-        <v>47.779000000000003</v>
-      </c>
-      <c r="R445" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="S445" s="41" t="s">
-        <v>210</v>
-      </c>
-      <c r="T445" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="U445" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="V445" s="76" t="s">
-        <v>197</v>
-      </c>
-      <c r="W445" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="X445" s="20"/>
-      <c r="Y445" s="20"/>
-      <c r="Z445" s="20"/>
-      <c r="AA445" s="20"/>
-      <c r="AB445" s="14"/>
-      <c r="AC445" s="14"/>
-      <c r="AD445" s="14"/>
-      <c r="AE445" s="14"/>
-      <c r="AF445" s="14"/>
-      <c r="AG445" s="14"/>
-      <c r="AH445" s="14"/>
-      <c r="AI445" s="14"/>
-      <c r="AJ445" s="14"/>
-      <c r="AK445" s="14"/>
-      <c r="AL445" s="14"/>
-      <c r="AM445" s="14"/>
-      <c r="AN445" s="10"/>
-      <c r="AO445" s="40"/>
-    </row>
-    <row r="446" spans="1:41" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A446" s="82" t="s">
-        <v>204</v>
-      </c>
-      <c r="B446" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="C446" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D446" s="11"/>
-      <c r="E446" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="F446" s="18">
-        <v>-46.875459999999997</v>
-      </c>
-      <c r="G446" s="18">
-        <v>37.858539999999998</v>
-      </c>
-      <c r="H446" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I446" s="14"/>
-      <c r="J446" s="14"/>
-      <c r="K446" s="20">
-        <v>3</v>
-      </c>
-      <c r="L446" s="20">
-        <v>1984.146</v>
-      </c>
-      <c r="M446" s="83">
-        <v>0</v>
-      </c>
-      <c r="N446" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="O446" s="20">
-        <v>1</v>
-      </c>
-      <c r="P446" s="20"/>
-      <c r="Q446" s="20">
-        <v>0</v>
-      </c>
-      <c r="R446" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="S446" s="41" t="s">
-        <v>210</v>
-      </c>
-      <c r="T446" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="U446" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="V446" s="76" t="s">
-        <v>197</v>
-      </c>
-      <c r="W446" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="X446" s="20"/>
-      <c r="Y446" s="20"/>
-      <c r="Z446" s="20"/>
-      <c r="AA446" s="20"/>
-      <c r="AB446" s="14"/>
-      <c r="AC446" s="14"/>
-      <c r="AD446" s="14"/>
-      <c r="AE446" s="14"/>
-      <c r="AF446" s="14"/>
-      <c r="AG446" s="14"/>
-      <c r="AH446" s="14"/>
-      <c r="AI446" s="14"/>
-      <c r="AJ446" s="14"/>
-      <c r="AK446" s="14"/>
-      <c r="AL446" s="14"/>
-      <c r="AM446" s="14"/>
-      <c r="AN446" s="10"/>
-      <c r="AO446" s="40"/>
-    </row>
-    <row r="447" spans="1:41" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A447" s="82" t="s">
-        <v>204</v>
-      </c>
-      <c r="B447" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="C447" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D447" s="11"/>
-      <c r="E447" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="F447" s="18">
-        <v>-46.875459999999997</v>
-      </c>
-      <c r="G447" s="18">
-        <v>37.858539999999998</v>
-      </c>
-      <c r="H447" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I447" s="14"/>
-      <c r="J447" s="14"/>
-      <c r="K447" s="20">
-        <v>4</v>
-      </c>
-      <c r="L447" s="20">
-        <v>2012.146</v>
-      </c>
-      <c r="M447" s="83">
-        <v>0</v>
-      </c>
-      <c r="N447" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="O447" s="20">
-        <v>0</v>
-      </c>
-      <c r="P447" s="20"/>
-      <c r="Q447" s="20">
-        <v>0</v>
-      </c>
-      <c r="R447" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="S447" s="41" t="s">
-        <v>210</v>
-      </c>
-      <c r="T447" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="U447" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="V447" s="76" t="s">
-        <v>197</v>
-      </c>
-      <c r="W447" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="X447" s="20"/>
-      <c r="Y447" s="20"/>
-      <c r="Z447" s="20"/>
-      <c r="AA447" s="20"/>
-      <c r="AB447" s="14"/>
-      <c r="AC447" s="14"/>
-      <c r="AD447" s="14"/>
-      <c r="AE447" s="14"/>
-      <c r="AF447" s="14"/>
-      <c r="AG447" s="14"/>
-      <c r="AH447" s="14"/>
-      <c r="AI447" s="14"/>
-      <c r="AJ447" s="14"/>
-      <c r="AK447" s="14"/>
-      <c r="AL447" s="14"/>
-      <c r="AM447" s="14"/>
-      <c r="AN447" s="10"/>
-      <c r="AO447" s="40"/>
-    </row>
-    <row r="448" spans="1:41" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A448" s="82" t="s">
-        <v>204</v>
-      </c>
-      <c r="B448" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="C448" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D448" s="11"/>
-      <c r="E448" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="F448" s="18">
-        <v>-46.875459999999997</v>
-      </c>
-      <c r="G448" s="18">
-        <v>37.858539999999998</v>
-      </c>
-      <c r="H448" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I448" s="14"/>
-      <c r="J448" s="14"/>
-      <c r="K448" s="20">
-        <v>5</v>
-      </c>
-      <c r="L448" s="20">
-        <v>2013.0619999999999</v>
-      </c>
-      <c r="M448" s="83">
-        <v>0.40926000000000001</v>
-      </c>
-      <c r="N448" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="O448" s="20">
-        <v>0</v>
-      </c>
-      <c r="P448" s="20"/>
-      <c r="Q448" s="20">
-        <v>40.926000000000002</v>
-      </c>
-      <c r="R448" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="S448" s="41" t="s">
-        <v>210</v>
-      </c>
-      <c r="T448" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="U448" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="V448" s="76" t="s">
-        <v>197</v>
-      </c>
-      <c r="W448" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="X448" s="20"/>
-      <c r="Y448" s="20"/>
-      <c r="Z448" s="20"/>
-      <c r="AA448" s="20"/>
-      <c r="AB448" s="14"/>
-      <c r="AC448" s="14"/>
-      <c r="AD448" s="14"/>
-      <c r="AE448" s="14"/>
-      <c r="AF448" s="14"/>
-      <c r="AG448" s="14"/>
-      <c r="AH448" s="14"/>
-      <c r="AI448" s="14"/>
-      <c r="AJ448" s="14"/>
-      <c r="AK448" s="14"/>
-      <c r="AL448" s="14"/>
-      <c r="AM448" s="14"/>
-      <c r="AN448" s="10"/>
-      <c r="AO448" s="40"/>
-    </row>
-    <row r="449" spans="1:41" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A449" s="82" t="s">
-        <v>204</v>
-      </c>
-      <c r="B449" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="C449" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D449" s="11"/>
-      <c r="E449" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="F449" s="18">
-        <v>-46.875459999999997</v>
-      </c>
-      <c r="G449" s="18">
-        <v>37.858539999999998</v>
-      </c>
-      <c r="H449" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I449" s="14"/>
-      <c r="J449" s="14"/>
-      <c r="K449" s="20">
-        <v>6</v>
-      </c>
-      <c r="L449" s="20">
-        <v>2014.0619999999999</v>
-      </c>
-      <c r="M449" s="83">
-        <v>0.2316</v>
-      </c>
-      <c r="N449" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="O449" s="20">
-        <v>0</v>
-      </c>
-      <c r="P449" s="20"/>
-      <c r="Q449" s="20">
-        <v>23.16</v>
-      </c>
-      <c r="R449" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="S449" s="41" t="s">
-        <v>210</v>
-      </c>
-      <c r="T449" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="U449" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="V449" s="76" t="s">
-        <v>197</v>
-      </c>
-      <c r="W449" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="X449" s="20"/>
-      <c r="Y449" s="20"/>
-      <c r="Z449" s="20"/>
-      <c r="AA449" s="20"/>
-      <c r="AB449" s="14"/>
-      <c r="AC449" s="14"/>
-      <c r="AD449" s="14"/>
-      <c r="AE449" s="14"/>
-      <c r="AF449" s="14"/>
-      <c r="AG449" s="14"/>
-      <c r="AH449" s="14"/>
-      <c r="AI449" s="14"/>
-      <c r="AJ449" s="14"/>
-      <c r="AK449" s="14"/>
-      <c r="AL449" s="14"/>
-      <c r="AM449" s="14"/>
-      <c r="AN449" s="10"/>
-      <c r="AO449" s="40"/>
-    </row>
-    <row r="450" spans="1:41" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A450" s="82" t="s">
-        <v>204</v>
-      </c>
-      <c r="B450" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="C450" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D450" s="11"/>
-      <c r="E450" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="F450" s="18">
-        <v>-46.875459999999997</v>
-      </c>
-      <c r="G450" s="18">
-        <v>37.858539999999998</v>
-      </c>
-      <c r="H450" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I450" s="14"/>
-      <c r="J450" s="14"/>
-      <c r="K450" s="20">
-        <v>7</v>
-      </c>
-      <c r="L450" s="20">
-        <v>2014.979</v>
-      </c>
-      <c r="M450" s="83">
-        <v>0.53617000000000004</v>
-      </c>
-      <c r="N450" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="O450" s="20">
-        <v>0</v>
-      </c>
-      <c r="P450" s="20"/>
-      <c r="Q450" s="20">
-        <v>53.616999999999997</v>
-      </c>
-      <c r="R450" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="S450" s="41" t="s">
-        <v>210</v>
-      </c>
-      <c r="T450" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="U450" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="V450" s="76" t="s">
-        <v>197</v>
-      </c>
-      <c r="W450" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="X450" s="20"/>
-      <c r="Y450" s="20"/>
-      <c r="Z450" s="20"/>
-      <c r="AA450" s="20"/>
-      <c r="AB450" s="14"/>
-      <c r="AC450" s="14"/>
-      <c r="AD450" s="14"/>
-      <c r="AE450" s="14"/>
-      <c r="AF450" s="14"/>
-      <c r="AG450" s="14"/>
-      <c r="AH450" s="14"/>
-      <c r="AI450" s="14"/>
-      <c r="AJ450" s="14"/>
-      <c r="AK450" s="14"/>
-      <c r="AL450" s="14"/>
-      <c r="AM450" s="14"/>
-      <c r="AN450" s="10"/>
-      <c r="AO450" s="40"/>
-    </row>
-    <row r="451" spans="1:41" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A451" s="82" t="s">
-        <v>204</v>
-      </c>
-      <c r="B451" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="C451" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D451" s="11"/>
-      <c r="E451" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="F451" s="18">
-        <v>-46.875459999999997</v>
-      </c>
-      <c r="G451" s="18">
-        <v>37.858539999999998</v>
-      </c>
-      <c r="H451" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I451" s="14"/>
-      <c r="J451" s="14"/>
-      <c r="K451" s="20">
-        <v>8</v>
-      </c>
-      <c r="L451" s="20">
-        <v>2016.0619999999999</v>
-      </c>
-      <c r="M451" s="83">
-        <v>0.35596</v>
-      </c>
-      <c r="N451" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="O451" s="20">
-        <v>0</v>
-      </c>
-      <c r="P451" s="20"/>
-      <c r="Q451" s="20">
-        <v>35.595999999999997</v>
-      </c>
-      <c r="R451" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="S451" s="41" t="s">
-        <v>210</v>
-      </c>
-      <c r="T451" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="U451" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="V451" s="76" t="s">
-        <v>197</v>
-      </c>
-      <c r="W451" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="X451" s="20"/>
-      <c r="Y451" s="20"/>
-      <c r="Z451" s="20"/>
-      <c r="AA451" s="20"/>
-      <c r="AB451" s="14"/>
-      <c r="AC451" s="14"/>
-      <c r="AD451" s="14"/>
-      <c r="AE451" s="14"/>
-      <c r="AF451" s="14"/>
-      <c r="AG451" s="14"/>
-      <c r="AH451" s="14"/>
-      <c r="AI451" s="14"/>
-      <c r="AJ451" s="14"/>
-      <c r="AK451" s="14"/>
-      <c r="AL451" s="14"/>
-      <c r="AM451" s="14"/>
-      <c r="AN451" s="10"/>
-      <c r="AO451" s="40"/>
-    </row>
-    <row r="452" spans="1:41" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A452" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="B452" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C452" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D452" s="25"/>
-      <c r="E452" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="F452" s="30">
-        <v>-46.876399999999997</v>
-      </c>
-      <c r="G452" s="30">
-        <v>37.859099999999998</v>
-      </c>
-      <c r="H452" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="I452" s="27"/>
-      <c r="J452" s="27"/>
-      <c r="K452" s="28">
-        <v>1</v>
-      </c>
-      <c r="L452" s="28">
-        <v>1980.0119999999999</v>
-      </c>
-      <c r="M452" s="81">
-        <v>0.35775000000000001</v>
-      </c>
-      <c r="N452" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="O452" s="28">
-        <v>1</v>
-      </c>
-      <c r="P452" s="28"/>
-      <c r="Q452" s="28">
-        <v>0.35775000000000001</v>
-      </c>
-      <c r="R452" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="S452" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="T452" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="U452" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V452" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="W452" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="X452" s="28"/>
-      <c r="Y452" s="28"/>
-      <c r="Z452" s="28"/>
-      <c r="AA452" s="28"/>
-      <c r="AB452" s="27"/>
-      <c r="AC452" s="27"/>
-      <c r="AD452" s="27"/>
-      <c r="AE452" s="27"/>
-      <c r="AF452" s="27"/>
-      <c r="AG452" s="27"/>
-      <c r="AH452" s="27"/>
-      <c r="AI452" s="27"/>
-      <c r="AJ452" s="27"/>
-      <c r="AK452" s="27"/>
-      <c r="AL452" s="27"/>
-      <c r="AM452" s="27"/>
-      <c r="AN452" s="25"/>
-      <c r="AO452" s="25"/>
-    </row>
-    <row r="453" spans="1:41" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A453" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="B453" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C453" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D453" s="25"/>
-      <c r="E453" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="F453" s="30">
-        <v>-46.876399999999997</v>
-      </c>
-      <c r="G453" s="30">
-        <v>37.859099999999998</v>
-      </c>
-      <c r="H453" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="I453" s="27"/>
-      <c r="J453" s="27"/>
-      <c r="K453" s="28">
-        <v>2</v>
-      </c>
-      <c r="L453" s="28">
-        <v>1983.029</v>
-      </c>
-      <c r="M453" s="81">
-        <v>0.45415999999999995</v>
-      </c>
-      <c r="N453" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="O453" s="28">
-        <v>1</v>
-      </c>
-      <c r="P453" s="28"/>
-      <c r="Q453" s="28">
-        <v>0.45415999999999995</v>
-      </c>
-      <c r="R453" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="S453" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="T453" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="U453" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V453" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="W453" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="X453" s="28"/>
-      <c r="Y453" s="28"/>
-      <c r="Z453" s="28"/>
-      <c r="AA453" s="28"/>
-      <c r="AB453" s="27"/>
-      <c r="AC453" s="27"/>
-      <c r="AD453" s="27"/>
-      <c r="AE453" s="27"/>
-      <c r="AF453" s="27"/>
-      <c r="AG453" s="27"/>
-      <c r="AH453" s="27"/>
-      <c r="AI453" s="27"/>
-      <c r="AJ453" s="27"/>
-      <c r="AK453" s="27"/>
-      <c r="AL453" s="27"/>
-      <c r="AM453" s="27"/>
-      <c r="AN453" s="25"/>
-      <c r="AO453" s="25"/>
-    </row>
-    <row r="454" spans="1:41" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A454" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="B454" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C454" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D454" s="25"/>
-      <c r="E454" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="F454" s="30">
-        <v>-46.876399999999997</v>
-      </c>
-      <c r="G454" s="30">
-        <v>37.859099999999998</v>
-      </c>
-      <c r="H454" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="I454" s="27"/>
-      <c r="J454" s="27"/>
-      <c r="K454" s="28">
-        <v>3</v>
-      </c>
-      <c r="L454" s="28">
-        <v>1983.029</v>
-      </c>
-      <c r="M454" s="81">
-        <v>0.64698</v>
-      </c>
-      <c r="N454" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="O454" s="28">
-        <v>1</v>
-      </c>
-      <c r="P454" s="28"/>
-      <c r="Q454" s="28">
-        <v>0.64698</v>
-      </c>
-      <c r="R454" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="S454" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="T454" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="U454" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V454" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="W454" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="X454" s="28"/>
-      <c r="Y454" s="28"/>
-      <c r="Z454" s="28"/>
-      <c r="AA454" s="28"/>
-      <c r="AB454" s="27"/>
-      <c r="AC454" s="27"/>
-      <c r="AD454" s="27"/>
-      <c r="AE454" s="27"/>
-      <c r="AF454" s="27"/>
-      <c r="AG454" s="27"/>
-      <c r="AH454" s="27"/>
-      <c r="AI454" s="27"/>
-      <c r="AJ454" s="27"/>
-      <c r="AK454" s="27"/>
-      <c r="AL454" s="27"/>
-      <c r="AM454" s="27"/>
-      <c r="AN454" s="25"/>
-      <c r="AO454" s="25"/>
-    </row>
-    <row r="455" spans="1:41" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A455" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="B455" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C455" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D455" s="25"/>
-      <c r="E455" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="F455" s="30">
-        <v>-46.876399999999997</v>
-      </c>
-      <c r="G455" s="30">
-        <v>37.859099999999998</v>
-      </c>
-      <c r="H455" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="I455" s="27"/>
-      <c r="J455" s="27"/>
-      <c r="K455" s="28">
-        <v>4</v>
-      </c>
-      <c r="L455" s="28">
-        <v>1991.1369999999999</v>
-      </c>
-      <c r="M455" s="81">
-        <v>0.21408000000000002</v>
-      </c>
-      <c r="N455" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="O455" s="28">
-        <v>0</v>
-      </c>
-      <c r="P455" s="28"/>
-      <c r="Q455" s="28">
-        <v>0.21408000000000002</v>
-      </c>
-      <c r="R455" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="S455" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="T455" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="U455" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V455" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="W455" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="X455" s="28"/>
-      <c r="Y455" s="28"/>
-      <c r="Z455" s="28"/>
-      <c r="AA455" s="28"/>
-      <c r="AB455" s="27"/>
-      <c r="AC455" s="27"/>
-      <c r="AD455" s="27"/>
-      <c r="AE455" s="27"/>
-      <c r="AF455" s="27"/>
-      <c r="AG455" s="27"/>
-      <c r="AH455" s="27"/>
-      <c r="AI455" s="27"/>
-      <c r="AJ455" s="27"/>
-      <c r="AK455" s="27"/>
-      <c r="AL455" s="27"/>
-      <c r="AM455" s="27"/>
-      <c r="AN455" s="25"/>
-      <c r="AO455" s="25"/>
-    </row>
-    <row r="456" spans="1:41" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A456" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="B456" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C456" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D456" s="25"/>
-      <c r="E456" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="F456" s="30">
-        <v>-46.876399999999997</v>
-      </c>
-      <c r="G456" s="30">
-        <v>37.859099999999998</v>
-      </c>
-      <c r="H456" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="I456" s="27"/>
-      <c r="J456" s="27"/>
-      <c r="K456" s="28">
-        <v>5</v>
-      </c>
-      <c r="L456" s="28">
-        <v>1997.2329999999999</v>
-      </c>
-      <c r="M456" s="81">
-        <v>0.78686000000000011</v>
-      </c>
-      <c r="N456" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="O456" s="28">
-        <v>0</v>
-      </c>
-      <c r="P456" s="28"/>
-      <c r="Q456" s="28">
-        <v>0.78686000000000011</v>
-      </c>
-      <c r="R456" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="S456" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="T456" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="U456" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V456" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="W456" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="X456" s="28"/>
-      <c r="Y456" s="28"/>
-      <c r="Z456" s="28"/>
-      <c r="AA456" s="28"/>
-      <c r="AB456" s="27"/>
-      <c r="AC456" s="27"/>
-      <c r="AD456" s="27"/>
-      <c r="AE456" s="27"/>
-      <c r="AF456" s="27"/>
-      <c r="AG456" s="27"/>
-      <c r="AH456" s="27"/>
-      <c r="AI456" s="27"/>
-      <c r="AJ456" s="27"/>
-      <c r="AK456" s="27"/>
-      <c r="AL456" s="27"/>
-      <c r="AM456" s="27"/>
-      <c r="AN456" s="25"/>
-      <c r="AO456" s="25"/>
-    </row>
-    <row r="457" spans="1:41" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A457" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="B457" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C457" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D457" s="25"/>
-      <c r="E457" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="F457" s="30">
-        <v>-46.876399999999997</v>
-      </c>
-      <c r="G457" s="30">
-        <v>37.859099999999998</v>
-      </c>
-      <c r="H457" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="I457" s="27"/>
-      <c r="J457" s="27"/>
-      <c r="K457" s="28">
-        <v>6</v>
-      </c>
-      <c r="L457" s="28">
-        <v>1998.1759999999999</v>
-      </c>
-      <c r="M457" s="81">
-        <v>0.52410000000000001</v>
-      </c>
-      <c r="N457" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="O457" s="28">
-        <v>0</v>
-      </c>
-      <c r="P457" s="28"/>
-      <c r="Q457" s="28">
-        <v>0.52410000000000001</v>
-      </c>
-      <c r="R457" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="S457" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="T457" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="U457" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V457" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="W457" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="X457" s="28"/>
-      <c r="Y457" s="28"/>
-      <c r="Z457" s="28"/>
-      <c r="AA457" s="28"/>
-      <c r="AB457" s="27"/>
-      <c r="AC457" s="27"/>
-      <c r="AD457" s="27"/>
-      <c r="AE457" s="27"/>
-      <c r="AF457" s="27"/>
-      <c r="AG457" s="27"/>
-      <c r="AH457" s="27"/>
-      <c r="AI457" s="27"/>
-      <c r="AJ457" s="27"/>
-      <c r="AK457" s="27"/>
-      <c r="AL457" s="27"/>
-      <c r="AM457" s="27"/>
-      <c r="AN457" s="25"/>
-      <c r="AO457" s="25"/>
-    </row>
-    <row r="458" spans="1:41" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A458" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="B458" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C458" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D458" s="25"/>
-      <c r="E458" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="F458" s="30">
-        <v>-46.876399999999997</v>
-      </c>
-      <c r="G458" s="30">
-        <v>37.859099999999998</v>
-      </c>
-      <c r="H458" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="I458" s="27"/>
-      <c r="J458" s="27"/>
-      <c r="K458" s="28">
-        <v>7</v>
-      </c>
-      <c r="L458" s="28">
-        <v>1999.181</v>
-      </c>
-      <c r="M458" s="81">
-        <v>0.41256999999999999</v>
-      </c>
-      <c r="N458" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="O458" s="28">
-        <v>0</v>
-      </c>
-      <c r="P458" s="28"/>
-      <c r="Q458" s="28">
-        <v>0.41256999999999999</v>
-      </c>
-      <c r="R458" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="S458" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="T458" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="U458" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V458" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="W458" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="X458" s="28"/>
-      <c r="Y458" s="28"/>
-      <c r="Z458" s="28"/>
-      <c r="AA458" s="28"/>
-      <c r="AB458" s="27"/>
-      <c r="AC458" s="27"/>
-      <c r="AD458" s="27"/>
-      <c r="AE458" s="27"/>
-      <c r="AF458" s="27"/>
-      <c r="AG458" s="27"/>
-      <c r="AH458" s="27"/>
-      <c r="AI458" s="27"/>
-      <c r="AJ458" s="27"/>
-      <c r="AK458" s="27"/>
-      <c r="AL458" s="27"/>
-      <c r="AM458" s="27"/>
-      <c r="AN458" s="25"/>
-      <c r="AO458" s="25"/>
-    </row>
-    <row r="459" spans="1:41" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A459" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="B459" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C459" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D459" s="25"/>
-      <c r="E459" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="F459" s="30">
-        <v>-46.876399999999997</v>
-      </c>
-      <c r="G459" s="30">
-        <v>37.859099999999998</v>
-      </c>
-      <c r="H459" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="I459" s="27"/>
-      <c r="J459" s="27"/>
-      <c r="K459" s="28">
-        <v>8</v>
-      </c>
-      <c r="L459" s="28">
-        <v>2000.1869999999999</v>
-      </c>
-      <c r="M459" s="81">
-        <v>0.70369000000000004</v>
-      </c>
-      <c r="N459" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="O459" s="28">
-        <v>0</v>
-      </c>
-      <c r="P459" s="28"/>
-      <c r="Q459" s="28">
-        <v>0.70369000000000004</v>
-      </c>
-      <c r="R459" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="S459" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="T459" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="U459" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V459" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="W459" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="X459" s="28"/>
-      <c r="Y459" s="28"/>
-      <c r="Z459" s="28"/>
-      <c r="AA459" s="28"/>
-      <c r="AB459" s="27"/>
-      <c r="AC459" s="27"/>
-      <c r="AD459" s="27"/>
-      <c r="AE459" s="27"/>
-      <c r="AF459" s="27"/>
-      <c r="AG459" s="27"/>
-      <c r="AH459" s="27"/>
-      <c r="AI459" s="27"/>
-      <c r="AJ459" s="27"/>
-      <c r="AK459" s="27"/>
-      <c r="AL459" s="27"/>
-      <c r="AM459" s="27"/>
-      <c r="AN459" s="25"/>
-      <c r="AO459" s="25"/>
-    </row>
-    <row r="460" spans="1:41" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A460" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="B460" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C460" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D460" s="25"/>
-      <c r="E460" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="F460" s="30">
-        <v>-46.876399999999997</v>
-      </c>
-      <c r="G460" s="30">
-        <v>37.859099999999998</v>
-      </c>
-      <c r="H460" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="I460" s="27"/>
-      <c r="J460" s="27"/>
-      <c r="K460" s="28">
-        <v>9</v>
-      </c>
-      <c r="L460" s="28">
-        <v>2001.2550000000001</v>
-      </c>
-      <c r="M460" s="81">
-        <v>0.44470999999999999</v>
-      </c>
-      <c r="N460" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="O460" s="28">
-        <v>0</v>
-      </c>
-      <c r="P460" s="28"/>
-      <c r="Q460" s="28">
-        <v>0.44470999999999999</v>
-      </c>
-      <c r="R460" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="S460" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="T460" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="U460" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V460" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="W460" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="X460" s="28"/>
-      <c r="Y460" s="28"/>
-      <c r="Z460" s="28"/>
-      <c r="AA460" s="28"/>
-      <c r="AB460" s="27"/>
-      <c r="AC460" s="27"/>
-      <c r="AD460" s="27"/>
-      <c r="AE460" s="27"/>
-      <c r="AF460" s="27"/>
-      <c r="AG460" s="27"/>
-      <c r="AH460" s="27"/>
-      <c r="AI460" s="27"/>
-      <c r="AJ460" s="27"/>
-      <c r="AK460" s="27"/>
-      <c r="AL460" s="27"/>
-      <c r="AM460" s="27"/>
-      <c r="AN460" s="25"/>
-      <c r="AO460" s="25"/>
-    </row>
-    <row r="461" spans="1:41" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A461" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="B461" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C461" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D461" s="25"/>
-      <c r="E461" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="F461" s="30">
-        <v>-46.876399999999997</v>
-      </c>
-      <c r="G461" s="30">
-        <v>37.859099999999998</v>
-      </c>
-      <c r="H461" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="I461" s="27"/>
-      <c r="J461" s="27"/>
-      <c r="K461" s="28">
-        <v>10</v>
-      </c>
-      <c r="L461" s="28">
-        <v>2002.261</v>
-      </c>
-      <c r="M461" s="81">
-        <v>0.73770999999999998</v>
-      </c>
-      <c r="N461" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="O461" s="28">
-        <v>0</v>
-      </c>
-      <c r="P461" s="28"/>
-      <c r="Q461" s="28">
-        <v>0.73770999999999998</v>
-      </c>
-      <c r="R461" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="S461" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="T461" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="U461" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V461" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="W461" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="X461" s="28"/>
-      <c r="Y461" s="28"/>
-      <c r="Z461" s="28"/>
-      <c r="AA461" s="28"/>
-      <c r="AB461" s="27"/>
-      <c r="AC461" s="27"/>
-      <c r="AD461" s="27"/>
-      <c r="AE461" s="27"/>
-      <c r="AF461" s="27"/>
-      <c r="AG461" s="27"/>
-      <c r="AH461" s="27"/>
-      <c r="AI461" s="27"/>
-      <c r="AJ461" s="27"/>
-      <c r="AK461" s="27"/>
-      <c r="AL461" s="27"/>
-      <c r="AM461" s="27"/>
-      <c r="AN461" s="25"/>
-      <c r="AO461" s="25"/>
-    </row>
-    <row r="462" spans="1:41" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A462" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="B462" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C462" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D462" s="25"/>
-      <c r="E462" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="F462" s="30">
-        <v>-46.876399999999997</v>
-      </c>
-      <c r="G462" s="30">
-        <v>37.859099999999998</v>
-      </c>
-      <c r="H462" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="I462" s="27"/>
-      <c r="J462" s="27"/>
-      <c r="K462" s="28">
-        <v>11</v>
-      </c>
-      <c r="L462" s="28">
-        <v>2012.1279999999999</v>
-      </c>
-      <c r="M462" s="81">
-        <v>0.62618000000000007</v>
-      </c>
-      <c r="N462" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="O462" s="28">
-        <v>0</v>
-      </c>
-      <c r="P462" s="28"/>
-      <c r="Q462" s="28">
-        <v>0.62618000000000007</v>
-      </c>
-      <c r="R462" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="S462" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="T462" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="U462" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V462" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="W462" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="X462" s="28"/>
-      <c r="Y462" s="28"/>
-      <c r="Z462" s="28"/>
-      <c r="AA462" s="28"/>
-      <c r="AB462" s="27"/>
-      <c r="AC462" s="27"/>
-      <c r="AD462" s="27"/>
-      <c r="AE462" s="27"/>
-      <c r="AF462" s="27"/>
-      <c r="AG462" s="27"/>
-      <c r="AH462" s="27"/>
-      <c r="AI462" s="27"/>
-      <c r="AJ462" s="27"/>
-      <c r="AK462" s="27"/>
-      <c r="AL462" s="27"/>
-      <c r="AM462" s="27"/>
-      <c r="AN462" s="25"/>
-      <c r="AO462" s="25"/>
-    </row>
-    <row r="463" spans="1:41" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A463" s="80" t="s">
-        <v>211</v>
-      </c>
-      <c r="B463" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C463" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D463" s="25"/>
-      <c r="E463" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="F463" s="30">
-        <v>-46.876399999999997</v>
-      </c>
-      <c r="G463" s="30">
-        <v>37.859099999999998</v>
-      </c>
-      <c r="H463" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="I463" s="27"/>
-      <c r="J463" s="27"/>
-      <c r="K463" s="28">
-        <v>12</v>
-      </c>
-      <c r="L463" s="28">
-        <v>2013.259</v>
-      </c>
-      <c r="M463" s="81">
-        <v>0.54490000000000005</v>
-      </c>
-      <c r="N463" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="O463" s="28">
-        <v>0</v>
-      </c>
-      <c r="P463" s="28"/>
-      <c r="Q463" s="28">
-        <v>0.54490000000000005</v>
-      </c>
-      <c r="R463" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="S463" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="T463" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="U463" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="V463" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="W463" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="X463" s="28"/>
-      <c r="Y463" s="28"/>
-      <c r="Z463" s="28"/>
-      <c r="AA463" s="28"/>
-      <c r="AB463" s="27"/>
-      <c r="AC463" s="27"/>
-      <c r="AD463" s="27"/>
-      <c r="AE463" s="27"/>
-      <c r="AF463" s="27"/>
-      <c r="AG463" s="27"/>
-      <c r="AH463" s="27"/>
-      <c r="AI463" s="27"/>
-      <c r="AJ463" s="27"/>
-      <c r="AK463" s="27"/>
-      <c r="AL463" s="27"/>
-      <c r="AM463" s="27"/>
-      <c r="AN463" s="25"/>
-      <c r="AO463" s="25"/>
-    </row>
-    <row r="464" spans="1:41" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A464" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B464" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C464" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D464" s="11"/>
-      <c r="E464" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F464" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G464" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H464" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I464" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J464" s="41"/>
-      <c r="K464" s="59">
-        <v>1</v>
-      </c>
-      <c r="L464" s="87">
-        <v>23071</v>
-      </c>
-      <c r="M464" s="10"/>
-      <c r="N464" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O464" s="16">
-        <v>1</v>
-      </c>
-      <c r="P464" s="16"/>
-      <c r="Q464" s="20">
-        <v>2</v>
-      </c>
-      <c r="R464" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S464" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T464" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U464" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V464" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W464" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X464" s="20"/>
-      <c r="Y464" s="20"/>
-      <c r="Z464" s="20"/>
-      <c r="AA464" s="14"/>
-      <c r="AB464" s="14"/>
-      <c r="AC464" s="14"/>
-      <c r="AD464" s="14"/>
-      <c r="AE464" s="14"/>
-      <c r="AF464" s="14"/>
-      <c r="AG464" s="14"/>
-      <c r="AH464" s="14"/>
-      <c r="AI464" s="14"/>
-      <c r="AJ464" s="14"/>
-      <c r="AK464" s="14"/>
-      <c r="AL464" s="14"/>
-      <c r="AM464" s="40"/>
-      <c r="AN464" s="40"/>
-    </row>
-    <row r="465" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A465" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B465" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C465" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D465" s="11"/>
-      <c r="E465" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F465" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G465" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H465" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I465" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J465" s="41"/>
-      <c r="K465" s="59">
-        <v>2</v>
-      </c>
-      <c r="L465" s="87">
-        <v>23285</v>
-      </c>
-      <c r="M465" s="10"/>
-      <c r="N465" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O465" s="16">
-        <v>1</v>
-      </c>
-      <c r="P465" s="16"/>
-      <c r="Q465" s="20">
-        <v>2</v>
-      </c>
-      <c r="R465" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S465" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T465" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U465" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V465" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W465" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X465" s="20"/>
-      <c r="Y465" s="20"/>
-      <c r="Z465" s="20"/>
-      <c r="AA465" s="14"/>
-      <c r="AB465" s="14"/>
-      <c r="AC465" s="14"/>
-      <c r="AD465" s="14"/>
-      <c r="AE465" s="14"/>
-      <c r="AF465" s="14"/>
-      <c r="AG465" s="14"/>
-      <c r="AH465" s="14"/>
-      <c r="AI465" s="14"/>
-      <c r="AJ465" s="14"/>
-      <c r="AK465" s="14"/>
-      <c r="AL465" s="14"/>
-      <c r="AM465" s="40"/>
-      <c r="AN465" s="40"/>
-    </row>
-    <row r="466" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A466" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B466" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C466" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D466" s="11"/>
-      <c r="E466" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F466" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G466" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H466" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I466" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J466" s="41"/>
-      <c r="K466" s="59">
-        <v>3</v>
-      </c>
-      <c r="L466" s="87">
-        <v>23651</v>
-      </c>
-      <c r="M466" s="10"/>
-      <c r="N466" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O466" s="16">
-        <v>1</v>
-      </c>
-      <c r="P466" s="16"/>
-      <c r="Q466" s="20">
-        <v>13</v>
-      </c>
-      <c r="R466" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S466" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T466" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U466" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V466" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W466" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X466" s="20"/>
-      <c r="Y466" s="20"/>
-      <c r="Z466" s="20"/>
-      <c r="AA466" s="14"/>
-      <c r="AB466" s="14"/>
-      <c r="AC466" s="14"/>
-      <c r="AD466" s="14"/>
-      <c r="AE466" s="14"/>
-      <c r="AF466" s="14"/>
-      <c r="AG466" s="14"/>
-      <c r="AH466" s="14"/>
-      <c r="AI466" s="14"/>
-      <c r="AJ466" s="14"/>
-      <c r="AK466" s="14"/>
-      <c r="AL466" s="14"/>
-      <c r="AM466" s="40"/>
-      <c r="AN466" s="40"/>
-    </row>
-    <row r="467" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A467" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B467" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C467" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D467" s="11"/>
-      <c r="E467" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F467" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G467" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H467" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I467" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J467" s="41"/>
-      <c r="K467" s="59">
-        <v>4</v>
-      </c>
-      <c r="L467" s="87">
-        <v>27820</v>
-      </c>
-      <c r="M467" s="10"/>
-      <c r="N467" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O467" s="16">
-        <v>1</v>
-      </c>
-      <c r="P467" s="16"/>
-      <c r="Q467" s="20">
-        <v>0</v>
-      </c>
-      <c r="R467" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S467" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T467" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U467" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V467" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W467" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X467" s="20"/>
-      <c r="Y467" s="20"/>
-      <c r="Z467" s="20"/>
-      <c r="AA467" s="14"/>
-      <c r="AB467" s="14"/>
-      <c r="AC467" s="14"/>
-      <c r="AD467" s="14"/>
-      <c r="AE467" s="14"/>
-      <c r="AF467" s="14"/>
-      <c r="AG467" s="14"/>
-      <c r="AH467" s="14"/>
-      <c r="AI467" s="14"/>
-      <c r="AJ467" s="14"/>
-      <c r="AK467" s="14"/>
-      <c r="AL467" s="14"/>
-      <c r="AM467" s="40"/>
-      <c r="AN467" s="40"/>
-    </row>
-    <row r="468" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A468" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B468" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C468" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D468" s="11"/>
-      <c r="E468" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F468" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G468" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H468" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I468" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J468" s="41"/>
-      <c r="K468" s="59">
-        <v>5</v>
-      </c>
-      <c r="L468" s="87">
-        <v>28430</v>
-      </c>
-      <c r="M468" s="10"/>
-      <c r="N468" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O468" s="16">
-        <v>1</v>
-      </c>
-      <c r="P468" s="16"/>
-      <c r="Q468" s="20">
-        <v>0</v>
-      </c>
-      <c r="R468" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S468" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T468" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U468" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V468" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W468" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X468" s="20"/>
-      <c r="Y468" s="20"/>
-      <c r="Z468" s="20"/>
-      <c r="AA468" s="14"/>
-      <c r="AB468" s="14"/>
-      <c r="AC468" s="14"/>
-      <c r="AD468" s="14"/>
-      <c r="AE468" s="14"/>
-      <c r="AF468" s="14"/>
-      <c r="AG468" s="14"/>
-      <c r="AH468" s="14"/>
-      <c r="AI468" s="14"/>
-      <c r="AJ468" s="14"/>
-      <c r="AK468" s="14"/>
-      <c r="AL468" s="14"/>
-      <c r="AM468" s="40"/>
-      <c r="AN468" s="40"/>
-    </row>
-    <row r="469" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A469" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B469" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C469" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D469" s="11"/>
-      <c r="E469" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F469" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G469" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H469" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I469" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J469" s="41"/>
-      <c r="K469" s="59">
-        <v>6</v>
-      </c>
-      <c r="L469" s="87">
-        <v>28795</v>
-      </c>
-      <c r="M469" s="10"/>
-      <c r="N469" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O469" s="16">
-        <v>1</v>
-      </c>
-      <c r="P469" s="16"/>
-      <c r="Q469" s="20">
-        <v>0</v>
-      </c>
-      <c r="R469" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S469" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T469" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U469" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V469" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W469" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X469" s="20"/>
-      <c r="Y469" s="20"/>
-      <c r="Z469" s="20"/>
-      <c r="AA469" s="14"/>
-      <c r="AB469" s="14"/>
-      <c r="AC469" s="14"/>
-      <c r="AD469" s="14"/>
-      <c r="AE469" s="14"/>
-      <c r="AF469" s="14"/>
-      <c r="AG469" s="14"/>
-      <c r="AH469" s="14"/>
-      <c r="AI469" s="14"/>
-      <c r="AJ469" s="14"/>
-      <c r="AK469" s="14"/>
-      <c r="AL469" s="14"/>
-      <c r="AM469" s="40"/>
-      <c r="AN469" s="40"/>
-    </row>
-    <row r="470" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A470" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B470" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C470" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D470" s="11"/>
-      <c r="E470" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F470" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G470" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H470" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I470" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J470" s="41"/>
-      <c r="K470" s="59">
-        <v>7</v>
-      </c>
-      <c r="L470" s="87">
-        <v>31503</v>
-      </c>
-      <c r="M470" s="10"/>
-      <c r="N470" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O470" s="16">
-        <v>0</v>
-      </c>
-      <c r="P470" s="16"/>
-      <c r="Q470" s="20">
-        <v>0</v>
-      </c>
-      <c r="R470" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S470" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T470" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U470" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V470" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W470" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X470" s="20"/>
-      <c r="Y470" s="20"/>
-      <c r="Z470" s="20"/>
-      <c r="AA470" s="14"/>
-      <c r="AB470" s="14"/>
-      <c r="AC470" s="14"/>
-      <c r="AD470" s="14"/>
-      <c r="AE470" s="14"/>
-      <c r="AF470" s="14"/>
-      <c r="AG470" s="14"/>
-      <c r="AH470" s="14"/>
-      <c r="AI470" s="14"/>
-      <c r="AJ470" s="14"/>
-      <c r="AK470" s="14"/>
-      <c r="AL470" s="14"/>
-      <c r="AM470" s="40"/>
-      <c r="AN470" s="40"/>
-    </row>
-    <row r="471" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A471" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B471" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C471" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D471" s="11"/>
-      <c r="E471" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F471" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G471" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H471" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I471" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J471" s="41"/>
-      <c r="K471" s="59">
-        <v>8</v>
-      </c>
-      <c r="L471" s="87">
-        <v>31656</v>
-      </c>
-      <c r="M471" s="10"/>
-      <c r="N471" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O471" s="16">
-        <v>0</v>
-      </c>
-      <c r="P471" s="16"/>
-      <c r="Q471" s="20">
-        <v>26</v>
-      </c>
-      <c r="R471" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S471" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T471" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U471" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V471" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W471" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X471" s="20"/>
-      <c r="Y471" s="20"/>
-      <c r="Z471" s="20"/>
-      <c r="AA471" s="14"/>
-      <c r="AB471" s="14"/>
-      <c r="AC471" s="14"/>
-      <c r="AD471" s="14"/>
-      <c r="AE471" s="14"/>
-      <c r="AF471" s="14"/>
-      <c r="AG471" s="14"/>
-      <c r="AH471" s="14"/>
-      <c r="AI471" s="14"/>
-      <c r="AJ471" s="14"/>
-      <c r="AK471" s="14"/>
-      <c r="AL471" s="14"/>
-      <c r="AM471" s="40"/>
-      <c r="AN471" s="40"/>
-    </row>
-    <row r="472" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A472" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B472" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C472" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D472" s="11"/>
-      <c r="E472" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F472" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G472" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H472" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I472" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="J472" s="41"/>
-      <c r="K472" s="59">
-        <v>9</v>
-      </c>
-      <c r="L472" s="87">
-        <v>33117</v>
-      </c>
-      <c r="M472" s="10"/>
-      <c r="N472" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O472" s="16">
-        <v>0</v>
-      </c>
-      <c r="P472" s="16"/>
-      <c r="Q472" s="20">
-        <v>24</v>
-      </c>
-      <c r="R472" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S472" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T472" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U472" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V472" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W472" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X472" s="20"/>
-      <c r="Y472" s="20"/>
-      <c r="Z472" s="20"/>
-      <c r="AA472" s="14"/>
-      <c r="AB472" s="14"/>
-      <c r="AC472" s="14"/>
-      <c r="AD472" s="14"/>
-      <c r="AE472" s="14"/>
-      <c r="AF472" s="14"/>
-      <c r="AG472" s="14"/>
-      <c r="AH472" s="14"/>
-      <c r="AI472" s="14"/>
-      <c r="AJ472" s="14"/>
-      <c r="AK472" s="14"/>
-      <c r="AL472" s="14"/>
-      <c r="AM472" s="40"/>
-      <c r="AN472" s="40"/>
-    </row>
-    <row r="473" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A473" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="B473" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C473" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D473" s="11"/>
-      <c r="E473" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F473" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G473" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H473" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I473" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="J473" s="41"/>
-      <c r="K473" s="59">
-        <v>1</v>
-      </c>
-      <c r="L473" s="87">
-        <v>23071</v>
-      </c>
-      <c r="M473" s="10"/>
-      <c r="N473" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O473" s="16">
-        <v>1</v>
-      </c>
-      <c r="P473" s="16"/>
-      <c r="Q473" s="20">
-        <v>0</v>
-      </c>
-      <c r="R473" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S473" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T473" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U473" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V473" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W473" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X473" s="20"/>
-      <c r="Y473" s="20"/>
-      <c r="Z473" s="20"/>
-      <c r="AA473" s="14"/>
-      <c r="AB473" s="14"/>
-      <c r="AC473" s="14"/>
-      <c r="AD473" s="14"/>
-      <c r="AE473" s="14"/>
-      <c r="AF473" s="14"/>
-      <c r="AG473" s="14"/>
-      <c r="AH473" s="14"/>
-      <c r="AI473" s="14"/>
-      <c r="AJ473" s="14"/>
-      <c r="AK473" s="14"/>
-      <c r="AL473" s="14"/>
-      <c r="AM473" s="40"/>
-      <c r="AN473" s="40"/>
-    </row>
-    <row r="474" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A474" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="B474" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C474" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D474" s="11"/>
-      <c r="E474" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F474" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G474" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H474" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I474" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="J474" s="41"/>
-      <c r="K474" s="59">
-        <v>2</v>
-      </c>
-      <c r="L474" s="87">
-        <v>23285</v>
-      </c>
-      <c r="M474" s="10"/>
-      <c r="N474" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O474" s="16">
-        <v>1</v>
-      </c>
-      <c r="P474" s="16"/>
-      <c r="Q474" s="20">
-        <v>5</v>
-      </c>
-      <c r="R474" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S474" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T474" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U474" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V474" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W474" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X474" s="20"/>
-      <c r="Y474" s="20"/>
-      <c r="Z474" s="20"/>
-      <c r="AA474" s="14"/>
-      <c r="AB474" s="14"/>
-      <c r="AC474" s="14"/>
-      <c r="AD474" s="14"/>
-      <c r="AE474" s="14"/>
-      <c r="AF474" s="14"/>
-      <c r="AG474" s="14"/>
-      <c r="AH474" s="14"/>
-      <c r="AI474" s="14"/>
-      <c r="AJ474" s="14"/>
-      <c r="AK474" s="14"/>
-      <c r="AL474" s="14"/>
-      <c r="AM474" s="40"/>
-      <c r="AN474" s="40"/>
-    </row>
-    <row r="475" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A475" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="B475" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C475" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D475" s="11"/>
-      <c r="E475" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F475" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G475" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H475" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I475" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="J475" s="41"/>
-      <c r="K475" s="59">
-        <v>3</v>
-      </c>
-      <c r="L475" s="87">
-        <v>23651</v>
-      </c>
-      <c r="M475" s="10"/>
-      <c r="N475" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O475" s="16">
-        <v>0</v>
-      </c>
-      <c r="P475" s="16"/>
-      <c r="Q475" s="20">
-        <v>10</v>
-      </c>
-      <c r="R475" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S475" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T475" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U475" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V475" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W475" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X475" s="20"/>
-      <c r="Y475" s="20"/>
-      <c r="Z475" s="20"/>
-      <c r="AA475" s="14"/>
-      <c r="AB475" s="14"/>
-      <c r="AC475" s="14"/>
-      <c r="AD475" s="14"/>
-      <c r="AE475" s="14"/>
-      <c r="AF475" s="14"/>
-      <c r="AG475" s="14"/>
-      <c r="AH475" s="14"/>
-      <c r="AI475" s="14"/>
-      <c r="AJ475" s="14"/>
-      <c r="AK475" s="14"/>
-      <c r="AL475" s="14"/>
-      <c r="AM475" s="40"/>
-      <c r="AN475" s="40"/>
-    </row>
-    <row r="476" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A476" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="B476" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C476" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D476" s="11"/>
-      <c r="E476" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F476" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G476" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H476" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I476" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="J476" s="41"/>
-      <c r="K476" s="59">
-        <v>4</v>
-      </c>
-      <c r="L476" s="87">
-        <v>27820</v>
-      </c>
-      <c r="M476" s="10"/>
-      <c r="N476" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O476" s="16">
-        <v>0</v>
-      </c>
-      <c r="P476" s="16"/>
-      <c r="Q476" s="20">
-        <v>14</v>
-      </c>
-      <c r="R476" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S476" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T476" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U476" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V476" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W476" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X476" s="20"/>
-      <c r="Y476" s="20"/>
-      <c r="Z476" s="20"/>
-      <c r="AA476" s="14"/>
-      <c r="AB476" s="14"/>
-      <c r="AC476" s="14"/>
-      <c r="AD476" s="14"/>
-      <c r="AE476" s="14"/>
-      <c r="AF476" s="14"/>
-      <c r="AG476" s="14"/>
-      <c r="AH476" s="14"/>
-      <c r="AI476" s="14"/>
-      <c r="AJ476" s="14"/>
-      <c r="AK476" s="14"/>
-      <c r="AL476" s="14"/>
-      <c r="AM476" s="40"/>
-      <c r="AN476" s="40"/>
-    </row>
-    <row r="477" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A477" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="B477" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C477" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D477" s="11"/>
-      <c r="E477" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F477" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G477" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H477" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I477" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="J477" s="41"/>
-      <c r="K477" s="59">
-        <v>5</v>
-      </c>
-      <c r="L477" s="87">
-        <v>28430</v>
-      </c>
-      <c r="M477" s="10"/>
-      <c r="N477" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O477" s="16">
-        <v>0</v>
-      </c>
-      <c r="P477" s="16"/>
-      <c r="Q477" s="20">
-        <v>25</v>
-      </c>
-      <c r="R477" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S477" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T477" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U477" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V477" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W477" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X477" s="20"/>
-      <c r="Y477" s="20"/>
-      <c r="Z477" s="20"/>
-      <c r="AA477" s="14"/>
-      <c r="AB477" s="14"/>
-      <c r="AC477" s="14"/>
-      <c r="AD477" s="14"/>
-      <c r="AE477" s="14"/>
-      <c r="AF477" s="14"/>
-      <c r="AG477" s="14"/>
-      <c r="AH477" s="14"/>
-      <c r="AI477" s="14"/>
-      <c r="AJ477" s="14"/>
-      <c r="AK477" s="14"/>
-      <c r="AL477" s="14"/>
-      <c r="AM477" s="40"/>
-      <c r="AN477" s="40"/>
-    </row>
-    <row r="478" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A478" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="B478" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C478" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D478" s="11"/>
-      <c r="E478" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F478" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G478" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H478" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I478" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="J478" s="41"/>
-      <c r="K478" s="59">
-        <v>6</v>
-      </c>
-      <c r="L478" s="87">
-        <v>28795</v>
-      </c>
-      <c r="M478" s="10"/>
-      <c r="N478" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O478" s="16">
-        <v>0</v>
-      </c>
-      <c r="P478" s="16"/>
-      <c r="Q478" s="20">
-        <v>5</v>
-      </c>
-      <c r="R478" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S478" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T478" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U478" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V478" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W478" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X478" s="20"/>
-      <c r="Y478" s="20"/>
-      <c r="Z478" s="20"/>
-      <c r="AA478" s="14"/>
-      <c r="AB478" s="14"/>
-      <c r="AC478" s="14"/>
-      <c r="AD478" s="14"/>
-      <c r="AE478" s="14"/>
-      <c r="AF478" s="14"/>
-      <c r="AG478" s="14"/>
-      <c r="AH478" s="14"/>
-      <c r="AI478" s="14"/>
-      <c r="AJ478" s="14"/>
-      <c r="AK478" s="14"/>
-      <c r="AL478" s="14"/>
-      <c r="AM478" s="40"/>
-      <c r="AN478" s="40"/>
-    </row>
-    <row r="479" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A479" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="B479" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C479" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D479" s="11"/>
-      <c r="E479" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F479" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G479" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H479" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I479" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="J479" s="41"/>
-      <c r="K479" s="59">
-        <v>7</v>
-      </c>
-      <c r="L479" s="87">
-        <v>31503</v>
-      </c>
-      <c r="M479" s="10"/>
-      <c r="N479" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O479" s="16">
-        <v>0</v>
-      </c>
-      <c r="P479" s="16"/>
-      <c r="Q479" s="20">
-        <v>26</v>
-      </c>
-      <c r="R479" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S479" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T479" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U479" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V479" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W479" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X479" s="20"/>
-      <c r="Y479" s="20"/>
-      <c r="Z479" s="20"/>
-      <c r="AA479" s="14"/>
-      <c r="AB479" s="14"/>
-      <c r="AC479" s="14"/>
-      <c r="AD479" s="14"/>
-      <c r="AE479" s="14"/>
-      <c r="AF479" s="14"/>
-      <c r="AG479" s="14"/>
-      <c r="AH479" s="14"/>
-      <c r="AI479" s="14"/>
-      <c r="AJ479" s="14"/>
-      <c r="AK479" s="14"/>
-      <c r="AL479" s="14"/>
-      <c r="AM479" s="40"/>
-      <c r="AN479" s="40"/>
-    </row>
-    <row r="480" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A480" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="B480" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C480" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D480" s="11"/>
-      <c r="E480" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F480" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G480" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H480" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I480" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="J480" s="41"/>
-      <c r="K480" s="59">
-        <v>8</v>
-      </c>
-      <c r="L480" s="87">
-        <v>31656</v>
-      </c>
-      <c r="M480" s="10"/>
-      <c r="N480" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O480" s="16">
-        <v>0</v>
-      </c>
-      <c r="P480" s="16"/>
-      <c r="Q480" s="20">
-        <v>12</v>
-      </c>
-      <c r="R480" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S480" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T480" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U480" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V480" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W480" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X480" s="20"/>
-      <c r="Y480" s="20"/>
-      <c r="Z480" s="20"/>
-      <c r="AA480" s="14"/>
-      <c r="AB480" s="14"/>
-      <c r="AC480" s="14"/>
-      <c r="AD480" s="14"/>
-      <c r="AE480" s="14"/>
-      <c r="AF480" s="14"/>
-      <c r="AG480" s="14"/>
-      <c r="AH480" s="14"/>
-      <c r="AI480" s="14"/>
-      <c r="AJ480" s="14"/>
-      <c r="AK480" s="14"/>
-      <c r="AL480" s="14"/>
-      <c r="AM480" s="40"/>
-      <c r="AN480" s="40"/>
-    </row>
-    <row r="481" spans="1:40" s="19" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A481" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="B481" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C481" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D481" s="11"/>
-      <c r="E481" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F481" s="18">
-        <v>-4.5</v>
-      </c>
-      <c r="G481" s="18">
-        <v>-172</v>
-      </c>
-      <c r="H481" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I481" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="J481" s="41"/>
-      <c r="K481" s="59">
-        <v>9</v>
-      </c>
-      <c r="L481" s="87">
-        <v>33117</v>
-      </c>
-      <c r="M481" s="10"/>
-      <c r="N481" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="O481" s="16">
-        <v>0</v>
-      </c>
-      <c r="P481" s="16"/>
-      <c r="Q481" s="20">
-        <v>18</v>
-      </c>
-      <c r="R481" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="S481" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="T481" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="U481" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V481" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="W481" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="X481" s="20"/>
-      <c r="Y481" s="20"/>
-      <c r="Z481" s="20"/>
-      <c r="AA481" s="14"/>
-      <c r="AB481" s="14"/>
-      <c r="AC481" s="14"/>
-      <c r="AD481" s="14"/>
-      <c r="AE481" s="14"/>
-      <c r="AF481" s="14"/>
-      <c r="AG481" s="14"/>
-      <c r="AH481" s="14"/>
-      <c r="AI481" s="14"/>
-      <c r="AJ481" s="14"/>
-      <c r="AK481" s="14"/>
-      <c r="AL481" s="14"/>
-      <c r="AM481" s="40"/>
-      <c r="AN481" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
